--- a/output/requirements_matrix/ALP_requirements_matrix.xlsx
+++ b/output/requirements_matrix/ALP_requirements_matrix.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L135"/>
+  <dimension ref="A1:L154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T16:52:33Z by SETUP | data 1056b7942a4e71f0</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T17:19:53Z by SETUP | data 18b487674243d713</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Site location</t>
+          <t>Site location and area</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>The Site is located on the northern Marmara coast of Türkiye (coastal industrial zone), approximately 12 hectares, levelled to +15.0 m above mean sea level, with direct access to the sea for cooling water intake and outfall.</t>
+          <t>The Site is a 12.0 ha plot (400 m east-west x 300 m north-south) on the northern Marmara coast, levelled by the Owner to +15.0 m, plant grid origin at the south-west corner, plant north = true north. The usable area after the 60 m public coastal strip, the 10 m stream-channel buffer on the west boundary and the 5 m landscaping strip is about 10.6 ha. A further 5 ha temporary construction area north of the plot is provided by the Owner (tie-in TP-A1). Details and existing features per ALP-OWN-GEN-001.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1085,7 +1085,8 @@
       <c r="I15" s="4" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0001</t>
+          <t>design_parameter/DP-CASE-0001
+design_parameter/DP-OWNR-0044</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1117,7 +1118,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Equipment shall operate at full capability between ambient dry-bulb temperatures of -8 degC and +40 degC, relative humidity 20 % to 100 %, and shall be designed for survival (not operation) between -15 degC and +45 degC.</t>
+          <t>Equipment shall operate at full capability between -8 degC and +40 degC dry bulb and 18 % to 100 % relative humidity, and survive -15 degC to +45 degC. Climatic data per ALP-OWN-MET-001 (10-year site record; extremes -11.4 degC / +39.6 degC).</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1169,7 +1170,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Guarantees refer to: ambient dry-bulb temperature 15.0 degC; relative humidity 70 %; barometric pressure 1011.5 mbar; seawater temperature at intake 16.0 degC; natural gas per ER-03.02 reference composition; grid frequency 50.0 Hz; power factor 0.85 lagging.</t>
+          <t>Guarantees refer to: ambient dry-bulb temperature 15.0 degC; relative humidity 70 %; barometric pressure 1011.5 mbar; seawater temperature at intake 16.0 degC (contractual reference; the measured annual mean of 15.4 degC in ALP-OWN-MAR-001 applies to the design range only); natural gas per ER-03.02 reference composition; grid frequency 50.0 Hz; power factor 0.85 lagging.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1222,7 +1223,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Seawater temperature range 6 degC to 27 degC at the intake; salinity 22 g/l to 26 g/l; suspended solids up to 50 mg/l during storms; presence of jellyfish and mussel larvae shall be considered in screen and biofouling design.</t>
+          <t>Seawater quality, temperature and marine conditions per ALP-OWN-MAR-001 (two-layer sea, pycnocline at 20 m to 25 m). Design range at the intake depth 6.9 degC to 27.0 degC, chloride up to 14,500 mg/l, TSS up to 140 mg/l in storms, occasional H2S in the lower layer, mussel settlement, jellyfish blooms up to 20 kg/m3 and mucilage events.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1505,41 +1506,51 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>ER-03.01</t>
+          <t>ER-02.10</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>ER-03 Fuel</t>
+          <t>ER-02 Site conditions and design data</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Fuel</t>
+          <t>Airborne salt and dust</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>The only fuel is pipeline natural gas from the national transmission system. No back-up liquid fuel is required; space shall be reserved for a future distillate system.</t>
+          <t>The plant shall be designed for the airborne contaminants in ALP-OWN-MET-001 section 6: sea-salt aerosol up to 165 ug/m3 (as NaCl) during lodos storms, chloride deposition up to 420 mg/m2 per day, PM10 up to 260 ug/m3. The gas turbine inlet air filtration shall keep sodium plus potassium at the compressor inlet within the OEM limit for all these conditions, including high-humidity and fog (coalescer/droplet separator stage upstream of the fine filters, hydrophobic final filters of class E12 or better). Outdoor electrical equipment: creepage distance for very heavy pollution (IEC 60815, 31 mm/kV).</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="n"/>
+          <t>analysis</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Filter design report with OEM confirmation (Na+K at compressor inlet below OEM limit at 165 ug/m3 NaCl); Na+K air sampler downstream of the filters with 12 months of data reported during the Defects Notification Period</t>
+        </is>
+      </c>
       <c r="H24" s="4" t="n"/>
       <c r="I24" s="4" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-OWNR-0005
+design_parameter/DP-OWNR-0007
+design_parameter/DP-OWNR-0008</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1551,47 +1562,42 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>ER-03.02</t>
+          <t>ER-02.11</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>ER-03 Fuel</t>
+          <t>ER-02 Site conditions and design data</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Fuel gas specification</t>
+          <t>Design ambient points</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Reference composition (mol %): CH4 93.0, C2H6 3.5, C3H8 0.8, C4+ 0.3, N2 1.6, CO2 0.8; LHV 48.4 MJ/kg. The plant shall accept the full network range: LHV 45.0 MJ/kg to 50.0 MJ/kg, Wobbe index 47 MJ/Nm3 to 52 MJ/Nm3, H2S below 5 mg/Nm3, and hydrogen admixture up to 10 vol %.</t>
+          <t>HVAC and cooling design: summer 0.4 % 32.8 degC / 48 % RH; freeze protection and heating: winter 99.6 % -4.8 degC; performance test ambient range 5 degC to 30 degC (ALP-OWN-MET-001 sections 3 and 7). Heat tracing for all outdoor water-filled lines and instruments.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>hvac</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>analysis</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>OEM confirmation of fuel range and H2 capability</t>
-        </is>
-      </c>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n"/>
       <c r="H25" s="4" t="n"/>
       <c r="I25" s="4" t="inlineStr"/>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0018
-design_parameter/DP-CASE-0019
-design_parameter/DP-CASE-0020
-design_parameter/DP-CASE-0021</t>
+          <t>design_parameter/DP-OWNR-0001
+design_parameter/DP-OWNR-0002
+design_parameter/DP-OWNR-0010</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -1608,27 +1614,27 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>ER-03.03</t>
+          <t>ER-02.12</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>ER-03 Fuel</t>
+          <t>ER-02 Site conditions and design data</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Gas supply conditions at terminal point</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Pressure at the terminal point 45 barg to 70 barg; temperature 5 degC to 25 degC. The gas receiving station shall provide the GT fuel skid with gas at the OEM-required pressure and superheat under all conditions without gas compressors.</t>
+          <t>Lightning protection per IEC 62305 with a risk assessment based on 26 thunderstorm days per year and ground flash density 2.4 flashes/km2/year (ALP-OWN-MET-001 section 5).</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1641,8 +1647,7 @@
       <c r="I26" s="4" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0022
-design_parameter/DP-CASE-0023</t>
+          <t>design_parameter/DP-OWNR-0009</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -1659,27 +1664,27 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>ER-03.04</t>
+          <t>ER-02.13</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>ER-03 Fuel</t>
+          <t>ER-02 Site conditions and design data</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Gas receiving and fiscal metering station</t>
+          <t>Existing features on the Site</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>2x100 % filtration/separation, 2x100 % water-bath or electric heaters, 2x100 % pressure-reduction streams with active/monitor regulators and slam-shut valves; fiscal metering with 2x100 % ultrasonic meters (OIML R137 accuracy class 0.5), on-line gas chromatograph and flow computers complying with the network operator's requirements.</t>
+          <t>The Contractor shall demolish and remove the abandoned warehouse foundations (E 300-360, N 20-60), protect the Owner's meteorological mast and groundwater wells, and keep clear of the buried 11 kV cable along the east boundary until the Owner has had it relocated (ALP-OWN-GEN-001 section 2).</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>civil</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1705,27 +1710,27 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>ER-03.05</t>
+          <t>ER-02.14</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>ER-03 Fuel</t>
+          <t>ER-02 Site conditions and design data</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Performance fuel gas heating</t>
+          <t>Access and transport</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>The GT fuel gas shall be preheated with intermediate-pressure feedwater to the OEM-optimised temperature (about 200 degC) to maximise combined cycle efficiency; a start-up heater shall be provided.</t>
+          <t>The Contractor is responsible for the transport of all plant to Site, including route surveys, permits for abnormal loads and temporary works, taking into account the 120 t bridge limits on the state road (ALP-OWN-GEN-001 section 3). Heavy components shall be landed through a temporary barge landing on the public coastal strip, designed, built, operated and removed by the Contractor; the Owner obtains the coastal permit (tie-in TP-M1).</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>civil</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1736,10 +1741,14 @@
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="4" t="n"/>
       <c r="I28" s="4" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-OWNR-0045</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1751,22 +1760,22 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>ER-04.01</t>
+          <t>ER-03.01</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>ER-04 Performance and operational requirements</t>
+          <t>ER-03 Fuel</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Net electrical output</t>
+          <t>Fuels</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Guaranteed net electrical output at SRC: not less than 600.0 MW at the 380 kV terminal point.</t>
+          <t>Primary fuel: pipeline natural gas per ALP-OWN-FUL-001. Secondary (back-up) fuel: light diesel oil (LDO) per ALP-OWN-FUL-002, for up to 500 hours per year. The gas turbine shall be dual-fuel with automatic transfer between fuels.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1776,32 +1785,16 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>&gt;= 600.0 MW corrected to SRC</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>PG-01</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>&gt;= 600 MW</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>design_parameter/DP-CASE-0028</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -1813,22 +1806,22 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>ER-04.02</t>
+          <t>ER-03.02</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>ER-04 Performance and operational requirements</t>
+          <t>ER-03 Fuel</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Net heat rate</t>
+          <t>Natural gas specification</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Guaranteed net heat rate at SRC: not more than 5,860 kJ/kWh (LHV), corresponding to a net efficiency of about 61.4 %.</t>
+          <t>The plant shall operate on the full natural gas range of ALP-OWN-FUL-001 sections 2 to 4: CH4 85.0 to 98.5 mol %, C2H6 up to 7.0 %, C3H8 up to 2.5 %, C4 up to 1.0 %, C5+ up to 0.2 %, N2 up to 4.0 %, CO2 up to 2.5 %, O2 up to 0.02 %; LHV 44.2 MJ/kg to 50.0 MJ/kg (emission limits apply over the whole range; performance guarantees at the reference gas); Wobbe index (GCV) 47.2 MJ/Sm3 to 51.8 MJ/Sm3 with rate of change up to 1 %/min. Hydrogen admixture up to 5 vol % without modification and with all guarantees; provisions for 10 vol % by future OEM retrofit (fuel system materials, gas detection, control system capacity). Reference composition for guarantees: CH4 93.0, C2H6 3.5, C3H8 0.8, i-C4 0.15, n-C4 0.15, C5+ 0.05, N2 1.55, CO2 0.8 mol %; LHV 48.4 MJ/kg.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1838,27 +1831,23 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>analysis</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>&lt;= 5,860 kJ/kWh corrected to SRC</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>PG-02</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 5860 kJ/kWh</t>
-        </is>
-      </c>
+          <t>OEM fuel specification compliance statement for the full range</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0029</t>
+          <t>design_parameter/DP-CASE-0018
+design_parameter/DP-CASE-0019
+design_parameter/DP-CASE-0020
+design_parameter/DP-CASE-0021
+design_parameter/DP-OWNR-0024</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -1875,22 +1864,22 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>ER-04.03</t>
+          <t>ER-03.03</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>ER-04 Performance and operational requirements</t>
+          <t>ER-03 Fuel</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Part-load efficiency</t>
+          <t>Gas supply conditions at terminal point</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Net heat rate at 60 % plant load shall not exceed 6,250 kJ/kWh (LHV) at SRC.</t>
+          <t>Pressure at the terminal point TP-G1: normal 55-65 barg, minimum 45 barg for full load, exceptional 40 barg for up to 72 h/year; temperature 5-25 degC (ALP-OWN-FUL-001 section 6). No gas compressor is provided: between 40 and 45 barg the gas turbine operates on gas at the pressure-limited load (about 60 % GT load at 40 barg); below 40 barg the control system transfers automatically to LDO (ER-03.10).</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1900,27 +1889,16 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>&lt;= 6,250 kJ/kWh</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>PG-03</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 6250 kJ/kWh</t>
-        </is>
-      </c>
+          <t>analysis</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="inlineStr"/>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0030</t>
+          <t>design_parameter/DP-CASE-0022
+design_parameter/DP-CASE-0023</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -1937,59 +1915,41 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>ER-04.04</t>
+          <t>ER-03.04</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>ER-04 Performance and operational requirements</t>
+          <t>ER-03 Fuel</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Start-up times</t>
+          <t>Gas receiving and fiscal metering station</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>From GT ignition to base load: hot start (shutdown &lt; 8 h) &lt;= 45 min; warm start (8 h to 48 h) &lt;= 90 min; cold start (&gt; 48 h) &lt;= 180 min, without exceeding the life consumption limits agreed with the OEM.</t>
+          <t>2x100 % filtration/separation, 2x100 % water-bath or electric heaters, 2x100 % pressure-reduction streams with active/monitor regulators and slam-shut valves; fiscal metering with 2x100 % ultrasonic meters (OIML R137 accuracy class 0.5), on-line gas chromatograph and flow computers complying with the network operator's requirements.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>demonstration</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>Hot start &lt;= 45 min demonstrated three times</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>PG-09</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 45 min</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>design_parameter/DP-CASE-0037
-design_parameter/DP-CASE-0038
-design_parameter/DP-CASE-0039</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>inspection</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2001,57 +1961,41 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>ER-04.05</t>
+          <t>ER-03.05</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>ER-04 Performance and operational requirements</t>
+          <t>ER-03 Fuel</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Load ramp rate</t>
+          <t>Performance fuel gas heating</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Combined cycle load ramp rate of at least 35 MW/min between minimum environmental load and base load.</t>
+          <t>The GT fuel gas shall be preheated with intermediate-pressure feedwater to the OEM-optimised temperature (about 200 degC) to maximise combined cycle efficiency; a start-up heater shall be provided.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>i_and_c</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>demonstration</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>&gt;= 35 MW/min</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>PG-10</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>&gt;= 35 MW/min</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>design_parameter/DP-CASE-0032</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2063,22 +2007,22 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>ER-04.06</t>
+          <t>ER-03.06</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>ER-04 Performance and operational requirements</t>
+          <t>ER-03 Fuel</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Minimum environmental load</t>
+          <t>Natural gas contaminant limits</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Stable emissions-compliant operation shall be possible down to 40 % of plant net output or lower.</t>
+          <t>At the gas turbine fuel skid inlet the gas shall meet the OEM limits and at least: total sulphur &lt;= 30 mg S/Sm3; H2S + COS &lt;= 5 mg/Sm3; mercury &lt;= 1 ug/Sm3; sodium + potassium, lead, vanadium and calcium within the OEM trace-metal limits (network data below 0.005 mg/Sm3, not guaranteed by the network operator); no free liquids; particulates removed to the OEM limit (coalescing filter-separators, 3 um absolute final filtration); superheat at least 28 K above the hydrocarbon and water dew points at all loads. The Contractor shall provide continuous monitoring of H2S and total sulphur and periodic sampling points for trace metals and mercury.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -2088,27 +2032,23 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>demonstration</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>&lt;= 40 %</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>PG-11</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 40 % of plant net output</t>
-        </is>
-      </c>
+          <t>Gas conditioning design and commissioning samples within limits</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0033</t>
+          <t>design_parameter/DP-OWNR-0025
+design_parameter/DP-OWNR-0026
+design_parameter/DP-OWNR-0027
+design_parameter/DP-OWNR-0028
+design_parameter/DP-OWNR-0029</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -2125,27 +2065,27 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>ER-04.07</t>
+          <t>ER-03.07</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>ER-04 Performance and operational requirements</t>
+          <t>ER-03 Fuel</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Frequency and voltage support</t>
+          <t>Light diesel oil specification and burner limits</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>The plant shall provide primary and secondary frequency control, fast frequency response and reactive power support as required by the Grid Code, including operation within 47.5 Hz to 52.5 Hz for the durations specified therein.</t>
+          <t>LDO as delivered per ALP-OWN-FUL-002 (TS EN 590 based: density 820-845 kg/m3, viscosity 2.0-4.5 mm2/s at 40 degC, flash point &gt;= 55 degC, sulphur &lt;= 10 mg/kg, water &lt;= 200 mg/kg, ash &lt;= 0.01 %, FAME &lt;= 7 %, LHV 42.6-43.2 MJ/kg). At the gas turbine fuel inlet: Na + K &lt;= 0.5 mg/kg, vanadium &lt;= 0.5 mg/kg, lead &lt;= 1.0 mg/kg, calcium &lt;= 2.0 mg/kg, water &lt;= 100 mg/kg, filtration to 5 um, or stricter OEM limits.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>electrical</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2155,14 +2095,17 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Grid Code compliance tests accepted by the TSO</t>
+          <t>Fuel samples at GT inlet within limits during LDO tests</t>
         </is>
       </c>
       <c r="H35" s="4" t="n"/>
       <c r="I35" s="4" t="inlineStr"/>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0026</t>
+          <t>design_parameter/DP-OWNR-0034
+design_parameter/DP-OWNR-0035
+design_parameter/DP-OWNR-0036
+design_parameter/DP-OWNR-0037</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -2179,32 +2122,32 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>ER-04.08</t>
+          <t>ER-03.08</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>ER-04 Performance and operational requirements</t>
+          <t>ER-03 Fuel</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Reactive capability</t>
+          <t>LDO unloading and storage</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Each generator shall be capable of power factor 0.85 lagging to 0.95 leading at rated active power at the generator terminals.</t>
+          <t>Road tanker unloading station with 4 bays (metering, strainers, spill containment, earthing), and two vertical fixed-roof storage tanks each of 3,500 m3 net working volume (together 72 hours of base-load operation on LDO; heel and fire-fighting reserves in addition), in a bund of 110 % of the largest tank, with foam fire protection per NFPA 11 and NFPA 30, level/leak monitoring and water draw-off. Operation beyond the storage autonomy is not required (resupply is limited to 25 trucks/day).</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>electrical</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>inspection</t>
         </is>
       </c>
       <c r="G36" s="5" t="n"/>
@@ -2212,7 +2155,7 @@
       <c r="I36" s="4" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0027</t>
+          <t>design_parameter/DP-OWNR-0038</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -2229,32 +2172,32 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>ER-04.09</t>
+          <t>ER-03.09</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>ER-04 Performance and operational requirements</t>
+          <t>ER-03 Fuel</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>House load and island operation</t>
+          <t>LDO forwarding and treatment</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>The unit shall survive a full load rejection to house load and remain in stable operation for at least 60 minutes.</t>
+          <t>2 x 100 % forwarding pumps, duplex filters, flow metering, and a mandatory fuel treatment system of 2 x 100 % centrifugal separators with water washing, sized to reduce Na+K from 1.8 mg/kg to below the ER-03.07 limit at the gas turbine inlet.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>i_and_c</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>demonstration</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G37" s="5" t="n"/>
@@ -2275,45 +2218,53 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>ER-04.10</t>
+          <t>ER-03.10</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>ER-04 Performance and operational requirements</t>
+          <t>ER-03 Fuel</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Auxiliary power</t>
+          <t>Fuel transfer and LDO start</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Auxiliary power consumption at base load shall not exceed 2.2 % of gross output; the value is included in the net output guarantee.</t>
+          <t>Automatic transfer from gas to LDO on loss of gas supply pressure, from any load between minimum environmental load and base load, without unit trip; manual on-load transfer back to gas; black start is not required but start-up on LDO with grid power shall be possible. Purging and liquid fuel system recirculation to avoid coking during gas operation.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>electrical</t>
+          <t>i_and_c</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>design_parameter/DP-CASE-0031</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>demonstration</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Automatic transfer demonstrated at 50 % and 100 % load</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>PG-18</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>&gt;= 100 % successful transfers</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2325,22 +2276,22 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>ER-04.11</t>
+          <t>ER-03.11</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>ER-04 Performance and operational requirements</t>
+          <t>ER-03 Fuel</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Degradation</t>
+          <t>NOx control and SCR on LDO</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>The Contractor shall submit recoverable and non-recoverable degradation curves for output and heat rate over 48,000 EOH; they apply for test corrections.</t>
+          <t>NOx on LDO shall be controlled by water injection (demineralised water) and the SCR; the SCR and ammonia system shall be designed for LDO operation (sulphur 10 mg/kg, ammonium bisulphate risk at the cold end).</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -2350,12 +2301,20 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G39" s="5" t="n"/>
-      <c r="H39" s="4" t="n"/>
-      <c r="I39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>PG-17</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 50 mg/Nm3</t>
+        </is>
+      </c>
       <c r="J39" s="5" t="inlineStr"/>
       <c r="K39" s="6" t="inlineStr">
         <is>
@@ -2371,7 +2330,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>ER-04.12</t>
+          <t>ER-04.01</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -2381,31 +2340,47 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Availability target</t>
+          <t>Net electrical output</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>The design shall support an equivalent availability factor of at least 93 % averaged over the first six years, considering the OEM maintenance programme.</t>
+          <t>Guaranteed net electrical output at SRC: not less than 600.0 MW at the 380 kV terminal point.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>analysis</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>&gt;= 600.0 MW corrected to SRC</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>PG-01</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>&gt;= 600 MW</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-CASE-0028</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2417,41 +2392,57 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>ER-05.01</t>
+          <t>ER-04.02</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>ER-05 Gas turbine</t>
+          <t>ER-04 Performance and operational requirements</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Gas turbine type</t>
+          <t>Net heat rate</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Heavy-duty, single-shaft, 50 Hz, H-class (or equivalent) gas turbine with dry low-NOx combustion capable of the fuel range in ER-03.02.</t>
+          <t>Guaranteed net heat rate at SRC: not more than 5,860 kJ/kWh (LHV), corresponding to a net efficiency of about 61.4 %.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr"/>
-      <c r="K41" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>&lt;= 5,860 kJ/kWh corrected to SRC</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>PG-02</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 5860 kJ/kWh</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-CASE-0029</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -2463,41 +2454,57 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>ER-05.02</t>
+          <t>ER-04.03</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>ER-05 Gas turbine</t>
+          <t>ER-04 Performance and operational requirements</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Inlet air system</t>
+          <t>Part-load efficiency</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Three-stage static air filtration (coastal environment, final stage EPA E12 per EN 1822), anti-icing, evaporative cooler provision, silencer.</t>
+          <t>Net heat rate at 60 % plant load shall not exceed 6,250 kJ/kWh (LHV) at SRC.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>inspection</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr"/>
-      <c r="K42" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>&lt;= 6,250 kJ/kWh</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>PG-03</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 6250 kJ/kWh</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-CASE-0030</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2509,27 +2516,27 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>ER-05.03</t>
+          <t>ER-04.04</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>ER-05 Gas turbine</t>
+          <t>ER-04 Performance and operational requirements</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Combustion dynamics monitoring</t>
+          <t>Start-up times</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>On-line combustion dynamics monitoring with automatic tuning shall be provided.</t>
+          <t>From GT ignition to base load: hot start (shutdown &lt; 8 h) &lt;= 45 min; warm start (8 h to 48 h) &lt;= 90 min; cold start (&gt; 48 h) &lt;= 180 min, without exceeding the life consumption limits agreed with the OEM.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>i_and_c</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2537,13 +2544,31 @@
           <t>demonstration</t>
         </is>
       </c>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="inlineStr"/>
-      <c r="J43" s="5" t="inlineStr"/>
-      <c r="K43" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Hot start &lt;= 45 min demonstrated three times</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>PG-09</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 45 min</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-CASE-0037
+design_parameter/DP-CASE-0038
+design_parameter/DP-CASE-0039</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -2555,41 +2580,57 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>ER-05.04</t>
+          <t>ER-04.05</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>ER-05 Gas turbine</t>
+          <t>ER-04 Performance and operational requirements</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Enclosure and ventilation</t>
+          <t>Load ramp rate</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Acoustic enclosure with ventilation, gas detection and fire suppression suitable for the hazardous area classification.</t>
+          <t>Combined cycle load ramp rate of at least 35 MW/min between minimum environmental load and base load.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>i_and_c</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>inspection</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
-      <c r="K44" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>demonstration</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>&gt;= 35 MW/min</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>PG-10</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>&gt;= 35 MW/min</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-CASE-0032</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2601,41 +2642,57 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>ER-05.05</t>
+          <t>ER-04.06</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>ER-05 Gas turbine</t>
+          <t>ER-04 Performance and operational requirements</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Compressor washing</t>
+          <t>Minimum environmental load</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>On-line and off-line compressor washing systems with detergent skid.</t>
+          <t>Stable emissions-compliant operation shall be possible down to 40 % of plant net output or lower.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>inspection</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr"/>
-      <c r="K45" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>demonstration</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>&lt;= 40 %</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>PG-11</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 40 % of plant net output</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-CASE-0033</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -2647,41 +2704,49 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>ER-05.06</t>
+          <t>ER-04.07</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>ER-05 Gas turbine</t>
+          <t>ER-04 Performance and operational requirements</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Condition monitoring and remote diagnostics</t>
+          <t>Frequency and voltage support</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Vibration, performance and combustion monitoring with secure remote diagnostic access for the OEM (IEC 62443 compliant).</t>
+          <t>The plant shall provide primary and secondary frequency control, fast frequency response and reactive power support as required by the Grid Code, including operation within 47.5 Hz to 52.5 Hz for the durations specified therein.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>i_and_c</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="n"/>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Grid Code compliance tests accepted by the TSO</t>
+        </is>
+      </c>
       <c r="H46" s="4" t="n"/>
       <c r="I46" s="4" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-CASE-0026</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -2693,41 +2758,45 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>ER-05.07</t>
+          <t>ER-04.08</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>ER-05 Gas turbine</t>
+          <t>ER-04 Performance and operational requirements</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Maintenance intervals</t>
+          <t>Reactive capability</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Hot gas path inspection interval shall be not less than 25,000 EOH and major inspection not less than 50,000 EOH at the operating regime of ER-01.03.</t>
+          <t>Each generator shall be capable of power factor 0.85 lagging to 0.95 leading at rated active power at the generator terminals.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G47" s="5" t="n"/>
       <c r="H47" s="4" t="n"/>
       <c r="I47" s="4" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-CASE-0027</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -2739,32 +2808,32 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>ER-06.01</t>
+          <t>ER-04.09</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>ER-06 Heat recovery steam generator</t>
+          <t>ER-04 Performance and operational requirements</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>HRSG type</t>
+          <t>House load and island operation</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Horizontal-gas-flow, triple-pressure, reheat, natural-circulation HRSG, designed for fast cycling (Benson or equivalent HP section acceptable).</t>
+          <t>The unit shall survive a full load rejection to house load and remain in stable operation for at least 60 minutes.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>i_and_c</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>demonstration</t>
         </is>
       </c>
       <c r="G48" s="5" t="n"/>
@@ -2785,45 +2854,45 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>ER-06.02</t>
+          <t>ER-04.10</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>ER-06 Heat recovery steam generator</t>
+          <t>ER-04 Performance and operational requirements</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Design code</t>
+          <t>Auxiliary power</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Pressure parts per ASME Section I or EN 12952, PED 2014/68/EU conformity assessment by a notified body.</t>
+          <t>Auxiliary power consumption at base load shall not exceed 2.2 % of gross output; the value is included in the net output guarantee.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>inspection</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>PED certificates delivered</t>
-        </is>
-      </c>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n"/>
       <c r="H49" s="4" t="n"/>
       <c r="I49" s="4" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-CASE-0031</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -2835,22 +2904,22 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>ER-06.03</t>
+          <t>ER-04.11</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>ER-06 Heat recovery steam generator</t>
+          <t>ER-04 Performance and operational requirements</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>SCR and CO catalyst</t>
+          <t>Degradation</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>In-duct SCR with aqueous ammonia (&lt; 25 %) injection and an oxidation catalyst sized for the emission guarantees at end of catalyst life (24,000 h).</t>
+          <t>The Contractor shall submit recoverable and non-recoverable degradation curves for output and heat rate over 48,000 EOH; they apply for test corrections.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -2860,20 +2929,12 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G50" s="5" t="n"/>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>PG-04</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 30 mg/Nm3</t>
-        </is>
-      </c>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr"/>
       <c r="K50" s="6" t="inlineStr">
         <is>
@@ -2889,32 +2950,32 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>ER-06.04</t>
+          <t>ER-04.12</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>ER-06 Heat recovery steam generator</t>
+          <t>ER-04 Performance and operational requirements</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Ammonia system</t>
+          <t>Availability target</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Aqueous ammonia storage (2x7 days at base load), unloading, vaporisation and dosing with leak detection and bunding.</t>
+          <t>The design shall support an equivalent availability factor of at least 93 % averaged over the first six years, considering the OEM maintenance programme.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>general</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>inspection</t>
+          <t>analysis</t>
         </is>
       </c>
       <c r="G51" s="5" t="n"/>
@@ -2935,22 +2996,22 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>ER-06.05</t>
+          <t>ER-05.01</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>ER-06 Heat recovery steam generator</t>
+          <t>ER-05 Gas turbine</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Cycling capability</t>
+          <t>Gas turbine type</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>The HRSG shall withstand the start regime of ER-01.03 without drum or header fatigue beyond design life (fatigue analysis per EN 12952-3).</t>
+          <t>Heavy-duty, single-shaft, 50 Hz, H-class (or equivalent) gas turbine with dry low-NOx combustion capable of the fuel range in ER-03.02.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -2960,7 +3021,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>analysis</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G52" s="5" t="n"/>
@@ -2981,27 +3042,27 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>ER-06.06</t>
+          <t>ER-05.02</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>ER-06 Heat recovery steam generator</t>
+          <t>ER-05 Gas turbine</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Stack</t>
+          <t>Inlet air system</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Steel stack 60 m high (subject to the EIA dispersion study), with CEMS platform, sampling ports per EN 15259 and aviation lighting.</t>
+          <t>Three-stage static air filtration (coastal environment, final stage EPA E12 per EN 1822), anti-icing, evaporative cooler provision, silencer.</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -3012,14 +3073,10 @@
       <c r="G53" s="5" t="n"/>
       <c r="H53" s="4" t="n"/>
       <c r="I53" s="4" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>design_parameter/DP-CASE-0043</t>
-        </is>
-      </c>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="J53" s="5" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3031,32 +3088,32 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>ER-06.07</t>
+          <t>ER-05.03</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>ER-06 Heat recovery steam generator</t>
+          <t>ER-05 Gas turbine</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Drains and blowdown</t>
+          <t>Combustion dynamics monitoring</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Continuous and intermittent blowdown, HRSG drains recovery to the condenser where water quality permits.</t>
+          <t>On-line combustion dynamics monitoring with automatic tuning shall be provided.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>i_and_c</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>demonstration</t>
         </is>
       </c>
       <c r="G54" s="5" t="n"/>
@@ -3077,27 +3134,27 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>ER-06.08</t>
+          <t>ER-05.04</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>ER-06 Heat recovery steam generator</t>
+          <t>ER-05 Gas turbine</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Preservation</t>
+          <t>Enclosure and ventilation</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Dry and wet lay-up systems (nitrogen capping and dehumidified air) for long shutdowns.</t>
+          <t>Acoustic enclosure with ventilation, gas detection and fire suppression suitable for the hazardous area classification.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -3123,22 +3180,22 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>ER-07.01</t>
+          <t>ER-05.05</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>ER-07 Steam turbine and condenser</t>
+          <t>ER-05 Gas turbine</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Steam turbine</t>
+          <t>Compressor washing</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Reheat condensing steam turbine with HP, IP and LP sections, axial or side exhaust, 50 Hz, with HP/IP/LP bypass systems of 100 % capacity.</t>
+          <t>On-line and off-line compressor washing systems with detergent skid.</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -3148,7 +3205,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>inspection</t>
         </is>
       </c>
       <c r="G56" s="5" t="n"/>
@@ -3169,27 +3226,27 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>ER-07.02</t>
+          <t>ER-05.06</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>ER-07 Steam turbine and condenser</t>
+          <t>ER-05 Gas turbine</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Main steam conditions</t>
+          <t>Condition monitoring and remote diagnostics</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>HP live steam about 170 bar(a)/600 degC and hot reheat about 600 degC at base load, as optimised by the OEM.</t>
+          <t>Vibration, performance and combustion monitoring with secure remote diagnostic access for the OEM (IEC 62443 compliant).</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>i_and_c</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3215,22 +3272,22 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>ER-07.03</t>
+          <t>ER-05.07</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>ER-07 Steam turbine and condenser</t>
+          <t>ER-05 Gas turbine</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Condenser</t>
+          <t>Maintenance intervals</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Surface condenser with titanium tubes (or super-duplex), divided water boxes for on-load cleaning, ball-type tube cleaning system.</t>
+          <t>Hot gas path inspection interval shall be not less than 25,000 EOH and major inspection not less than 50,000 EOH at the operating regime of ER-01.03.</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -3240,7 +3297,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>inspection</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G58" s="5" t="n"/>
@@ -3261,57 +3318,41 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>ER-07.04</t>
+          <t>ER-06.01</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>ER-07 Steam turbine and condenser</t>
+          <t>ER-06 Heat recovery steam generator</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Cooling water temperature rise</t>
+          <t>HRSG type</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Temperature rise across the condenser shall not exceed 7 K at base load.</t>
+          <t>Horizontal-gas-flow, triple-pressure, reheat, natural-circulation HRSG, designed for fast cycling (Benson or equivalent HP section acceptable).</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>&lt;= 7 K</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>PG-13</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 7 K</t>
-        </is>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>design_parameter/DP-CASE-0015</t>
-        </is>
-      </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="inlineStr"/>
+      <c r="J59" s="5" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3323,22 +3364,22 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>ER-07.05</t>
+          <t>ER-06.02</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>ER-07 Steam turbine and condenser</t>
+          <t>ER-06 Heat recovery steam generator</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Vacuum system</t>
+          <t>Design code</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>2x100 % liquid-ring vacuum pumps (holding) plus hogging capability for fast start-up.</t>
+          <t>Pressure parts per ASME Section I or EN 12952, PED 2014/68/EU conformity assessment by a notified body.</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -3351,7 +3392,11 @@
           <t>inspection</t>
         </is>
       </c>
-      <c r="G60" s="5" t="n"/>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>PED certificates delivered</t>
+        </is>
+      </c>
       <c r="H60" s="4" t="n"/>
       <c r="I60" s="4" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr"/>
@@ -3369,37 +3414,45 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>ER-07.06</t>
+          <t>ER-06.03</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>ER-07 Steam turbine and condenser</t>
+          <t>ER-06 Heat recovery steam generator</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Lube and control oil</t>
+          <t>SCR and CO catalyst</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Fire-resistant control fluid, lube oil system with 2x100 % AC pumps, DC emergency pump and oil purification.</t>
+          <t>In-duct SCR with aqueous ammonia (&lt; 25 %) injection and an oxidation catalyst sized for the emission guarantees at end of catalyst life (24,000 h).</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>inspection</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G61" s="5" t="n"/>
-      <c r="H61" s="4" t="n"/>
-      <c r="I61" s="4" t="inlineStr"/>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>PG-04</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 30 mg/Nm3</t>
+        </is>
+      </c>
       <c r="J61" s="5" t="inlineStr"/>
       <c r="K61" s="6" t="inlineStr">
         <is>
@@ -3415,27 +3468,27 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>ER-08.01</t>
+          <t>ER-06.04</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>ER-08 Cooling water system</t>
+          <t>ER-06 Heat recovery steam generator</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Once-through seawater cooling</t>
+          <t>Ammonia system</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Offshore submerged intake head with velocity cap (intake velocity &lt;= 0.15 m/s), intake pipelines, pump house, and outfall with diffuser.</t>
+          <t>Aqueous ammonia storage (2x7 days at base load), unloading, vaporisation and dosing with leak detection and bunding.</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>civil</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -3461,22 +3514,22 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>ER-08.02</t>
+          <t>ER-06.05</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>ER-08 Cooling water system</t>
+          <t>ER-06 Heat recovery steam generator</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Screening</t>
+          <t>Cycling capability</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Bar screens, 2x100 % travelling band screens with fish return system, trash rakes.</t>
+          <t>The HRSG shall withstand the start regime of ER-01.03 without drum or header fatigue beyond design life (fatigue analysis per EN 12952-3).</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -3486,7 +3539,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>inspection</t>
+          <t>analysis</t>
         </is>
       </c>
       <c r="G63" s="5" t="n"/>
@@ -3507,41 +3560,45 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>ER-08.03</t>
+          <t>ER-06.06</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>ER-08 Cooling water system</t>
+          <t>ER-06 Heat recovery steam generator</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Circulating water pumps</t>
+          <t>Stack</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>2x50 % vertical CW pumps with a common spare pump assembly stored on Site; materials suitable for seawater (duplex).</t>
+          <t>Steel stack 65 m high (EIA decision ALP-OWN-ENV-001), with CEMS platform, sampling ports per EN 15259 and aviation lighting.</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>inspection</t>
         </is>
       </c>
       <c r="G64" s="5" t="n"/>
       <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="inlineStr"/>
-      <c r="J64" s="5" t="inlineStr"/>
-      <c r="K64" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-CASE-0043</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -3553,22 +3610,22 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>ER-08.04</t>
+          <t>ER-06.07</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>ER-08 Cooling water system</t>
+          <t>ER-06 Heat recovery steam generator</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Biofouling control</t>
+          <t>Drains and blowdown</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Electro-chlorination with intermittent/shock dosing; residual chlorine at outfall &lt;= 0.1 mg/l.</t>
+          <t>Continuous and intermittent blowdown, HRSG drains recovery to the condenser where water quality permits.</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -3578,24 +3635,16 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>&lt;= 0.1 mg/l residual chlorine</t>
-        </is>
-      </c>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="n"/>
       <c r="H65" s="4" t="n"/>
       <c r="I65" s="4" t="inlineStr"/>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t>design_parameter/DP-CASE-0017</t>
-        </is>
-      </c>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="J65" s="5" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -3607,22 +3656,22 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>ER-08.05</t>
+          <t>ER-06.08</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>ER-08 Cooling water system</t>
+          <t>ER-06 Heat recovery steam generator</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Thermal plume</t>
+          <t>Preservation</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>The outfall shall limit the temperature excess to &lt;= 3 K at the edge of the 100 m mixing zone.</t>
+          <t>Dry and wet lay-up systems (nitrogen capping and dehumidified air) for long shutdowns.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -3632,32 +3681,16 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>&lt;= 3 K</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>PG-14</t>
-        </is>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 3 K</t>
-        </is>
-      </c>
-      <c r="J66" s="5" t="inlineStr">
-        <is>
-          <t>design_parameter/DP-CASE-0016</t>
-        </is>
-      </c>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>inspection</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="inlineStr"/>
+      <c r="J66" s="5" t="inlineStr"/>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -3669,22 +3702,22 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>ER-08.06</t>
+          <t>ER-07.01</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>ER-08 Cooling water system</t>
+          <t>ER-07 Steam turbine and condenser</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Closed cooling water</t>
+          <t>Steam turbine</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Closed cooling water circuit for auxiliaries with 2x100 % plate heat exchangers (titanium plates) and 2x100 % pumps.</t>
+          <t>Reheat condensing steam turbine with HP, IP and LP sections, axial or side exhaust, 50 Hz, with HP/IP/LP bypass systems of 100 % capacity.</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -3694,7 +3727,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>inspection</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G67" s="5" t="n"/>
@@ -3715,22 +3748,22 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>ER-09.01</t>
+          <t>ER-07.02</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>ER-09 Water treatment and effluents</t>
+          <t>ER-07 Steam turbine and condenser</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Raw water</t>
+          <t>Main steam conditions</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Seawater reverse osmosis (2x100 %) producing service and demineralisation feed water; no groundwater abstraction.</t>
+          <t>HP live steam about 170 bar(a)/600 degC and hot reheat about 600 degC at base load, as optimised by the OEM.</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -3740,7 +3773,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G68" s="5" t="n"/>
@@ -3761,32 +3794,32 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>ER-09.02</t>
+          <t>ER-07.03</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>ER-09 Water treatment and effluents</t>
+          <t>ER-07 Steam turbine and condenser</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Demineralised water</t>
+          <t>Condenser</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Two-pass RO plus electrodeionisation, 2x100 %, conductivity &lt; 0.1 uS/cm, silica &lt; 10 ug/l; storage for 3 days of cycle make-up.</t>
+          <t>Single-shell or two-shell surface condenser with titanium tubes (Grade 2, welded) and titanium-clad tube sheets, divided water boxes for on-load cleaning of one half, and an automatic ball-type tube cleaning system.</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>inspection</t>
         </is>
       </c>
       <c r="G69" s="5" t="n"/>
@@ -3807,22 +3840,22 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>ER-09.03</t>
+          <t>ER-07.04</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>ER-09 Water treatment and effluents</t>
+          <t>ER-07 Steam turbine and condenser</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Cycle chemistry</t>
+          <t>Cooling water temperature rise</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Water/steam chemistry per VGB-S-010 (all-volatile treatment, oxygenated where applicable) with on-line analysers and sampling panel.</t>
+          <t>Temperature rise across the condenser shall not exceed 7 K at base load.</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -3832,16 +3865,32 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="4" t="n"/>
-      <c r="I70" s="4" t="inlineStr"/>
-      <c r="J70" s="5" t="inlineStr"/>
-      <c r="K70" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>&lt;= 7 K</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>PG-13</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 7 K</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-CASE-0015</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -3853,27 +3902,27 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>ER-09.04</t>
+          <t>ER-07.05</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>ER-09 Water treatment and effluents</t>
+          <t>ER-07 Steam turbine and condenser</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Condensate polishing</t>
+          <t>Vacuum system</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Full-flow condensate polishing for start-up and seawater ingress events.</t>
+          <t>2x100 % liquid-ring vacuum pumps (holding) plus hogging capability for fast start-up.</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -3899,39 +3948,35 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>ER-09.05</t>
+          <t>ER-07.06</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>ER-09 Water treatment and effluents</t>
+          <t>ER-07 Steam turbine and condenser</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Waste water</t>
+          <t>Lube and control oil</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Neutralisation, oil separation and treatment so that effluents meet the Turkish Water Pollution Control Regulation discharge limits before the outfall.</t>
+          <t>Fire-resistant control fluid, lube oil system with 2x100 % AC pumps, DC emergency pump and oil purification.</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>hse</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>Effluent within permit limits</t>
-        </is>
-      </c>
+          <t>inspection</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="n"/>
       <c r="H72" s="4" t="n"/>
       <c r="I72" s="4" t="inlineStr"/>
       <c r="J72" s="5" t="inlineStr"/>
@@ -3949,41 +3994,50 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>ER-09.06</t>
+          <t>ER-07.07</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>ER-09 Water treatment and effluents</t>
+          <t>ER-07 Steam turbine and condenser</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Stormwater</t>
+          <t>Condenser design standard</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Separate clean and potentially oily stormwater drainage with oil interceptors.</t>
+          <t>Thermal design per HEI Standards for Steam Surface Condensers (11th edition or later): cleanliness factor 0.85, 5 % tube plugging margin, tube velocity 1.8 m/s to 2.2 m/s, titanium wall per HEI. Hotwell storage at least 3 minutes of maximum condensate flow; dissolved oxygen at hotwell outlet &lt;= 20 ug/l in normal operation.</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>civil</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>inspection</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="n"/>
+          <t>analysis</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Condenser datasheet and HEI calculation approved</t>
+        </is>
+      </c>
       <c r="H73" s="4" t="n"/>
       <c r="I73" s="4" t="inlineStr"/>
-      <c r="J73" s="5" t="inlineStr"/>
-      <c r="K73" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-OWNR-0022
+design_parameter/DP-OWNR-0023</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -3995,27 +4049,27 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>ER-10.01</t>
+          <t>ER-07.08</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>ER-10 Balance of plant mechanical systems</t>
+          <t>ER-07 Steam turbine and condenser</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Feed water pumps</t>
+          <t>Condenser pressure</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>2x100 % variable-speed (VFD or hydraulic coupling) HP/IP boiler feed pumps.</t>
+          <t>Design condenser pressure at base load and Site Reference Conditions (seawater 16.0 degC, 7 K rise): not more than 36 mbar(a). At the maximum seawater temperature (27.0 degC) the plant shall run at base load without load limitation; the back-pressure shall stay within the steam turbine continuous limits with margin to the alarm value.</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -4023,13 +4077,21 @@
           <t>test</t>
         </is>
       </c>
-      <c r="G74" s="5" t="n"/>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Design requirement (condenser datasheet and HEI calculation); contractual compliance through PG-02; ASME PTC 12.2 test for information</t>
+        </is>
+      </c>
       <c r="H74" s="4" t="n"/>
       <c r="I74" s="4" t="inlineStr"/>
-      <c r="J74" s="5" t="inlineStr"/>
-      <c r="K74" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-OWNR-0021</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -4041,22 +4103,22 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>ER-10.02</t>
+          <t>ER-07.09</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>ER-10 Balance of plant mechanical systems</t>
+          <t>ER-07 Steam turbine and condenser</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Condensate pumps</t>
+          <t>Steam bypass to the condenser</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>2x100 % condensate extraction pumps.</t>
+          <t>The condenser shall accept 100 % HP/IP/LP bypass steam at the maximum steam flow (including cold-ambient and LDO cases) with desuperheating, dump-device design per HEI, and protection against shell overheating and tube erosion.</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -4066,7 +4128,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>analysis</t>
         </is>
       </c>
       <c r="G75" s="5" t="n"/>
@@ -4087,27 +4149,27 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>ER-10.03</t>
+          <t>ER-07.10</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>ER-10 Balance of plant mechanical systems</t>
+          <t>ER-07 Steam turbine and condenser</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Compressed air</t>
+          <t>Condenser leak detection and protection</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>2x100 % oil-free compressors, 2x100 % dryers, instrument air dew point -40 degC, receiver for 15 min of instrument air after loss of compressors.</t>
+          <t>Cation conductivity measurement per water box half and in the hotwell with automatic alarm and isolation logic for seawater ingress; water boxes rubber-lined with impressed-current cathodic protection; air in-leakage allowance and vacuum pump sizing per HEI.</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>i_and_c</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -4133,32 +4195,32 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>ER-10.04</t>
+          <t>ER-07.11</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>ER-10 Balance of plant mechanical systems</t>
+          <t>ER-07 Steam turbine and condenser</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Auxiliary boiler</t>
+          <t>Circulating water flow</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Gas-fired auxiliary boiler for start-up and sealing steam, sized for a cold start without external steam.</t>
+          <t>Circulating water flow for the design heat duty at 7 K rise (indicatively 43,000 m3/h to 47,000 m3/h, to be confirmed by the Contractor); CW system hydraulic transient analysis including pump trip and valve closure.</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>analysis</t>
         </is>
       </c>
       <c r="G77" s="5" t="n"/>
@@ -4179,39 +4241,35 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>ER-10.05</t>
+          <t>ER-08.01</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>ER-10 Balance of plant mechanical systems</t>
+          <t>ER-08 Cooling water system</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Fire protection</t>
+          <t>Once-through seawater cooling</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Fire detection and protection per NFPA 850 and Turkish Fire Regulation: ring main, 2x100 % electric plus diesel fire pumps, water mist/CO2 for GT enclosure, deluge for transformers, gas detection, fire alarm system.</t>
+          <t>Offshore intake head above the pycnocline at about -12 m (at least 3 m above seabed, about 650 m offshore) with velocity cap and intake velocity &lt;= 0.15 m/s; intake pipelines; pump house; outfall diffuser at least 250 m from the intake discharging into the upper layer (ALP-OWN-MAR-001 section 6).</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>hse</t>
+          <t>civil</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>Insurer and fire brigade acceptance</t>
-        </is>
-      </c>
+          <t>inspection</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="n"/>
       <c r="H78" s="4" t="n"/>
       <c r="I78" s="4" t="inlineStr"/>
       <c r="J78" s="5" t="inlineStr"/>
@@ -4229,32 +4287,32 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>ER-10.06</t>
+          <t>ER-08.02</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>ER-10 Balance of plant mechanical systems</t>
+          <t>ER-08 Cooling water system</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Screening</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>HVAC for all buildings; electrical and control rooms with N+1 cooling and positive pressure with filtered (coastal) air.</t>
+          <t>Bar screens, 2x100 % travelling band screens with fish return system, trash rakes.</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>hvac</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>inspection</t>
         </is>
       </c>
       <c r="G79" s="5" t="n"/>
@@ -4275,22 +4333,22 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>ER-10.07</t>
+          <t>ER-08.03</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>ER-10 Balance of plant mechanical systems</t>
+          <t>ER-08 Cooling water system</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Cranes</t>
+          <t>Circulating water pumps</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Turbine hall EOT crane sized for the heaviest maintenance lift (excluding generator stator), and maintenance hoists for pumps and valves.</t>
+          <t>2x50 % vertical CW pumps with a common spare pump assembly stored on Site; materials suitable for seawater (duplex).</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -4321,41 +4379,49 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>ER-10.08</t>
+          <t>ER-08.04</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>ER-10 Balance of plant mechanical systems</t>
+          <t>ER-08 Cooling water system</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Nitrogen and hydrogen</t>
+          <t>Biofouling control</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Nitrogen supply for purging and preservation; hydrogen supply for generator cooling if hydrogen-cooled generators are offered.</t>
+          <t>Electro-chlorination with intermittent/shock dosing; residual chlorine at outfall &lt;= 0.1 mg/l.</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>inspection</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="n"/>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>&lt;= 0.1 mg/l residual chlorine</t>
+        </is>
+      </c>
       <c r="H81" s="4" t="n"/>
       <c r="I81" s="4" t="inlineStr"/>
-      <c r="J81" s="5" t="inlineStr"/>
-      <c r="K81" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-CASE-0017</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -4367,27 +4433,27 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>ER-11.01</t>
+          <t>ER-08.05</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>ER-11 Electrical systems</t>
+          <t>ER-08 Cooling water system</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Grid connection</t>
+          <t>Thermal plume</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Connection to the 380 kV transmission system via a GIS switchyard with double busbar and bus coupler, two line bays and two generator transformer bays, designed for 50 kA short-circuit current.</t>
+          <t>The outfall shall limit the temperature excess to &lt;= 3 K at the edge of the 100 m mixing zone.</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>electrical</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -4395,13 +4461,24 @@
           <t>test</t>
         </is>
       </c>
-      <c r="G82" s="5" t="n"/>
-      <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="inlineStr"/>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>&lt;= 3 K</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>PG-14</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 3 K</t>
+        </is>
+      </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0024
-design_parameter/DP-CASE-0025</t>
+          <t>design_parameter/DP-CASE-0016</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
@@ -4418,32 +4495,32 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>ER-11.02</t>
+          <t>ER-08.06</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>ER-11 Electrical systems</t>
+          <t>ER-08 Cooling water system</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Generators</t>
+          <t>Closed cooling water</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Air- or hydrogen-cooled synchronous generators per IEC 60034, 50 Hz, static excitation with PSS, generator circuit breakers per IEC/IEEE 62271-37-013.</t>
+          <t>Closed cooling water circuit for auxiliaries with 2x100 % plate heat exchangers (titanium plates) and 2x100 % pumps.</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>electrical</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>inspection</t>
         </is>
       </c>
       <c r="G83" s="5" t="n"/>
@@ -4464,41 +4541,45 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>ER-11.03</t>
+          <t>ER-08.07</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>ER-11 Electrical systems</t>
+          <t>ER-08 Cooling water system</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Generator step-up transformers</t>
+          <t>Jellyfish and mucilage</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>One GSU per generator, ONAN/ONAF, rated for the maximum generator output at -8 degC, on-load tap changer, per IEC 60076; fire walls between transformers.</t>
+          <t>Screens, trash rakes and screen wash shall remain operable at jellyfish loads up to 20 kg/m3 and during mucilage events; the CW system shall allow operation at reduced flow with automatic load reduction rather than trip.</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>electrical</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>demonstration</t>
         </is>
       </c>
       <c r="G84" s="5" t="n"/>
       <c r="H84" s="4" t="n"/>
       <c r="I84" s="4" t="inlineStr"/>
-      <c r="J84" s="5" t="inlineStr"/>
-      <c r="K84" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-OWNR-0019</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -4510,27 +4591,27 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>ER-11.04</t>
+          <t>ER-09.01</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>ER-11 Electrical systems</t>
+          <t>ER-09 Water treatment and effluents</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Auxiliary power supply</t>
+          <t>Raw water</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Two unit auxiliary transformers, 10.5 kV MV switchboards (2 sections with bus tie), 0.4 kV PMCC with automatic transfer. Start-up power from the grid via back-feed through the GSU.</t>
+          <t>Seawater reverse osmosis (2 x 100 %) with ultrafiltration pre-treatment (raw SDI15 &gt; 5), designed for the upper-layer quality of ALP-OWN-MAR-001 including boron removal for demineralisation feed.</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>electrical</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -4556,27 +4637,27 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>ER-11.05</t>
+          <t>ER-09.02</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>ER-11 Electrical systems</t>
+          <t>ER-09 Water treatment and effluents</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Emergency power</t>
+          <t>Demineralised water</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Emergency diesel generator for safe shutdown loads (turning gear, lube oil, emergency lighting); the diesel fire pump has its own independent drive; UPS (2x100 %) for DCS and critical loads with 60 min autonomy; 220 V DC and 24 V DC systems.</t>
+          <t>Two-pass RO plus electrodeionisation, 2 x 100 %, conductivity &lt; 0.1 uS/cm, silica &lt; 10 ug/l, with capacity for continuous water injection at 50 % load on LDO; demineralised water storage 2 x 1,250 m3 (3 days of cycle make-up plus about 24 h of water injection); connection point for mobile demin trailers.</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>electrical</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -4602,32 +4683,32 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>ER-11.06</t>
+          <t>ER-09.03</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>ER-11 Electrical systems</t>
+          <t>ER-09 Water treatment and effluents</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Cycle chemistry</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Duplicated main protection (Main 1/Main 2 from different manufacturers where required by the TSO) for generators, transformers, busbars and lines.</t>
+          <t>Water/steam chemistry per VGB-S-010 (all-volatile treatment, oxygenated where applicable) with on-line analysers and sampling panel.</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>electrical</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G87" s="5" t="n"/>
@@ -4648,32 +4729,32 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>ER-11.07</t>
+          <t>ER-09.04</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>ER-11 Electrical systems</t>
+          <t>ER-09 Water treatment and effluents</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Earthing and lightning</t>
+          <t>Condensate polishing</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Earthing grid per IEEE 80 with safe touch and step voltages; lightning protection per IEC 62305.</t>
+          <t>Full-flow condensate polishing for start-up and seawater ingress events.</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>electrical</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>inspection</t>
         </is>
       </c>
       <c r="G88" s="5" t="n"/>
@@ -4694,35 +4775,39 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>ER-11.08</t>
+          <t>ER-09.05</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>ER-11 Electrical systems</t>
+          <t>ER-09 Water treatment and effluents</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Cables</t>
+          <t>Waste water</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Cables per IEC standards, halogen-free flame-retardant inside buildings, fire-rated cables for safety circuits.</t>
+          <t>Neutralisation, oil separation and treatment of process wastewater, and a packaged biological treatment plant with UV disinfection for sanitary wastewater (no municipal sewer), so that all effluents meet the Turkish Water Pollution Control Regulation sea-discharge limits before the outfall.</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>electrical</t>
+          <t>hse</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>inspection</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="n"/>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>Effluent within permit limits</t>
+        </is>
+      </c>
       <c r="H89" s="4" t="n"/>
       <c r="I89" s="4" t="inlineStr"/>
       <c r="J89" s="5" t="inlineStr"/>
@@ -4740,32 +4825,32 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>ER-11.09</t>
+          <t>ER-09.06</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>ER-11 Electrical systems</t>
+          <t>ER-09 Water treatment and effluents</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Metering and TSO interface</t>
+          <t>Stormwater</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Revenue metering per TSO/market operator rules (main and check meters, class 0.2S), RTU and telecommunication to the national dispatch centre.</t>
+          <t>Separate clean and potentially oily stormwater drainage with oil interceptors.</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>electrical</t>
+          <t>civil</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>inspection</t>
         </is>
       </c>
       <c r="G90" s="5" t="n"/>
@@ -4786,27 +4871,27 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>ER-12.01</t>
+          <t>ER-10.01</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>ER-12 Instrumentation, control and cybersecurity</t>
+          <t>ER-10 Balance of plant mechanical systems</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Distributed control system</t>
+          <t>Feed water pumps</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Single integrated plant DCS for GT, ST, HRSG and BOP with redundant controllers, networks and power supplies; operation of the whole plant from the central control room by two operators.</t>
+          <t>2x100 % variable-speed (VFD or hydraulic coupling) HP/IP boiler feed pumps.</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>i_and_c</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -4832,32 +4917,32 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>ER-12.02</t>
+          <t>ER-10.02</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>ER-12 Instrumentation, control and cybersecurity</t>
+          <t>ER-10 Balance of plant mechanical systems</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Automation level</t>
+          <t>Condensate pumps</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Automatic start-up and shutdown sequences (one-button start to base load) and automatic load control from the dispatch set-point.</t>
+          <t>2x100 % condensate extraction pumps.</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>i_and_c</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>demonstration</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G92" s="5" t="n"/>
@@ -4878,39 +4963,35 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>ER-12.03</t>
+          <t>ER-10.03</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>ER-12 Instrumentation, control and cybersecurity</t>
+          <t>ER-10 Balance of plant mechanical systems</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Safety instrumented systems</t>
+          <t>Compressed air</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>SIS per IEC 61511 with SIL verification, including burner management and HRSG protection.</t>
+          <t>2x100 % oil-free compressors, 2x100 % dryers, instrument air dew point -40 degC, receiver for 15 min of instrument air after loss of compressors.</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>i_and_c</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>analysis</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>SIL verification reports approved</t>
-        </is>
-      </c>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="n"/>
       <c r="H93" s="4" t="n"/>
       <c r="I93" s="4" t="inlineStr"/>
       <c r="J93" s="5" t="inlineStr"/>
@@ -4928,27 +5009,27 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>ER-12.04</t>
+          <t>ER-10.04</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>ER-12 Instrumentation, control and cybersecurity</t>
+          <t>ER-10 Balance of plant mechanical systems</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>CEMS</t>
+          <t>Auxiliary boiler</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Certified continuous emission monitoring (NOx, CO, O2, NH3, flow, moisture) per EN 14181 with data transmission to the environmental authority.</t>
+          <t>Gas-fired auxiliary boiler for start-up and sealing steam, sized for a cold start without external steam.</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>i_and_c</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -4974,27 +5055,27 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>ER-12.05</t>
+          <t>ER-10.05</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>ER-12 Instrumentation, control and cybersecurity</t>
+          <t>ER-10 Balance of plant mechanical systems</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Historian and performance monitoring</t>
+          <t>Fire protection</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Plant historian (5 years on-line storage) and on-line performance calculation per ASME PTC 46 principles.</t>
+          <t>Fire detection and protection per NFPA 850 and Turkish Fire Regulation: ring main, 2x100 % electric plus diesel fire pumps, water mist/CO2 for GT enclosure, deluge for transformers, gas detection, fire alarm system.</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>i_and_c</t>
+          <t>hse</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -5002,7 +5083,11 @@
           <t>test</t>
         </is>
       </c>
-      <c r="G95" s="5" t="n"/>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>Insurer and fire brigade acceptance</t>
+        </is>
+      </c>
       <c r="H95" s="4" t="n"/>
       <c r="I95" s="4" t="inlineStr"/>
       <c r="J95" s="5" t="inlineStr"/>
@@ -5020,32 +5105,32 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>ER-12.06</t>
+          <t>ER-10.06</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>ER-12 Instrumentation, control and cybersecurity</t>
+          <t>ER-10 Balance of plant mechanical systems</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Operator training simulator</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>High-fidelity operator training simulator of the whole plant, delivered 6 months before first fire.</t>
+          <t>HVAC for all buildings; electrical and control rooms with N+1 cooling and positive pressure with filtered (coastal) air.</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>i_and_c</t>
+          <t>hvac</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>demonstration</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G96" s="5" t="n"/>
@@ -5066,27 +5151,27 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>ER-12.07</t>
+          <t>ER-10.07</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>ER-12 Instrumentation, control and cybersecurity</t>
+          <t>ER-10 Balance of plant mechanical systems</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Cranes</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>OT cybersecurity per IEC 62443 (target security level SL2), zones and conduits, DMZ, patch and backup management, security acceptance test.</t>
+          <t>Turbine hall EOT crane sized for the heaviest maintenance lift (excluding generator stator), and maintenance hoists for pumps and valves.</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>i_and_c</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -5094,11 +5179,7 @@
           <t>test</t>
         </is>
       </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>Security acceptance test passed</t>
-        </is>
-      </c>
+      <c r="G97" s="5" t="n"/>
       <c r="H97" s="4" t="n"/>
       <c r="I97" s="4" t="inlineStr"/>
       <c r="J97" s="5" t="inlineStr"/>
@@ -5116,32 +5197,32 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>ER-12.08</t>
+          <t>ER-10.08</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>ER-12 Instrumentation, control and cybersecurity</t>
+          <t>ER-10 Balance of plant mechanical systems</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Time synchronisation</t>
+          <t>Nitrogen and hydrogen</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>GPS time synchronisation of DCS, protection relays and recorders (1 ms sequence of events).</t>
+          <t>Nitrogen supply for purging and preservation; hydrogen supply for generator cooling if hydrogen-cooled generators are offered.</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>i_and_c</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>inspection</t>
         </is>
       </c>
       <c r="G98" s="5" t="n"/>
@@ -5162,41 +5243,46 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>ER-13.01</t>
+          <t>ER-11.01</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>ER-13 Civil, structural and architectural works</t>
+          <t>ER-11 Electrical systems</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Foundations</t>
+          <t>Grid connection</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Turbine and generator foundations designed for dynamic loads with separated foundations from buildings; settlement limits per OEM.</t>
+          <t>Connection to the 380 kV transmission system via an indoor GIS switchyard in a ventilated building (salt atmosphere), double busbar and bus coupler, two line bays and two generator transformer bays, designed for 50 kA short-circuit current; outdoor bushings with creepage per ER-02.10.</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>civil</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>analysis</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G99" s="5" t="n"/>
       <c r="H99" s="4" t="n"/>
       <c r="I99" s="4" t="inlineStr"/>
-      <c r="J99" s="5" t="inlineStr"/>
-      <c r="K99" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-CASE-0024
+design_parameter/DP-CASE-0025</t>
+        </is>
+      </c>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -5208,32 +5294,32 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>ER-13.02</t>
+          <t>ER-11.02</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>ER-13 Civil, structural and architectural works</t>
+          <t>ER-11 Electrical systems</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Buildings</t>
+          <t>Generators</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Turbine hall, control and electrical building, administration building, workshop/warehouse, water treatment building, gatehouse, fire station.</t>
+          <t>Air- or hydrogen-cooled synchronous generators per IEC 60034, 50 Hz, static excitation with PSS, generator circuit breakers per IEC/IEEE 62271-37-013.</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>civil</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>inspection</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G100" s="5" t="n"/>
@@ -5254,32 +5340,32 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>ER-13.03</t>
+          <t>ER-11.03</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>ER-13 Civil, structural and architectural works</t>
+          <t>ER-11 Electrical systems</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Structural steel</t>
+          <t>Generator step-up transformers</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Structural steel per EN 1993 with seismic detailing, hot-dip galvanised outdoors (EN ISO 1461).</t>
+          <t>One GSU per generator, ONAN/ONAF, rated for the maximum generator output at -8 degC, on-load tap changer, per IEC 60076; fire walls between transformers.</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>inspection</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G101" s="5" t="n"/>
@@ -5300,32 +5386,32 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>ER-13.04</t>
+          <t>ER-11.04</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>ER-13 Civil, structural and architectural works</t>
+          <t>ER-11 Electrical systems</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>Auxiliary power supply</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Concrete per EN 1992 / TS 500 with exposure class XS for marine-exposed elements; minimum 50-year durability.</t>
+          <t>Two unit auxiliary transformers, 10.5 kV MV switchboards (2 sections with bus tie), 0.4 kV PMCC with automatic transfer. Start-up power from the grid via back-feed through the GSU.</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>civil</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>inspection</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G102" s="5" t="n"/>
@@ -5346,32 +5432,32 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>ER-13.05</t>
+          <t>ER-11.05</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>ER-13 Civil, structural and architectural works</t>
+          <t>ER-11 Electrical systems</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Roads and drainage</t>
+          <t>Emergency power</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Internal asphalt roads for 40 t axle loads to the heaviest delivery route, surface water drainage for ER-02.05 rainfall.</t>
+          <t>Emergency diesel generator for safe shutdown loads (turning gear, lube oil, emergency lighting); the diesel fire pump has its own independent drive; UPS (2x100 %) for DCS and critical loads with 60 min autonomy; 220 V DC and 24 V DC systems.</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>civil</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>inspection</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G103" s="5" t="n"/>
@@ -5392,32 +5478,32 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>ER-13.06</t>
+          <t>ER-11.06</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>ER-13 Civil, structural and architectural works</t>
+          <t>ER-11 Electrical systems</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Marine works</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Intake and outfall pipelines (HDPE or GRP) with ballast and scour protection, designed for 50-year wave conditions.</t>
+          <t>Duplicated main protection (Main 1/Main 2 from different manufacturers where required by the TSO) for generators, transformers, busbars and lines.</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>civil</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>analysis</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G104" s="5" t="n"/>
@@ -5438,39 +5524,35 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>ER-14.01</t>
+          <t>ER-11.07</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>ER-14 Environment, health and safety</t>
+          <t>ER-11 Electrical systems</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>EIA compliance</t>
+          <t>Earthing and lightning</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>The Works shall comply with the conditions of the positive EIA decision and the Environmental Law (No. 2872) and its regulations.</t>
+          <t>Earthing grid per IEEE 80 with safe touch and step voltages; lightning protection per IEC 62305.</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>hse</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
-        <is>
-          <t>No outstanding EIA non-conformities at Taking-Over</t>
-        </is>
-      </c>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="n"/>
       <c r="H105" s="4" t="n"/>
       <c r="I105" s="4" t="inlineStr"/>
       <c r="J105" s="5" t="inlineStr"/>
@@ -5488,59 +5570,41 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>ER-14.02</t>
+          <t>ER-11.08</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>ER-14 Environment, health and safety</t>
+          <t>ER-11 Electrical systems</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Air emissions</t>
+          <t>Cables</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>NOx &lt;= 30 mg/Nm3 and CO &lt;= 30 mg/Nm3 (dry, 15 % O2) between 50 % and 100 % GT load; NH3 slip &lt;= 5 mg/Nm3.</t>
+          <t>Cables per IEC standards, halogen-free flame-retardant inside buildings, fire-rated cables for safety circuits.</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>hse</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>Within guaranteed limits</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>PG-04</t>
-        </is>
-      </c>
-      <c r="I106" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 30 mg/Nm3</t>
-        </is>
-      </c>
-      <c r="J106" s="5" t="inlineStr">
-        <is>
-          <t>design_parameter/DP-CASE-0040
-design_parameter/DP-CASE-0041
-design_parameter/DP-CASE-0042</t>
-        </is>
-      </c>
-      <c r="K106" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>inspection</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="n"/>
+      <c r="H106" s="4" t="n"/>
+      <c r="I106" s="4" t="inlineStr"/>
+      <c r="J106" s="5" t="inlineStr"/>
+      <c r="K106" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
@@ -5552,27 +5616,27 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>ER-14.03</t>
+          <t>ER-11.09</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>ER-14 Environment, health and safety</t>
+          <t>ER-11 Electrical systems</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Near-field noise</t>
+          <t>Metering and TSO interface</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Maximum 85 dB(A) at 1 m from any equipment in normal operation.</t>
+          <t>Revenue metering per TSO/market operator rules (main and check meters, class 0.2S), RTU and telecommunication to the national dispatch centre.</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>hse</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -5580,29 +5644,13 @@
           <t>test</t>
         </is>
       </c>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>&lt;= 85 dB(A)</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="inlineStr">
-        <is>
-          <t>PG-07</t>
-        </is>
-      </c>
-      <c r="I107" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 85 dB(A)</t>
-        </is>
-      </c>
-      <c r="J107" s="5" t="inlineStr">
-        <is>
-          <t>design_parameter/DP-CASE-0044</t>
-        </is>
-      </c>
-      <c r="K107" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="G107" s="5" t="n"/>
+      <c r="H107" s="4" t="n"/>
+      <c r="I107" s="4" t="inlineStr"/>
+      <c r="J107" s="5" t="inlineStr"/>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -5614,27 +5662,27 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>ER-14.04</t>
+          <t>ER-12.01</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>ER-14 Environment, health and safety</t>
+          <t>ER-12 Instrumentation, control and cybersecurity</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Environmental noise</t>
+          <t>Distributed control system</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Maximum 45 dB(A) LAeq night at the nearest sensitive receptor.</t>
+          <t>Single integrated plant DCS for GT, ST, HRSG and BOP with redundant controllers, networks and power supplies; operation of the whole plant from the central control room by two operators.</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>hse</t>
+          <t>i_and_c</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
@@ -5642,29 +5690,13 @@
           <t>test</t>
         </is>
       </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>&lt;= 45 dB(A)</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>PG-08</t>
-        </is>
-      </c>
-      <c r="I108" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 45 dB(A)</t>
-        </is>
-      </c>
-      <c r="J108" s="5" t="inlineStr">
-        <is>
-          <t>design_parameter/DP-CASE-0045</t>
-        </is>
-      </c>
-      <c r="K108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="G108" s="5" t="n"/>
+      <c r="H108" s="4" t="n"/>
+      <c r="I108" s="4" t="inlineStr"/>
+      <c r="J108" s="5" t="inlineStr"/>
+      <c r="K108" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
@@ -5676,32 +5708,32 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>ER-14.05</t>
+          <t>ER-12.02</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>ER-14 Environment, health and safety</t>
+          <t>ER-12 Instrumentation, control and cybersecurity</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Occupational health and safety</t>
+          <t>Automation level</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Construction and design shall comply with the Occupational Health and Safety Law (No. 6331); the Contractor shall implement an ISO 45001-certified HSE management system and a lost-time-injury target of zero.</t>
+          <t>Automatic start-up and shutdown sequences (one-button start to base load) and automatic load control from the dispatch set-point.</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>hse</t>
+          <t>i_and_c</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>demonstration</t>
         </is>
       </c>
       <c r="G109" s="5" t="n"/>
@@ -5722,35 +5754,39 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>ER-14.06</t>
+          <t>ER-12.03</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>ER-14 Environment, health and safety</t>
+          <t>ER-12 Instrumentation, control and cybersecurity</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Hazardous areas</t>
+          <t>Safety instrumented systems</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Hazardous area classification per IEC 60079-10-1; equipment certified accordingly.</t>
+          <t>SIS per IEC 61511 with SIL verification, including burner management and HRSG protection.</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>hse</t>
+          <t>i_and_c</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="G110" s="5" t="n"/>
+          <t>analysis</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>SIL verification reports approved</t>
+        </is>
+      </c>
       <c r="H110" s="4" t="n"/>
       <c r="I110" s="4" t="inlineStr"/>
       <c r="J110" s="5" t="inlineStr"/>
@@ -5768,39 +5804,35 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>ER-14.07</t>
+          <t>ER-12.04</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>ER-14 Environment, health and safety</t>
+          <t>ER-12 Instrumentation, control and cybersecurity</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Process safety studies</t>
+          <t>CEMS</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>HAZID, HAZOP, SIL determination, fire and explosion risk assessment and a Major Accident Prevention assessment where applicable.</t>
+          <t>Certified continuous emission monitoring (NOx, CO, O2, NH3, flow, moisture) per EN 14181 with data transmission to the environmental authority.</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>hse</t>
+          <t>i_and_c</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>All actions closed before first fire</t>
-        </is>
-      </c>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="n"/>
       <c r="H111" s="4" t="n"/>
       <c r="I111" s="4" t="inlineStr"/>
       <c r="J111" s="5" t="inlineStr"/>
@@ -5818,32 +5850,32 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>ER-14.08</t>
+          <t>ER-12.05</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>ER-14 Environment, health and safety</t>
+          <t>ER-12 Instrumentation, control and cybersecurity</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Carbon capture readiness</t>
+          <t>Historian and performance monitoring</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Space reservation and tie-in points for a future post-combustion carbon capture plant at the HRSG outlet.</t>
+          <t>Plant historian (5 years on-line storage) and on-line performance calculation per ASME PTC 46 principles.</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>i_and_c</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G112" s="5" t="n"/>
@@ -5864,32 +5896,32 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>ER-15.01</t>
+          <t>ER-12.06</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>ER-15 Quality, inspection and testing during manufacture</t>
+          <t>ER-12 Instrumentation, control and cybersecurity</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Quality management</t>
+          <t>Operator training simulator</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>ISO 9001 quality management for the Contractor and all major subcontractors; project quality plan within 30 days of NTP.</t>
+          <t>High-fidelity operator training simulator of the whole plant, delivered 6 months before first fire.</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>i_and_c</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>demonstration</t>
         </is>
       </c>
       <c r="G113" s="5" t="n"/>
@@ -5910,35 +5942,39 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>ER-15.02</t>
+          <t>ER-12.07</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>ER-15 Quality, inspection and testing during manufacture</t>
+          <t>ER-12 Instrumentation, control and cybersecurity</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Inspection and test plans</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>ITPs for all major equipment with hold and witness points for the Engineer, 15 days' notice for witnessed tests.</t>
+          <t>OT cybersecurity per IEC 62443 (target security level SL2), zones and conduits, DMZ, patch and backup management, security acceptance test.</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>i_and_c</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="G114" s="5" t="n"/>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>Security acceptance test passed</t>
+        </is>
+      </c>
       <c r="H114" s="4" t="n"/>
       <c r="I114" s="4" t="inlineStr"/>
       <c r="J114" s="5" t="inlineStr"/>
@@ -5956,27 +5992,27 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>ER-15.03</t>
+          <t>ER-12.08</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>ER-15 Quality, inspection and testing during manufacture</t>
+          <t>ER-12 Instrumentation, control and cybersecurity</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Factory acceptance tests</t>
+          <t>Time synchronisation</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>FATs at least for: GT and ST control systems, generators, GSU transformers, GIS, MV switchgear, DCS, CEMS.</t>
+          <t>GPS time synchronisation of DCS, protection relays and recorders (1 ms sequence of events).</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>i_and_c</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
@@ -6002,32 +6038,32 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>ER-15.04</t>
+          <t>ER-13.01</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>ER-15 Quality, inspection and testing during manufacture</t>
+          <t>ER-13 Civil, structural and architectural works</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Material traceability</t>
+          <t>Foundations</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Material certificates per EN 10204 3.1 (3.2 for pressure parts above 50 bar) and positive material identification of alloy piping.</t>
+          <t>Turbine and generator foundations designed for dynamic loads with separated foundations from buildings; settlement limits per OEM.</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>civil</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>inspection</t>
+          <t>analysis</t>
         </is>
       </c>
       <c r="G116" s="5" t="n"/>
@@ -6048,27 +6084,27 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>ER-15.05</t>
+          <t>ER-13.02</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>ER-15 Quality, inspection and testing during manufacture</t>
+          <t>ER-13 Civil, structural and architectural works</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Welding</t>
+          <t>Buildings</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Welding per ASME IX / EN ISO 15614, 100 % NDE of HP/HRH/main steam butt welds.</t>
+          <t>Turbine hall, control and electrical building, administration building, workshop/warehouse, water treatment building, gatehouse, fire station.</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>piping</t>
+          <t>civil</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -6094,32 +6130,32 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>ER-16.01</t>
+          <t>ER-13.03</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>ER-16 Commissioning and Tests on Completion</t>
+          <t>ER-13 Civil, structural and architectural works</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Commissioning plan</t>
+          <t>Structural steel</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>System-based commissioning plan with pre-commissioning, cold and hot commissioning, submitted 9 months before first fire.</t>
+          <t>Structural steel per EN 1993 with seismic detailing, hot-dip galvanised outdoors (EN ISO 1461).</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>commissioning</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>inspection</t>
         </is>
       </c>
       <c r="G118" s="5" t="n"/>
@@ -6140,32 +6176,32 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>ER-16.02</t>
+          <t>ER-13.04</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>ER-16 Commissioning and Tests on Completion</t>
+          <t>ER-13 Civil, structural and architectural works</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Steam blowing and chemical cleaning</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>Chemical cleaning of the HRSG and steam blowing of steam lines to OEM cleanliness criteria.</t>
+          <t>Concrete per EN 1992 / TS 500 with exposure class XS for marine-exposed elements; minimum 50-year durability.</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>commissioning</t>
+          <t>civil</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>inspection</t>
         </is>
       </c>
       <c r="G119" s="5" t="n"/>
@@ -6186,39 +6222,35 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>ER-16.03</t>
+          <t>ER-13.05</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>ER-16 Commissioning and Tests on Completion</t>
+          <t>ER-13 Civil, structural and architectural works</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Grid Code compliance tests</t>
+          <t>Roads and drainage</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>All tests required by the TSO for connection and commercial operation, including reactive capability and frequency response.</t>
+          <t>Internal asphalt roads for 40 t axle loads to the heaviest delivery route, surface water drainage for ER-02.05 rainfall.</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>electrical</t>
+          <t>civil</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>TSO acceptance</t>
-        </is>
-      </c>
+          <t>inspection</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="n"/>
       <c r="H120" s="4" t="n"/>
       <c r="I120" s="4" t="inlineStr"/>
       <c r="J120" s="5" t="inlineStr"/>
@@ -6236,49 +6268,37 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>ER-16.04</t>
+          <t>ER-13.06</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>ER-16 Commissioning and Tests on Completion</t>
+          <t>ER-13 Civil, structural and architectural works</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Performance test</t>
+          <t>Marine works</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Performance test per ASME PTC 46 within 30 days after initial operation, test procedure submitted 90 days before, with instrument calibration traceable to national standards.</t>
+          <t>Intake and outfall pipelines (HDPE or GRP) with ballast and scour protection, designed for 50-year wave conditions.</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>commissioning</t>
+          <t>civil</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>PG-01/PG-02/PG-03 demonstrated</t>
-        </is>
-      </c>
-      <c r="H121" s="4" t="inlineStr">
-        <is>
-          <t>PG-01</t>
-        </is>
-      </c>
-      <c r="I121" s="4" t="inlineStr">
-        <is>
-          <t>&gt;= 600 MW</t>
-        </is>
-      </c>
+          <t>analysis</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="n"/>
+      <c r="H121" s="4" t="n"/>
+      <c r="I121" s="4" t="inlineStr"/>
       <c r="J121" s="5" t="inlineStr"/>
       <c r="K121" s="6" t="inlineStr">
         <is>
@@ -6294,22 +6314,22 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>ER-16.05</t>
+          <t>ER-14.01</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>ER-16 Commissioning and Tests on Completion</t>
+          <t>ER-14 Environment, health and safety</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Emission and noise tests</t>
+          <t>EIA compliance</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Emission tests by an accredited laboratory and noise surveys per PG-04 to PG-08.</t>
+          <t>The Works shall comply with the conditions of the positive EIA decision and the Environmental Law (No. 2872) and its regulations.</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -6319,20 +6339,16 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="G122" s="5" t="n"/>
-      <c r="H122" s="4" t="inlineStr">
-        <is>
-          <t>PG-04</t>
-        </is>
-      </c>
-      <c r="I122" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 30 mg/Nm3</t>
-        </is>
-      </c>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>No outstanding EIA non-conformities at Taking-Over</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="n"/>
+      <c r="I122" s="4" t="inlineStr"/>
       <c r="J122" s="5" t="inlineStr"/>
       <c r="K122" s="6" t="inlineStr">
         <is>
@@ -6348,49 +6364,62 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>ER-16.06</t>
+          <t>ER-14.02</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>ER-16 Commissioning and Tests on Completion</t>
+          <t>ER-14 Environment, health and safety</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Operational demonstration</t>
+          <t>Air emissions</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Demonstration of start times, ramp rates, minimum load, load rejection and trip tests.</t>
+          <t>Natural gas: NOx &lt;= 30 mg/Nm3, CO &lt;= 30 mg/Nm3, NH3 slip &lt;= 5 mg/Nm3. LDO: NOx &lt;= 50 mg/Nm3, CO &lt;= 50 mg/Nm3, SO2 &lt;= 10 mg/Nm3, dust &lt;= 5 mg/Nm3, NH3 slip &lt;= 5 mg/Nm3. All dry, 15 % O2, 50 % to 100 % GT load (ALP-OWN-ENV-001 section 1).</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>commissioning</t>
+          <t>hse</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>demonstration</t>
-        </is>
-      </c>
-      <c r="G123" s="5" t="n"/>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>Within guaranteed limits</t>
+        </is>
+      </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>PG-09</t>
+          <t>PG-04</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>&lt;= 45 min</t>
-        </is>
-      </c>
-      <c r="J123" s="5" t="inlineStr"/>
-      <c r="K123" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>&lt;= 30 mg/Nm3</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-CASE-0040
+design_parameter/DP-CASE-0041
+design_parameter/DP-CASE-0042
+design_parameter/DP-OWNR-0041
+design_parameter/DP-OWNR-0042
+design_parameter/DP-OWNR-0043</t>
+        </is>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -6402,27 +6431,27 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>ER-16.07</t>
+          <t>ER-14.03</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>ER-16 Commissioning and Tests on Completion</t>
+          <t>ER-14 Environment, health and safety</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>Reliability run</t>
+          <t>Near-field noise</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>30-day continuous reliability run with availability &gt;= 98 %; restarted after rectification if failed.</t>
+          <t>Maximum 85 dB(A) at 1 m from any equipment in normal operation.</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>commissioning</t>
+          <t>hse</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
@@ -6432,23 +6461,27 @@
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>&gt;= 98 %</t>
+          <t>&lt;= 85 dB(A)</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>PG-12</t>
+          <t>PG-07</t>
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>&gt;= 98 %</t>
-        </is>
-      </c>
-      <c r="J124" s="5" t="inlineStr"/>
-      <c r="K124" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>&lt;= 85 dB(A)</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-CASE-0044</t>
+        </is>
+      </c>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L124" s="4" t="inlineStr">
@@ -6460,41 +6493,57 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>ER-17.01</t>
+          <t>ER-14.04</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>ER-17 Documentation, training, O&amp;M and spares</t>
+          <t>ER-14 Environment, health and safety</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Document management</t>
+          <t>Environmental noise</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Documents submitted electronically with the Owner's numbering and a master document register; review period 14 days (21 days for the Basic Design Package).</t>
+          <t>Maximum 45 dB(A) LAeq night at the nearest sensitive receptor.</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>project_control</t>
+          <t>hse</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="G125" s="5" t="n"/>
-      <c r="H125" s="4" t="n"/>
-      <c r="I125" s="4" t="inlineStr"/>
-      <c r="J125" s="5" t="inlineStr"/>
-      <c r="K125" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>&lt;= 45 dB(A)</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>PG-08</t>
+        </is>
+      </c>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 45 dB(A)</t>
+        </is>
+      </c>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-CASE-0045</t>
+        </is>
+      </c>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -6506,27 +6555,27 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>ER-17.02</t>
+          <t>ER-14.05</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>ER-17 Documentation, training, O&amp;M and spares</t>
+          <t>ER-14 Environment, health and safety</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Schedule and reporting</t>
+          <t>Occupational health and safety</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Level 3 CPM schedule (MS Project XML or Primavera P6) with monthly updates, S-curves and progress reports.</t>
+          <t>Construction and design shall comply with the Occupational Health and Safety Law (No. 6331); the Contractor shall implement an ISO 45001-certified HSE management system and a lost-time-injury target of zero.</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>project_control</t>
+          <t>hse</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
@@ -6552,27 +6601,27 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>ER-17.03</t>
+          <t>ER-14.06</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>ER-17 Documentation, training, O&amp;M and spares</t>
+          <t>ER-14 Environment, health and safety</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>As-built documentation</t>
+          <t>Hazardous areas</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>As-built drawings, 3D model and engineering database within 3 months of Taking-Over.</t>
+          <t>Hazardous area classification per IEC 60079-10-1; equipment certified accordingly.</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>hse</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
@@ -6598,27 +6647,27 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>ER-17.04</t>
+          <t>ER-14.07</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>ER-17 Documentation, training, O&amp;M and spares</t>
+          <t>ER-14 Environment, health and safety</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>O&amp;M manuals</t>
+          <t>Process safety studies</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Operation and maintenance manuals (English, operating procedures also in Turkish) 6 months before first fire, final at Taking-Over.</t>
+          <t>HAZID, HAZOP, SIL determination, fire and explosion risk assessment and a Major Accident Prevention assessment where applicable.</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>hse</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
@@ -6626,7 +6675,11 @@
           <t>review</t>
         </is>
       </c>
-      <c r="G128" s="5" t="n"/>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>All actions closed before first fire</t>
+        </is>
+      </c>
       <c r="H128" s="4" t="n"/>
       <c r="I128" s="4" t="inlineStr"/>
       <c r="J128" s="5" t="inlineStr"/>
@@ -6644,32 +6697,32 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>ER-17.05</t>
+          <t>ER-14.08</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>ER-17 Documentation, training, O&amp;M and spares</t>
+          <t>ER-14 Environment, health and safety</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Carbon capture readiness</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Classroom, simulator and on-the-job training for 60 Owner staff (operators, maintenance, I&amp;C, chemistry), minimum 12 weeks per key trade.</t>
+          <t>Space reservation and tie-in points for a future post-combustion carbon capture plant at the HRSG outlet.</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>demonstration</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G129" s="5" t="n"/>
@@ -6690,22 +6743,22 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>ER-17.06</t>
+          <t>ER-15.01</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>ER-17 Documentation, training, O&amp;M and spares</t>
+          <t>ER-15 Quality, inspection and testing during manufacture</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Spare parts</t>
+          <t>Quality management</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Commissioning spares, special tools, and a recommended two-year operating spares list with prices valid for 18 months.</t>
+          <t>ISO 9001 quality management for the Contractor and all major subcontractors; project quality plan within 30 days of NTP.</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -6736,22 +6789,22 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>ER-17.07</t>
+          <t>ER-15.02</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>ER-17 Documentation, training, O&amp;M and spares</t>
+          <t>ER-15 Quality, inspection and testing during manufacture</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Long-term service</t>
+          <t>Inspection and test plans</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>The power island supplier shall offer a long-term service agreement for GT/ST/generators (separate contract, not part of the Contract Price).</t>
+          <t>ITPs for all major equipment with hold and witness points for the Engineer, 15 days' notice for witnessed tests.</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -6782,22 +6835,22 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>ER-18.01</t>
+          <t>ER-15.03</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>ER-18 Interfaces and terminal points</t>
+          <t>ER-15 Quality, inspection and testing during manufacture</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>Terminal points</t>
+          <t>Factory acceptance tests</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Terminal points and scope limits are defined in Appendix D; the Contractor shall provide all works up to and including the terminal points.</t>
+          <t>FATs at least for: GT and ST control systems, generators, GSU transformers, GIS, MV switchgear, DCS, CEMS.</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
@@ -6807,7 +6860,7 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G132" s="5" t="n"/>
@@ -6828,32 +6881,32 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>ER-18.02</t>
+          <t>ER-15.04</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>ER-18 Interfaces and terminal points</t>
+          <t>ER-15 Quality, inspection and testing during manufacture</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Grid connection interface</t>
+          <t>Material traceability</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>The Contractor shall coordinate with the TSO and the Owner's transmission line contractor for protection settings, SCADA and energisation.</t>
+          <t>Material certificates per EN 10204 3.1 (3.2 for pressure parts above 50 bar) and positive material identification of alloy piping.</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>electrical</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>inspection</t>
         </is>
       </c>
       <c r="G133" s="5" t="n"/>
@@ -6874,32 +6927,32 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>ER-18.03</t>
+          <t>ER-15.05</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>ER-18 Interfaces and terminal points</t>
+          <t>ER-15 Quality, inspection and testing during manufacture</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>Gas network interface</t>
+          <t>Welding</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>The Contractor shall coordinate the gas receiving station tie-in, pressure protection and metering approval with the gas network operator.</t>
+          <t>Welding per ASME IX / EN ISO 15614, 100 % NDE of HP/HRH/main steam butt welds.</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>piping</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>inspection</t>
         </is>
       </c>
       <c r="G134" s="5" t="n"/>
@@ -6920,27 +6973,27 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>ER-18.04</t>
+          <t>ER-16.01</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>ER-18 Interfaces and terminal points</t>
+          <t>ER-16 Commissioning and Tests on Completion</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>Owner's engineering database</t>
+          <t>Commissioning plan</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>All interface data shall be exchanged through the Owner's engineering database (single source of truth).</t>
+          <t>System-based commissioning plan with pre-commissioning, cold and hot commissioning, submitted 9 months before first fire.</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>commissioning</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
@@ -6958,6 +7011,936 @@
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>ER-16.02</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>ER-16 Commissioning and Tests on Completion</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>Steam blowing and chemical cleaning</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>Chemical cleaning of the HRSG and steam blowing of steam lines to OEM cleanliness criteria.</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>commissioning</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="n"/>
+      <c r="H136" s="4" t="n"/>
+      <c r="I136" s="4" t="inlineStr"/>
+      <c r="J136" s="5" t="inlineStr"/>
+      <c r="K136" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>ER-16.03</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>ER-16 Commissioning and Tests on Completion</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>Grid Code compliance tests</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>All tests required by the TSO for connection and commercial operation, including reactive capability and frequency response.</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>electrical</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>TSO acceptance</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="n"/>
+      <c r="I137" s="4" t="inlineStr"/>
+      <c r="J137" s="5" t="inlineStr"/>
+      <c r="K137" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L137" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>ER-16.04</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>ER-16 Commissioning and Tests on Completion</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>Performance test</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>Performance test per ASME PTC 46 within 30 days after initial operation, test procedure submitted 90 days before, with instrument calibration traceable to national standards.</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>commissioning</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>PG-01/PG-02/PG-03 demonstrated</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>PG-01</t>
+        </is>
+      </c>
+      <c r="I138" s="4" t="inlineStr">
+        <is>
+          <t>&gt;= 600 MW</t>
+        </is>
+      </c>
+      <c r="J138" s="5" t="inlineStr"/>
+      <c r="K138" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>ER-16.05</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>ER-16 Commissioning and Tests on Completion</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>Emission and noise tests</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>Emission tests by an accredited laboratory and noise surveys per PG-04 to PG-08.</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>hse</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="n"/>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>PG-04</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 30 mg/Nm3</t>
+        </is>
+      </c>
+      <c r="J139" s="5" t="inlineStr"/>
+      <c r="K139" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>ER-16.06</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>ER-16 Commissioning and Tests on Completion</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>Operational demonstration</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>Demonstration of start times, ramp rates, minimum load, load rejection and trip tests.</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>commissioning</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>demonstration</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="n"/>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>PG-09</t>
+        </is>
+      </c>
+      <c r="I140" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 45 min</t>
+        </is>
+      </c>
+      <c r="J140" s="5" t="inlineStr"/>
+      <c r="K140" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L140" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>ER-16.07</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>ER-16 Commissioning and Tests on Completion</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>Reliability run</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>30-day continuous reliability run with availability &gt;= 98 %; restarted after rectification if failed.</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>commissioning</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>&gt;= 98 %</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>PG-12</t>
+        </is>
+      </c>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>&gt;= 98 %</t>
+        </is>
+      </c>
+      <c r="J141" s="5" t="inlineStr"/>
+      <c r="K141" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L141" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>ER-16.08</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>ER-16 Commissioning and Tests on Completion</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>Tests on LDO</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>Performance test on LDO (24 h, corrected to SRC), emission tests on LDO, automatic fuel transfer tests and a start on LDO.</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>commissioning</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>PG-15, PG-16, PG-17, PG-18 demonstrated</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>PG-15</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t>&gt;= 560 MW</t>
+        </is>
+      </c>
+      <c r="J142" s="5" t="inlineStr"/>
+      <c r="K142" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>ER-17.01</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>ER-17 Documentation, training, O&amp;M and spares</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>Document management</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>Documents submitted electronically with the Owner's numbering and a master document register; review period 14 days (21 days for the Basic Design Package).</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>project_control</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="n"/>
+      <c r="H143" s="4" t="n"/>
+      <c r="I143" s="4" t="inlineStr"/>
+      <c r="J143" s="5" t="inlineStr"/>
+      <c r="K143" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L143" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>ER-17.02</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>ER-17 Documentation, training, O&amp;M and spares</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>Schedule and reporting</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>Level 3 CPM schedule (MS Project XML or Primavera P6) with monthly updates, S-curves and progress reports.</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>project_control</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G144" s="5" t="n"/>
+      <c r="H144" s="4" t="n"/>
+      <c r="I144" s="4" t="inlineStr"/>
+      <c r="J144" s="5" t="inlineStr"/>
+      <c r="K144" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L144" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>ER-17.03</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>ER-17 Documentation, training, O&amp;M and spares</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>As-built documentation</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>As-built drawings, 3D model and engineering database within 3 months of Taking-Over.</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="n"/>
+      <c r="H145" s="4" t="n"/>
+      <c r="I145" s="4" t="inlineStr"/>
+      <c r="J145" s="5" t="inlineStr"/>
+      <c r="K145" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L145" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>ER-17.04</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>ER-17 Documentation, training, O&amp;M and spares</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>O&amp;M manuals</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>Operation and maintenance manuals (English, operating procedures also in Turkish) 6 months before first fire, final at Taking-Over.</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="n"/>
+      <c r="H146" s="4" t="n"/>
+      <c r="I146" s="4" t="inlineStr"/>
+      <c r="J146" s="5" t="inlineStr"/>
+      <c r="K146" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L146" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>ER-17.05</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>ER-17 Documentation, training, O&amp;M and spares</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>Classroom, simulator and on-the-job training for 60 Owner staff (operators, maintenance, I&amp;C, chemistry), minimum 12 weeks per key trade.</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>demonstration</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="n"/>
+      <c r="H147" s="4" t="n"/>
+      <c r="I147" s="4" t="inlineStr"/>
+      <c r="J147" s="5" t="inlineStr"/>
+      <c r="K147" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L147" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>ER-17.06</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>ER-17 Documentation, training, O&amp;M and spares</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>Spare parts</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>Commissioning spares, special tools, and a recommended two-year operating spares list with prices valid for 18 months.</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G148" s="5" t="n"/>
+      <c r="H148" s="4" t="n"/>
+      <c r="I148" s="4" t="inlineStr"/>
+      <c r="J148" s="5" t="inlineStr"/>
+      <c r="K148" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L148" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>ER-17.07</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>ER-17 Documentation, training, O&amp;M and spares</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>Long-term service</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>The power island supplier shall offer a long-term service agreement for GT/ST/generators (separate contract, not part of the Contract Price).</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="n"/>
+      <c r="H149" s="4" t="n"/>
+      <c r="I149" s="4" t="inlineStr"/>
+      <c r="J149" s="5" t="inlineStr"/>
+      <c r="K149" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L149" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>ER-18.01</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>ER-18 Interfaces and terminal points</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>Terminal points</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>Terminal points and scope limits are defined in Appendix D; the Contractor shall provide all works up to and including the terminal points.</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="n"/>
+      <c r="H150" s="4" t="n"/>
+      <c r="I150" s="4" t="inlineStr"/>
+      <c r="J150" s="5" t="inlineStr"/>
+      <c r="K150" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>ER-18.02</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>ER-18 Interfaces and terminal points</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>Grid connection interface</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>The Owner builds and energises the 380 kV line up to TP-E1 (available by 2028-07-15, an Owner-furnished item under Sub-Clause 2.4) and coordinates the line energisation with the TSO. The Contractor coordinates plant-side protection settings, SCADA and the Grid Code compliance tests with the TSO and the Owner's line contractor.</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>electrical</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G151" s="5" t="n"/>
+      <c r="H151" s="4" t="n"/>
+      <c r="I151" s="4" t="inlineStr"/>
+      <c r="J151" s="5" t="inlineStr"/>
+      <c r="K151" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L151" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>ER-18.03</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>ER-18 Interfaces and terminal points</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>Gas network interface</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>The Contractor shall coordinate the gas receiving station tie-in, pressure protection and metering approval with the gas network operator.</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G152" s="5" t="n"/>
+      <c r="H152" s="4" t="n"/>
+      <c r="I152" s="4" t="inlineStr"/>
+      <c r="J152" s="5" t="inlineStr"/>
+      <c r="K152" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L152" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>ER-18.04</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>ER-18 Interfaces and terminal points</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>Owner's engineering database</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>All interface data shall be exchanged through the Owner's engineering database (single source of truth).</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G153" s="5" t="n"/>
+      <c r="H153" s="4" t="n"/>
+      <c r="I153" s="4" t="inlineStr"/>
+      <c r="J153" s="5" t="inlineStr"/>
+      <c r="K153" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L153" s="4" t="inlineStr">
+        <is>
+          <t>contractual</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>ER-18.05</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>ER-18 Interfaces and terminal points</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>Tie-in register</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>The tie-in points, their location, conditions and the Owner's availability dates are listed in the tie-in register (Appendix D). The Contractor's scope starts at each tie-in; the Contractor shall verify the conditions and coordinate the interface works.</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G154" s="5" t="n"/>
+      <c r="H154" s="4" t="n"/>
+      <c r="I154" s="4" t="inlineStr"/>
+      <c r="J154" s="5" t="inlineStr"/>
+      <c r="K154" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L154" s="4" t="inlineStr">
         <is>
           <t>contractual</t>
         </is>
@@ -6976,7 +7959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7002,7 +7985,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T16:52:33Z by SETUP | data 1056b7942a4e71f0</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T17:19:53Z by SETUP | data 18b487674243d713</t>
         </is>
       </c>
     </row>
@@ -7684,6 +8667,182 @@
       <c r="K18" s="4" t="inlineStr">
         <is>
           <t>ER-08.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>PG-15</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Net electrical output on LDO at Site Reference Conditions</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>performance</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>560</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>543.2</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>800</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>EUR per kW shortfall</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>ER-16.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>PG-16</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Net heat rate (LHV) on LDO at Site Reference Conditions</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>performance</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>6150</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>kJ/kWh</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>6334.5</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>EUR per kJ/kWh excess</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PG-17</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>NOx emission on LDO (as NO2)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>emissions</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>mg/Nm3</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>No LD: the Contractor shall rectify until compliant (permit condition).</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>ER-03.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>PG-18</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Automatic fuel transfer gas to LDO without trip</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>% successful transfers</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Must rectify; Taking-Over not issued before successful demonstration.</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>ER-03.10</t>
         </is>
       </c>
     </row>
@@ -7700,7 +8859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7723,7 +8882,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T16:52:33Z by SETUP | data 1056b7942a4e71f0</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T17:19:53Z by SETUP | data 18b487674243d713</t>
         </is>
       </c>
     </row>
@@ -9402,7 +10561,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Potable water and sewage connections at site boundary</t>
+          <t>Potable water connection at site boundary (no sewer available)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -9684,6 +10843,230 @@
       <c r="H55" s="5" t="inlineStr">
         <is>
           <t>Owner's warehouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>SC-052</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Fuel oil</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>LDO truck unloading station (4 bays), storage tanks 2 x 50 %, bund, foam system</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>Tanker coupling at unloading bays</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>SC-053</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Fuel oil</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>LDO forwarding pumps, filters, metering, fuel treatment (2 x 100 % centrifugal separators)</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>GT liquid fuel skid inlet flange</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>SC-054</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Power island</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Dual-fuel GT combustion system, liquid fuel skid, water injection skid, purge system</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>SC-055</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Commissioning</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>LDO first fill of the storage tanks</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="n"/>
+      <c r="G59" s="4" t="n"/>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Tanker coupling at unloading bays</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>SC-056</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Commissioning</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>LDO for tests beyond the first fill</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="n"/>
+      <c r="G60" s="4" t="n"/>
+      <c r="H60" s="5" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>SC-057</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Balance of plant</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Packaged sanitary wastewater treatment plant (biological + UV), discharge via outfall</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Discharge into the outfall</t>
         </is>
       </c>
     </row>
@@ -9725,7 +11108,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T16:52:33Z by SETUP | data 1056b7942a4e71f0</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T17:19:53Z by SETUP | data 18b487674243d713</t>
         </is>
       </c>
     </row>
@@ -9822,28 +11205,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>77.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -9856,22 +11239,22 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
         <v>2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>40</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
@@ -9880,7 +11263,7 @@
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -9992,25 +11375,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>16.7</v>
+        <v>27.3</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
@@ -10026,16 +11409,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -10050,7 +11433,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -10298,10 +11681,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -10310,7 +11693,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -10366,7 +11749,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -10387,7 +11770,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -10400,13 +11783,13 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>20.6</v>
+        <v>24.7</v>
       </c>
     </row>
   </sheetData>

--- a/output/requirements_matrix/ALP_requirements_matrix.xlsx
+++ b/output/requirements_matrix/ALP_requirements_matrix.xlsx
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T17:19:53Z by SETUP | data 18b487674243d713</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T17:46:40Z by SETUP | data b226b6c9cd57c954</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>The Site is a 12.0 ha plot (400 m east-west x 300 m north-south) on the northern Marmara coast, levelled by the Owner to +15.0 m, plant grid origin at the south-west corner, plant north = true north. The usable area after the 60 m public coastal strip, the 10 m stream-channel buffer on the west boundary and the 5 m landscaping strip is about 10.6 ha. A further 5 ha temporary construction area north of the plot is provided by the Owner (tie-in TP-A1). Details and existing features per ALP-OWN-GEN-001.</t>
+          <t>The Site is a 12.0 ha plot (400 m east-west x 300 m north-south) on the northern Marmara coast, levelled by the Owner to +15.0 m, plant grid origin at the south-west corner, plant north = true north. The usable area inside the 10 m stream-channel buffer on the west boundary and the 5 m landscaping strip is about 10.6 ha (E 20-395, N 12-295); the 60 m public coastal strip lies between the plot and the shoreline. A further 5.04 ha temporary construction area north of the plot (E 0-180, N 320-600) is provided by the Owner (tie-in TP-A1). Details and existing features per ALP-OWN-GEN-001 and drawings ALP-OWN-DWG-001 (external connections) and ALP-OWN-DWG-002 (site and construction area plan).</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -7985,7 +7985,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T17:19:53Z by SETUP | data 18b487674243d713</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T17:46:40Z by SETUP | data b226b6c9cd57c954</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T17:19:53Z by SETUP | data 18b487674243d713</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T17:46:40Z by SETUP | data b226b6c9cd57c954</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T17:19:53Z by SETUP | data 18b487674243d713</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T17:46:40Z by SETUP | data b226b6c9cd57c954</t>
         </is>
       </c>
     </row>

--- a/output/requirements_matrix/ALP_requirements_matrix.xlsx
+++ b/output/requirements_matrix/ALP_requirements_matrix.xlsx
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T17:46:40Z by SETUP | data b226b6c9cd57c954</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T18:30:49Z by SETUP | data f8f7008e372ad5f4</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,8 @@
           <t>design_parameter/DP-CASE-0010
 design_parameter/DP-CASE-0011
 design_parameter/DP-CASE-0012
-design_parameter/DP-CASE-0014</t>
+design_parameter/DP-CASE-0014
+hmb_case/SRC-NG-100</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1847,7 +1848,8 @@
 design_parameter/DP-CASE-0019
 design_parameter/DP-CASE-0020
 design_parameter/DP-CASE-0021
-design_parameter/DP-OWNR-0024</t>
+design_parameter/DP-OWNR-0024
+hmb_case/SRC-NG-100</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -7959,7 +7961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7985,7 +7987,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T17:46:40Z by SETUP | data b226b6c9cd57c954</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T18:30:49Z by SETUP | data f8f7008e372ad5f4</t>
         </is>
       </c>
     </row>
@@ -8049,12 +8051,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>PG-01</t>
+          <t>IG-01</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Net electrical output at Site Reference Conditions</t>
+          <t>Power island gross output at the generator terminals</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -8063,7 +8065,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -8075,37 +8077,21 @@
           <t>min</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>582</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>EUR per kW shortfall</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Below 97 % of the guaranteed value the Owner may reject the Works after the rectification period (Sub-Clause 12.5).</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>ER-04.01, ER-16.04</t>
-        </is>
-      </c>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>PG-02</t>
+          <t>IG-02</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Net heat rate (LHV) at Site Reference Conditions</t>
+          <t>Power island gross heat rate (LHV)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -8114,7 +8100,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5860</v>
+        <v>5745</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -8126,37 +8112,21 @@
           <t>max</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>6035.8</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>400000</v>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>EUR per kJ/kWh excess</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>Above 103 % of the guaranteed value the Owner may reject the Works after the rectification period.</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>ER-04.02</t>
-        </is>
-      </c>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>PG-03</t>
+          <t>IG-03</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Net heat rate (LHV) at 60 % plant load</t>
+          <t>GT output at the generator terminals</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -8165,56 +8135,46 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>6250</v>
+        <v>418</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>kJ/kWh</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>EUR per kJ/kWh excess</t>
-        </is>
-      </c>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
       <c r="J7" s="5" t="n"/>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>ER-04.03</t>
-        </is>
-      </c>
+      <c r="K7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>PG-04</t>
+          <t>IG-04</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>NOx emission (as NO2)</t>
+          <t>Condenser pressure at 16.0 degC seawater and 36,050 m3/h</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>emissions</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>30</v>
+        <v>35.5</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>mg/Nm3</t>
+          <t>mbar(a)</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -8225,39 +8185,31 @@
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="n"/>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>No LD: the Contractor shall rectify at its cost until compliant; Taking-Over is not issued before compliance.</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>ER-06.03, ER-14.02, ER-16.05</t>
-        </is>
-      </c>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>PG-05</t>
+          <t>IG-05</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>CO emission</t>
+          <t>IEC auxiliary loads (excl. GSU losses)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>emissions</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>30</v>
+        <v>2700</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>mg/Nm3</t>
+          <t>kW</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -8268,22 +8220,18 @@
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="4" t="n"/>
       <c r="I9" s="4" t="n"/>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>Must rectify (as PG-04).</t>
-        </is>
-      </c>
+      <c r="J9" s="5" t="n"/>
       <c r="K9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>PG-06</t>
+          <t>IG-06</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Ammonia slip from the SCR</t>
+          <t>NOx at HRSG outlet (15 % O2, dry), 40-100 % GT load, natural gas</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -8292,7 +8240,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -8307,78 +8255,82 @@
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n"/>
       <c r="I10" s="4" t="n"/>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>Must rectify.</t>
-        </is>
-      </c>
+      <c r="J10" s="5" t="n"/>
       <c r="K10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>PG-07</t>
+          <t>PG-01</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Near-field noise</t>
+          <t>Net electrical output at Site Reference Conditions</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>noise</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>85</v>
+        <v>600</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>dB(A)</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>582</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>EUR per kW shortfall</t>
+        </is>
+      </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Must rectify.</t>
+          <t>Below 97 % of the guaranteed value the Owner may reject the Works after the rectification period (Sub-Clause 12.5).</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>ER-14.03</t>
+          <t>ER-04.01, ER-16.04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>PG-08</t>
+          <t>PG-02</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Noise at nearest sensitive receptor (night)</t>
+          <t>Net heat rate (LHV) at Site Reference Conditions</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>noise</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>45</v>
+        <v>5860</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>dB(A)</t>
+          <t>kJ/kWh</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -8386,48 +8338,50 @@
           <t>max</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n"/>
+      <c r="G12" s="4" t="n">
+        <v>6035.8</v>
+      </c>
       <c r="H12" s="4" t="n">
-        <v>250000</v>
+        <v>400000</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>EUR per dB(A) exceedance (after rectification attempts)</t>
+          <t>EUR per kJ/kWh excess</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Contractor to rectify first; LD only if rectification fails.</t>
+          <t>Above 103 % of the guaranteed value the Owner may reject the Works after the rectification period.</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>ER-14.04</t>
+          <t>ER-04.02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>PG-09</t>
+          <t>PG-03</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Hot start time to base load</t>
+          <t>Net heat rate (LHV) at 60 % plant load</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>45</v>
+        <v>6250</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>kJ/kWh</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -8437,87 +8391,85 @@
       </c>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n">
-        <v>20000</v>
+        <v>150000</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>EUR per minute exceedance</t>
+          <t>EUR per kJ/kWh excess</t>
         </is>
       </c>
       <c r="J13" s="5" t="n"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>ER-04.04, ER-16.06</t>
+          <t>ER-04.03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>PG-10</t>
+          <t>PG-04</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Load ramp rate in combined cycle</t>
+          <t>NOx emission (as NO2)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>MW/min</t>
+          <t>mg/Nm3</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>max</t>
         </is>
       </c>
       <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n">
-        <v>100000</v>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>EUR per MW/min shortfall</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>No LD: the Contractor shall rectify at its cost until compliant; Taking-Over is not issued before compliance.</t>
+        </is>
+      </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>ER-04.05</t>
+          <t>ER-06.03, ER-14.02, ER-16.05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>PG-11</t>
+          <t>PG-05</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Minimum environmental load</t>
+          <t>CO emission</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>% of plant net output</t>
+          <t>mg/Nm3</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -8526,48 +8478,42 @@
         </is>
       </c>
       <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n">
-        <v>300000</v>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>EUR per percentage point exceedance</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>ER-04.06</t>
-        </is>
-      </c>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Must rectify (as PG-04).</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>PG-12</t>
+          <t>PG-06</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Reliability run availability</t>
+          <t>Ammonia slip from the SCR</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>reliability</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>mg/Nm3</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>max</t>
         </is>
       </c>
       <c r="G16" s="4" t="n"/>
@@ -8575,37 +8521,33 @@
       <c r="I16" s="4" t="n"/>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Failed run to be repeated from the start after rectification.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>ER-16.07</t>
-        </is>
-      </c>
+          <t>Must rectify.</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>PG-13</t>
+          <t>PG-07</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Condenser cooling water temperature rise</t>
+          <t>Near-field noise</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>environmental</t>
+          <t>noise</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>dB(A)</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -8618,37 +8560,37 @@
       <c r="I17" s="4" t="n"/>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Must rectify (EIA permit condition).</t>
+          <t>Must rectify.</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>ER-07.04</t>
+          <t>ER-14.03</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>PG-14</t>
+          <t>PG-08</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Thermal plume at edge of mixing zone</t>
+          <t>Noise at nearest sensitive receptor (night)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>environmental</t>
+          <t>noise</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>dB(A)</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -8657,131 +8599,137 @@
         </is>
       </c>
       <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
+      <c r="H18" s="4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>EUR per dB(A) exceedance (after rectification attempts)</t>
+        </is>
+      </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Must rectify (EIA permit condition).</t>
+          <t>Contractor to rectify first; LD only if rectification fails.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>ER-08.05</t>
+          <t>ER-14.04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>PG-15</t>
+          <t>PG-09</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Net electrical output on LDO at Site Reference Conditions</t>
+          <t>Hot start time to base load</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>560</v>
+        <v>45</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>min</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>543.2</v>
-      </c>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n"/>
       <c r="H19" s="4" t="n">
-        <v>800</v>
+        <v>20000</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>EUR per kW shortfall</t>
+          <t>EUR per minute exceedance</t>
         </is>
       </c>
       <c r="J19" s="5" t="n"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>ER-16.08</t>
+          <t>ER-04.04, ER-16.06</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>PG-16</t>
+          <t>PG-10</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Net heat rate (LHV) on LDO at Site Reference Conditions</t>
+          <t>Load ramp rate in combined cycle</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>6150</v>
+        <v>35</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>kJ/kWh</t>
+          <t>MW/min</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>6334.5</v>
-      </c>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="n">
-        <v>60000</v>
+        <v>100000</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>EUR per kJ/kWh excess</t>
+          <t>EUR per MW/min shortfall</t>
         </is>
       </c>
       <c r="J20" s="5" t="n"/>
-      <c r="K20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>ER-04.05</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>PG-17</t>
+          <t>PG-11</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>NOx emission on LDO (as NO2)</t>
+          <t>Minimum environmental load</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>emissions</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>mg/Nm3</t>
+          <t>% of plant net output</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -8790,41 +8738,43 @@
         </is>
       </c>
       <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>No LD: the Contractor shall rectify until compliant (permit condition).</t>
-        </is>
-      </c>
+      <c r="H21" s="4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>EUR per percentage point exceedance</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="n"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>ER-03.11</t>
+          <t>ER-04.06</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>PG-18</t>
+          <t>PG-12</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Automatic fuel transfer gas to LDO without trip</t>
+          <t>Reliability run availability</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>reliability</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>% successful transfers</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -8837,10 +8787,272 @@
       <c r="I22" s="4" t="n"/>
       <c r="J22" s="5" t="inlineStr">
         <is>
+          <t>Failed run to be repeated from the start after rectification.</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>ER-16.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>PG-13</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Condenser cooling water temperature rise</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>environmental</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Must rectify (EIA permit condition).</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>ER-07.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>PG-14</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Thermal plume at edge of mixing zone</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>environmental</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Must rectify (EIA permit condition).</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>ER-08.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>PG-15</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Net electrical output on LDO at Site Reference Conditions</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>performance</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>560</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>543.2</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>800</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>EUR per kW shortfall</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>ER-16.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>PG-16</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Net heat rate (LHV) on LDO at Site Reference Conditions</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>performance</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>6150</v>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>kJ/kWh</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>6334.5</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>EUR per kJ/kWh excess</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>PG-17</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>NOx emission on LDO (as NO2)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>emissions</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>mg/Nm3</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>No LD: the Contractor shall rectify until compliant (permit condition).</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>ER-03.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>PG-18</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Automatic fuel transfer gas to LDO without trip</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>% successful transfers</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
           <t>Must rectify; Taking-Over not issued before successful demonstration.</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>ER-03.10</t>
         </is>
@@ -8859,7 +9071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8882,7 +9094,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T17:46:40Z by SETUP | data b226b6c9cd57c954</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T18:30:49Z by SETUP | data f8f7008e372ad5f4</t>
         </is>
       </c>
     </row>
@@ -8931,125 +9143,141 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>SC-001</t>
+          <t>DR-001</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Site</t>
+          <t>Gas turbine and fuel</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Land, access rights and site handover (levelled to +15.0 m)</t>
+          <t>Gas turbine package incl. enclosure, lube oil, hydraulic and fuel skids</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Site boundary per land-use plan</t>
-        </is>
-      </c>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SC-002</t>
+          <t>DR-002</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Site</t>
+          <t>Gas turbine and fuel</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Environmental Impact Assessment (EIA) positive decision</t>
+          <t>GT inlet air filter house, anti-icing, silencer, inlet duct</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SC-003</t>
+          <t>DR-003</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Site</t>
+          <t>Gas turbine and fuel</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Construction, operating and building permits (Contractor supplies all design inputs)</t>
+          <t>GT exhaust diffuser and expansion joint to HRSG</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SC-004</t>
+          <t>DR-004</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Site</t>
+          <t>Gas turbine and fuel</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Geotechnical and topographic surveys (baseline supplied by Owner, confirmatory by Contractor)</t>
+          <t>Performance fuel gas heater and GT gas skid (from IF-01)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -9057,23 +9285,27 @@
           <t>IEPC</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
       <c r="H8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>SC-005</t>
+          <t>DR-005</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Site</t>
+          <t>Gas turbine and fuel</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Site preparation, fencing, roads, drainage, temporary facilities</t>
+          <t>Gas receiving and metering station, start-up gas heating, final filtration 3 um</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -9091,23 +9323,27 @@
           <t>IEPC</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SC-006</t>
+          <t>DR-006</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Power island</t>
+          <t>Gas turbine and fuel</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Gas turbine package incl. auxiliaries, enclosure, inlet air filtration, exhaust diffuser</t>
+          <t>Liquid fuel skid, water injection skid, purge and recirculation (from IF-02/03)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -9130,36 +9366,32 @@
           <t>IEC</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>GT exhaust flange to HRSG inlet duct</t>
-        </is>
-      </c>
+      <c r="H10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>SC-007</t>
+          <t>DR-007</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Power island</t>
+          <t>Gas turbine and fuel</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>GT generator incl. excitation, protection, cooling</t>
+          <t>LDO unloading, storage, forwarding and treatment</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>IEC</t>
+          <t>IEPC</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>IEC</t>
+          <t>IEPC</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -9169,29 +9401,25 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>IEC</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Generator terminals (IPB connection)</t>
-        </is>
-      </c>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>SC-008</t>
+          <t>DR-008</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Power island</t>
+          <t>Gas turbine and fuel</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Steam turbine (HP/IP/LP, reheat) incl. lube/control oil, gland steam, turning gear</t>
+          <t>Compressor washing skid</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -9219,17 +9447,17 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SC-009</t>
+          <t>DR-009</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Power island</t>
+          <t>Gas turbine and fuel</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>ST generator incl. excitation, protection</t>
+          <t>GT enclosure fire suppression (CO2) and gas detection</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -9252,26 +9480,22 @@
           <t>IEC</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>Generator terminals</t>
-        </is>
-      </c>
+      <c r="H13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SC-010</t>
+          <t>DR-010</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Power island</t>
+          <t>HRSG</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>HRSG triple-pressure reheat, horizontal, natural circulation, with SCR and CO catalyst</t>
+          <t>HRSG pressure parts, casing, drums, platforms, CPH recirculation pumps</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -9291,39 +9515,35 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>IEC</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>HRSG outlet to stack</t>
-        </is>
-      </c>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>SC-011</t>
+          <t>DR-011</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Power island</t>
+          <t>HRSG</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Stack 60 m with CEMS platform and silencer</t>
+          <t>SCR catalyst, ammonia injection grid and skid, CO catalyst</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -9341,27 +9561,27 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>SC-012</t>
+          <t>DR-012</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Power island</t>
+          <t>HRSG</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Water-cooled condenser (seawater), vacuum system</t>
+          <t>Aqueous ammonia unloading, storage and forwarding</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>IEC</t>
+          <t>IEPC</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>IEC</t>
+          <t>IEPC</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -9371,39 +9591,35 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>IEC</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>Cooling water flanges at condenser water boxes</t>
-        </is>
-      </c>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>SC-013</t>
+          <t>DR-013</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Power island</t>
+          <t>HRSG</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Power island control system (TCS/ST controls) integrated in plant DCS</t>
+          <t>HRSG blowdown tanks, drain tanks, atmospheric flash tanks</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>IEC</t>
+          <t>IEPC</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>IEC</t>
+          <t>IEPC</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -9413,39 +9629,35 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>IEC</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>DCS interface (redundant fibre)</t>
-        </is>
-      </c>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>SC-014</t>
+          <t>DR-014</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Power island</t>
+          <t>HRSG</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>GSU transformers (GT and ST), isolated phase busducts, generator circuit breakers</t>
+          <t>Chemical dosing and steam/water sampling (SWAS)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>IEC</t>
+          <t>IEPC</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>IEC</t>
+          <t>IEPC</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -9455,29 +9667,25 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>IEC</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>GSU HV bushings</t>
-        </is>
-      </c>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>SC-015</t>
+          <t>DR-015</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Balance of plant</t>
+          <t>HRSG</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Condensate and boiler feed water systems (pumps 2x100 %)</t>
+          <t>Stack incl. silencer, CEMS, aviation lighting</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -9505,27 +9713,27 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>SC-016</t>
+          <t>DR-016</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Balance of plant</t>
+          <t>Steam turbine and steam piping</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Seawater intake, screens, CW pumps (2x50 %), outfall and diffuser</t>
+          <t>Steam turbine with valves, lube/EHC oil, gland steam system, turning gear</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -9535,39 +9743,35 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>Offshore intake head / outfall diffuser</t>
-        </is>
-      </c>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>SC-017</t>
+          <t>DR-017</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Balance of plant</t>
+          <t>Steam turbine and steam piping</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Electro-chlorination for biofouling control</t>
+          <t>HP / IP / LP bypass valves with desuperheaters</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -9577,7 +9781,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="H21" s="5" t="n"/>
@@ -9585,17 +9789,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>SC-018</t>
+          <t>DR-018</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Balance of plant</t>
+          <t>Steam turbine and steam piping</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Seawater reverse osmosis and demineralisation plant</t>
+          <t>HP, cold reheat, hot reheat and LP steam piping HRSG - ST incl. supports</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -9623,17 +9827,17 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>SC-019</t>
+          <t>DR-019</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Balance of plant</t>
+          <t>Steam turbine and steam piping</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Condensate polishing plant</t>
+          <t>Bypass piping and spray water piping</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -9661,17 +9865,17 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>SC-020</t>
+          <t>DR-020</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Balance of plant</t>
+          <t>Steam turbine and steam piping</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Waste water treatment and effluent monitoring</t>
+          <t>ST drains, drain collection and flash tank</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -9694,36 +9898,32 @@
           <t>IEPC</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>Discharge point to outfall</t>
-        </is>
-      </c>
+      <c r="H24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>SC-021</t>
+          <t>DR-021</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Balance of plant</t>
+          <t>Condenser and cycle</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Closed cooling water system with plate heat exchangers</t>
+          <t>Condenser incl. dump devices, hotwell, vacuum pumps</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -9741,17 +9941,17 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>SC-022</t>
+          <t>DR-022</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Balance of plant</t>
+          <t>Condenser and cycle</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Compressed air (service and instrument) 2x100 %</t>
+          <t>Tube cleaning ball system and debris filters</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -9779,17 +9979,17 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>SC-023</t>
+          <t>DR-023</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Balance of plant</t>
+          <t>Condenser and cycle</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Auxiliary boiler (gas-fired) for start-up steam</t>
+          <t>Circulating water system, intake, pumps, outfall, electro-chlorination</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -9817,17 +10017,17 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>SC-024</t>
+          <t>DR-024</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Balance of plant</t>
+          <t>Condenser and cycle</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Fire detection and protection per NFPA 850</t>
+          <t>Condensate pumps, boiler feed pumps, condensate polishing</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -9855,17 +10055,17 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>SC-025</t>
+          <t>DR-025</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Balance of plant</t>
+          <t>Condenser and cycle</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>HVAC for all buildings and electrical rooms</t>
+          <t>Closed cooling water system</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -9893,27 +10093,27 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>SC-026</t>
+          <t>DR-026</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Balance of plant</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Cranes and hoists (turbine hall EOT crane)</t>
+          <t>GT and ST generators incl. excitation, neutral earthing</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -9923,7 +10123,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="H30" s="5" t="n"/>
@@ -9931,69 +10131,65 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>SC-027</t>
+          <t>DR-027</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Fuel gas</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Gas pipeline from national transmission system to plant boundary</t>
+          <t>Generator circuit breakers, isolated phase busducts</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
+          <t>IEPC</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Owner valve at plant boundary (inlet flange of gas receiving station)</t>
-        </is>
-      </c>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>SC-028</t>
+          <t>DR-028</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Fuel gas</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Gas receiving and metering station (fiscal metering, filtration, heating, pressure control)</t>
+          <t>GT and ST generator step-up transformers</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -10003,29 +10199,25 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>Inlet flange at plant boundary</t>
-        </is>
-      </c>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>SC-029</t>
+          <t>DR-029</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Fuel gas</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Performance gas heater and GT fuel skid</t>
+          <t>SFC and isolation transformer</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -10053,7 +10245,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>SC-030</t>
+          <t>DR-030</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -10063,17 +10255,17 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>380 kV GIS switchyard (double busbar) within plant boundary</t>
+          <t>Generator and GSU protection panels</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -10083,19 +10275,15 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>380 kV line gantry / cable sealing ends</t>
-        </is>
-      </c>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>SC-031</t>
+          <t>DR-031</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -10105,39 +10293,35 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>380 kV transmission connection line and remote substation works</t>
+          <t>H2 and CO2 bottle racks and supply piping</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
+          <t>IEPC</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
+          <t>IEPC</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
+          <t>IEPC</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Line gantry at switchyard</t>
-        </is>
-      </c>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>SC-032</t>
+          <t>DR-032</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -10147,7 +10331,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Unit auxiliary transformers, MV switchgear 10.5 kV, LV 0.4 kV distribution</t>
+          <t>Unit auxiliary transformers, MV/LV switchgear, UPS/DC, cabling</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -10175,7 +10359,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>SC-033</t>
+          <t>DR-033</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -10185,7 +10369,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Emergency diesel generator and UPS / DC systems</t>
+          <t>380 kV connection GSU - GIS, GIS switchyard</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -10213,27 +10397,27 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>SC-034</t>
+          <t>DR-034</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>I&amp;C</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Earthing, lightning protection, cabling, cable trays</t>
+          <t>Turbine control system (TCS) for GT, ST, generators, HRSG protection (SIS)</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -10243,7 +10427,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="H38" s="5" t="n"/>
@@ -10251,17 +10435,17 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>SC-035</t>
+          <t>DR-035</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>I&amp;C</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Revenue metering and TSO SCADA/telecom interface</t>
+          <t>Plant DCS incl. HRSG and BOP control, operator stations</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -10284,16 +10468,12 @@
           <t>IEPC</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>TSO RTU interface in control building</t>
-        </is>
-      </c>
+      <c r="H39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>SC-036</t>
+          <t>DR-036</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -10303,7 +10483,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Plant DCS, historian, operator training simulator</t>
+          <t>CEMS</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -10331,7 +10511,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>SC-037</t>
+          <t>DR-037</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -10341,7 +10521,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Safety instrumented systems (burner management, HRSG protection) per IEC 61511</t>
+          <t>Vibration and performance monitoring, remote diagnostics</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -10369,17 +10549,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>SC-038</t>
+          <t>DR-038</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>I&amp;C</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Continuous emission monitoring system (CEMS)</t>
+          <t>Foundations of IEC equipment (GT, generators, ST, HRSG, condenser, GSUs)</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -10397,31 +10577,23 @@
           <t>IEPC</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>IEPC</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>Data link to environmental authority</t>
-        </is>
-      </c>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>SC-039</t>
+          <t>DR-039</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>I&amp;C</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Plant security, CCTV, access control, cybersecurity (IEC 62443)</t>
+          <t>Turbine hall(s), cranes, HRSG access structures beyond IEC platforms</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -10439,61 +10611,49 @@
           <t>IEPC</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>IEPC</t>
-        </is>
-      </c>
+      <c r="G43" s="4" t="n"/>
       <c r="H43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>SC-040</t>
+          <t>DR-040</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Transport, tests, training</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Piling, foundations, structures, turbine hall, HRSG structure</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>IEPC</t>
-        </is>
-      </c>
+          <t>Transport of IEC equipment to site (incl. heavy transport, barge, SPMT)</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>IEPC</t>
-        </is>
-      </c>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
       <c r="H44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>SC-041</t>
+          <t>DR-041</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Transport, tests, training</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Buildings: control, administration, workshop/warehouse, water treatment, gatehouse</t>
+          <t>Performance test</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -10501,67 +10661,59 @@
           <t>IEPC</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>IEPC</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>IEPC</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
       <c r="H45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>SC-042</t>
+          <t>DR-042</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Transport, tests, training</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Marine works for intake and outfall (dredging, pipes, heads)</t>
+          <t>Training of Owner staff on IEC equipment</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>IEPC</t>
-        </is>
-      </c>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>SC-043</t>
+          <t>SC-001</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Site</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Potable water connection at site boundary (no sewer available)</t>
+          <t>Land, access rights and site handover (levelled to +15.0 m)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -10582,24 +10734,24 @@
       <c r="G47" s="4" t="n"/>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Site boundary per land-use plan</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>SC-044</t>
+          <t>SC-002</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Site</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Telecommunication connection (fibre) to site boundary</t>
+          <t>Environmental Impact Assessment (EIA) positive decision</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -10612,32 +10764,24 @@
           <t>OWNER</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>OWNER</t>
-        </is>
-      </c>
+      <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+      <c r="H48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>SC-045</t>
+          <t>SC-003</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Site</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Construction power and water</t>
+          <t>Construction, operating and building permits (Contractor supplies all design inputs)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -10647,31 +10791,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>IEPC</t>
-        </is>
-      </c>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="n"/>
       <c r="G49" s="4" t="n"/>
       <c r="H49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>SC-046</t>
+          <t>SC-004</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Commissioning</t>
+          <t>Site</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Consumables until Taking-Over (except natural gas)</t>
+          <t>Geotechnical and topographic surveys (baseline supplied by Owner, confirmatory by Contractor)</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -10684,192 +10824,236 @@
           <t>IEPC</t>
         </is>
       </c>
-      <c r="F50" s="4" t="n"/>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
       <c r="G50" s="4" t="n"/>
       <c r="H50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>SC-047</t>
+          <t>SC-005</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Commissioning</t>
+          <t>Site</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Natural gas for commissioning and tests</t>
+          <t>Site preparation, fencing, roads, drainage, temporary facilities</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
+          <t>IEPC</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="n"/>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
       <c r="G51" s="4" t="n"/>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>Gas receiving station inlet</t>
-        </is>
-      </c>
+      <c r="H51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>SC-048</t>
+          <t>SC-006</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Commissioning</t>
+          <t>Power island</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Grid access for back-feed and test energy; purchase of test energy</t>
+          <t>Gas turbine package incl. auxiliaries, enclosure, inlet air filtration, exhaust diffuser</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="n"/>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="5" t="n"/>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>GT exhaust flange to HRSG inlet duct</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>SC-049</t>
+          <t>SC-007</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Commissioning</t>
+          <t>Power island</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Operation and maintenance staff for training and commissioning participation</t>
+          <t>GT generator incl. excitation, protection, cooling</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="n"/>
-      <c r="G53" s="4" t="n"/>
-      <c r="H53" s="5" t="n"/>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Generator terminals (IPB connection)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>SC-050</t>
+          <t>SC-008</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Spares</t>
+          <t>Power island</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Commissioning spares and special tools</t>
+          <t>Steam turbine (HP/IP/LP, reheat) incl. lube/control oil, gland steam, turning gear</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="n"/>
-      <c r="G54" s="4" t="n"/>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
       <c r="H54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>SC-051</t>
+          <t>SC-009</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Spares</t>
+          <t>Power island</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Two-year operating spares (priced list, Owner option)</t>
+          <t>ST generator incl. excitation, protection</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="n"/>
-      <c r="G55" s="4" t="n"/>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Owner's warehouse</t>
+          <t>Generator terminals</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>SC-052</t>
+          <t>SC-010</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Fuel oil</t>
+          <t>Power island</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>LDO truck unloading station (4 bays), storage tanks 2 x 50 %, bund, foam system</t>
+          <t>HRSG triple-pressure reheat, horizontal, natural circulation, with SCR and CO catalyst</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -10879,29 +11063,29 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>Tanker coupling at unloading bays</t>
+          <t>HRSG outlet to stack</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>SC-053</t>
+          <t>SC-011</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Fuel oil</t>
+          <t>Power island</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>LDO forwarding pumps, filters, metering, fuel treatment (2 x 100 % centrifugal separators)</t>
+          <t>Stack 60 m with CEMS platform and silencer</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -10924,16 +11108,12 @@
           <t>IEPC</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>GT liquid fuel skid inlet flange</t>
-        </is>
-      </c>
+      <c r="H57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>SC-054</t>
+          <t>SC-012</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -10943,7 +11123,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Dual-fuel GT combustion system, liquid fuel skid, water injection skid, purge system</t>
+          <t>Water-cooled condenser (seawater), vacuum system</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -10966,105 +11146,1697 @@
           <t>IEC</t>
         </is>
       </c>
-      <c r="H58" s="5" t="n"/>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Cooling water flanges at condenser water boxes</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>SC-055</t>
+          <t>SC-013</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Commissioning</t>
+          <t>Power island</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>LDO first fill of the storage tanks</t>
+          <t>Power island control system (TCS/ST controls) integrated in plant DCS</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
+          <t>IEC</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>OWNER</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="n"/>
-      <c r="G59" s="4" t="n"/>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Tanker coupling at unloading bays</t>
+          <t>DCS interface (redundant fibre)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>SC-056</t>
+          <t>SC-014</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Commissioning</t>
+          <t>Power island</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>LDO for tests beyond the first fill</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="n"/>
+          <t>GSU transformers (GT and ST), isolated phase busducts, generator circuit breakers</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>IEPC</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="n"/>
-      <c r="G60" s="4" t="n"/>
-      <c r="H60" s="5" t="n"/>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>GSU HV bushings</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
+          <t>SC-015</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Balance of plant</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Condensate and boiler feed water systems (pumps 2x100 %)</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>SC-016</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Balance of plant</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Seawater intake, screens, CW pumps (2x50 %), outfall and diffuser</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Offshore intake head / outfall diffuser</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>SC-017</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Balance of plant</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Electro-chlorination for biofouling control</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>SC-018</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Balance of plant</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Seawater reverse osmosis and demineralisation plant</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>SC-019</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Balance of plant</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Condensate polishing plant</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>SC-020</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Balance of plant</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Waste water treatment and effluent monitoring</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Discharge point to outfall</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>SC-021</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Balance of plant</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Closed cooling water system with plate heat exchangers</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>SC-022</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Balance of plant</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Compressed air (service and instrument) 2x100 %</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>SC-023</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Balance of plant</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Auxiliary boiler (gas-fired) for start-up steam</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>SC-024</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Balance of plant</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Fire detection and protection per NFPA 850</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>SC-025</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Balance of plant</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>HVAC for all buildings and electrical rooms</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>SC-026</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Balance of plant</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Cranes and hoists (turbine hall EOT crane)</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>SC-027</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Fuel gas</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Gas pipeline from national transmission system to plant boundary</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Owner valve at plant boundary (inlet flange of gas receiving station)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>SC-028</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Fuel gas</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Gas receiving and metering station (fiscal metering, filtration, heating, pressure control)</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>Inlet flange at plant boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>SC-029</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Fuel gas</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Performance gas heater and GT fuel skid</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>SC-030</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>380 kV GIS switchyard (double busbar) within plant boundary</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>380 kV line gantry / cable sealing ends</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>SC-031</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>380 kV transmission connection line and remote substation works</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Line gantry at switchyard</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>SC-032</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Unit auxiliary transformers, MV switchgear 10.5 kV, LV 0.4 kV distribution</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>SC-033</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Emergency diesel generator and UPS / DC systems</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>SC-034</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Earthing, lightning protection, cabling, cable trays</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>SC-035</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Revenue metering and TSO SCADA/telecom interface</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>TSO RTU interface in control building</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>SC-036</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>I&amp;C</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Plant DCS, historian, operator training simulator</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>SC-037</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>I&amp;C</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Safety instrumented systems (burner management, HRSG protection) per IEC 61511</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>SC-038</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>I&amp;C</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Continuous emission monitoring system (CEMS)</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>Data link to environmental authority</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>SC-039</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>I&amp;C</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Plant security, CCTV, access control, cybersecurity (IEC 62443)</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>SC-040</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Civil</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Piling, foundations, structures, turbine hall, HRSG structure</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="n"/>
+      <c r="H86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>SC-041</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Civil</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Buildings: control, administration, workshop/warehouse, water treatment, gatehouse</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="n"/>
+      <c r="H87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>SC-042</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Civil</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Marine works for intake and outfall (dredging, pipes, heads)</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="n"/>
+      <c r="H88" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>SC-043</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Potable water connection at site boundary (no sewer available)</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="n"/>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>SC-044</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Telecommunication connection (fibre) to site boundary</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="n"/>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>SC-045</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Construction power and water</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="n"/>
+      <c r="H91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>SC-046</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Commissioning</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Consumables until Taking-Over (except natural gas)</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="n"/>
+      <c r="G92" s="4" t="n"/>
+      <c r="H92" s="5" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>SC-047</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Commissioning</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Natural gas for commissioning and tests</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="n"/>
+      <c r="G93" s="4" t="n"/>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>Gas receiving station inlet</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>SC-048</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Commissioning</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Grid access for back-feed and test energy; purchase of test energy</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="n"/>
+      <c r="H94" s="5" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>SC-049</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Commissioning</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Operation and maintenance staff for training and commissioning participation</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="n"/>
+      <c r="G95" s="4" t="n"/>
+      <c r="H95" s="5" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>SC-050</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Spares</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Commissioning spares and special tools</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="n"/>
+      <c r="G96" s="4" t="n"/>
+      <c r="H96" s="5" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>SC-051</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Spares</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Two-year operating spares (priced list, Owner option)</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="n"/>
+      <c r="G97" s="4" t="n"/>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>Owner's warehouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>SC-052</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Fuel oil</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>LDO truck unloading station (4 bays), storage tanks 2 x 50 %, bund, foam system</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>Tanker coupling at unloading bays</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>SC-053</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Fuel oil</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>LDO forwarding pumps, filters, metering, fuel treatment (2 x 100 % centrifugal separators)</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>GT liquid fuel skid inlet flange</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>SC-054</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Power island</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Dual-fuel GT combustion system, liquid fuel skid, water injection skid, purge system</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>SC-055</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Commissioning</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>LDO first fill of the storage tanks</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="n"/>
+      <c r="G101" s="4" t="n"/>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>Tanker coupling at unloading bays</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>SC-056</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Commissioning</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>LDO for tests beyond the first fill</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="n"/>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="n"/>
+      <c r="G102" s="4" t="n"/>
+      <c r="H102" s="5" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
           <t>SC-057</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>Balance of plant</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
         <is>
           <t>Packaged sanitary wastewater treatment plant (biological + UV), discharge via outfall</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>IEPC</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>IEPC</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>IEPC</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>IEPC</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>IEPC</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
         <is>
           <t>Discharge into the outfall</t>
         </is>
@@ -11108,7 +12880,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T17:46:40Z by SETUP | data b226b6c9cd57c954</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T18:30:49Z by SETUP | data f8f7008e372ad5f4</t>
         </is>
       </c>
     </row>

--- a/output/requirements_matrix/ALP_requirements_matrix.xlsx
+++ b/output/requirements_matrix/ALP_requirements_matrix.xlsx
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T18:30:49Z by SETUP | data f8f7008e372ad5f4</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T18:48:59Z by SETUP | data 8e875a4b1e374b26</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7987,7 +7987,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T18:30:49Z by SETUP | data f8f7008e372ad5f4</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T18:48:59Z by SETUP | data 8e875a4b1e374b26</t>
         </is>
       </c>
     </row>
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5745</v>
+        <v>5735</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Condenser pressure at 16.0 degC seawater and 36,050 m3/h</t>
+          <t>Condenser pressure at 16.0 degC seawater, 36,050-38,000 m3/h (corrected to 36,050 m3/h)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -8261,12 +8261,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>PG-01</t>
+          <t>IG-07</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Net electrical output at Site Reference Conditions</t>
+          <t>Power island gross heat rate (LHV) at the GT load for 60 % plant net load</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -8275,49 +8275,33 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>600</v>
+        <v>6060</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>kJ/kWh</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>582</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>EUR per kW shortfall</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Below 97 % of the guaranteed value the Owner may reject the Works after the rectification period (Sub-Clause 12.5).</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>ER-04.01, ER-16.04</t>
-        </is>
-      </c>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>PG-02</t>
+          <t>PG-01</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Net heat rate (LHV) at Site Reference Conditions</t>
+          <t>Net electrical output at Site Reference Conditions</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -8326,49 +8310,49 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5860</v>
+        <v>600</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>kJ/kWh</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6035.8</v>
+        <v>582</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>400000</v>
+        <v>2200</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>EUR per kJ/kWh excess</t>
+          <t>EUR per kW shortfall</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Above 103 % of the guaranteed value the Owner may reject the Works after the rectification period.</t>
+          <t>Below 97 % of the guaranteed value the Owner may reject the Works after the rectification period (Sub-Clause 12.5).</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>ER-04.02</t>
+          <t>ER-04.01, ER-16.04</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>PG-03</t>
+          <t>PG-02</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Net heat rate (LHV) at 60 % plant load</t>
+          <t>Net heat rate (LHV) at Site Reference Conditions</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -8377,7 +8361,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6250</v>
+        <v>5860</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -8389,44 +8373,50 @@
           <t>max</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n"/>
+      <c r="G13" s="4" t="n">
+        <v>6035.8</v>
+      </c>
       <c r="H13" s="4" t="n">
-        <v>150000</v>
+        <v>400000</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
           <t>EUR per kJ/kWh excess</t>
         </is>
       </c>
-      <c r="J13" s="5" t="n"/>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Above 103 % of the guaranteed value the Owner may reject the Works after the rectification period.</t>
+        </is>
+      </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>ER-04.03</t>
+          <t>ER-04.02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>PG-04</t>
+          <t>PG-03</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>NOx emission (as NO2)</t>
+          <t>Net heat rate (LHV) at 60 % plant load</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>emissions</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>30</v>
+        <v>6250</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>mg/Nm3</t>
+          <t>kJ/kWh</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -8435,28 +8425,30 @@
         </is>
       </c>
       <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>No LD: the Contractor shall rectify at its cost until compliant; Taking-Over is not issued before compliance.</t>
-        </is>
-      </c>
+      <c r="H14" s="4" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>EUR per kJ/kWh excess</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="n"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>ER-06.03, ER-14.02, ER-16.05</t>
+          <t>ER-04.03</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>PG-05</t>
+          <t>PG-04</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>CO emission</t>
+          <t>NOx emission (as NO2)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -8482,20 +8474,24 @@
       <c r="I15" s="4" t="n"/>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Must rectify (as PG-04).</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr"/>
+          <t>No LD: the Contractor shall rectify at its cost until compliant; Taking-Over is not issued before compliance.</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>ER-06.03, ER-14.02, ER-16.05</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>PG-06</t>
+          <t>PG-05</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Ammonia slip from the SCR</t>
+          <t>CO emission</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -8504,7 +8500,7 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
@@ -8521,7 +8517,7 @@
       <c r="I16" s="4" t="n"/>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Must rectify.</t>
+          <t>Must rectify (as PG-04).</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
@@ -8529,25 +8525,25 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>PG-07</t>
+          <t>PG-06</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Near-field noise</t>
+          <t>Ammonia slip from the SCR</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>noise</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>dB(A)</t>
+          <t>mg/Nm3</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -8563,21 +8559,17 @@
           <t>Must rectify.</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>ER-14.03</t>
-        </is>
-      </c>
+      <c r="K17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>PG-08</t>
+          <t>PG-07</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Noise at nearest sensitive receptor (night)</t>
+          <t>Near-field noise</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -8586,7 +8578,7 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
@@ -8599,39 +8591,33 @@
         </is>
       </c>
       <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>EUR per dB(A) exceedance (after rectification attempts)</t>
-        </is>
-      </c>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Contractor to rectify first; LD only if rectification fails.</t>
+          <t>Must rectify.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>ER-14.04</t>
+          <t>ER-14.03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>PG-09</t>
+          <t>PG-08</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Hot start time to base load</t>
+          <t>Noise at nearest sensitive receptor (night)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>noise</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
@@ -8639,7 +8625,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>dB(A)</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -8649,29 +8635,33 @@
       </c>
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="4" t="n">
-        <v>20000</v>
+        <v>250000</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>EUR per minute exceedance</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="n"/>
+          <t>EUR per dB(A) exceedance (after rectification attempts)</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Contractor to rectify first; LD only if rectification fails.</t>
+        </is>
+      </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>ER-04.04, ER-16.06</t>
+          <t>ER-14.04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>PG-10</t>
+          <t>PG-09</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Load ramp rate in combined cycle</t>
+          <t>Hot start time to base load</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -8680,43 +8670,43 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>MW/min</t>
+          <t>min</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>max</t>
         </is>
       </c>
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="n">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>EUR per MW/min shortfall</t>
+          <t>EUR per minute exceedance</t>
         </is>
       </c>
       <c r="J20" s="5" t="n"/>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>ER-04.05</t>
+          <t>ER-04.04, ER-16.06</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>PG-11</t>
+          <t>PG-10</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Minimum environmental load</t>
+          <t>Load ramp rate in combined cycle</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -8725,104 +8715,106 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>% of plant net output</t>
+          <t>MW/min</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>EUR per percentage point exceedance</t>
+          <t>EUR per MW/min shortfall</t>
         </is>
       </c>
       <c r="J21" s="5" t="n"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>ER-04.06</t>
+          <t>ER-04.05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>PG-12</t>
+          <t>PG-11</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Reliability run availability</t>
+          <t>Minimum environmental load</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>reliability</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>% of plant net output</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>max</t>
         </is>
       </c>
       <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>Failed run to be repeated from the start after rectification.</t>
-        </is>
-      </c>
+      <c r="H22" s="4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>EUR per percentage point exceedance</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="n"/>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>ER-16.07</t>
+          <t>ER-04.06</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>PG-13</t>
+          <t>PG-12</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Condenser cooling water temperature rise</t>
+          <t>Reliability run availability</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>environmental</t>
+          <t>reliability</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G23" s="4" t="n"/>
@@ -8830,24 +8822,24 @@
       <c r="I23" s="4" t="n"/>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Must rectify (EIA permit condition).</t>
+          <t>Failed run to be repeated from the start after rectification.</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>ER-07.04</t>
+          <t>ER-16.07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>PG-14</t>
+          <t>PG-13</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Thermal plume at edge of mixing zone</t>
+          <t>Condenser cooling water temperature rise</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -8856,7 +8848,7 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -8878,66 +8870,62 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>ER-08.05</t>
+          <t>ER-07.04</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>PG-15</t>
+          <t>PG-14</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Net electrical output on LDO at Site Reference Conditions</t>
+          <t>Thermal plume at edge of mixing zone</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>environmental</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>560</v>
+        <v>3</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>K</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>543.2</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>800</v>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>EUR per kW shortfall</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="n"/>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Must rectify (EIA permit condition).</t>
+        </is>
+      </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>ER-16.08</t>
+          <t>ER-08.05</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>PG-16</t>
+          <t>PG-15</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Net heat rate (LHV) on LDO at Site Reference Conditions</t>
+          <t>Net electrical output on LDO at Site Reference Conditions</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -8946,54 +8934,58 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>6150</v>
+        <v>560</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>kJ/kWh</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6334.5</v>
+        <v>543.2</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>60000</v>
+        <v>800</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>EUR per kJ/kWh excess</t>
+          <t>EUR per kW shortfall</t>
         </is>
       </c>
       <c r="J26" s="5" t="n"/>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>ER-16.08</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>PG-17</t>
+          <t>PG-16</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>NOx emission on LDO (as NO2)</t>
+          <t>Net heat rate (LHV) on LDO at Site Reference Conditions</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>emissions</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>50</v>
+        <v>6150</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>mg/Nm3</t>
+          <t>kJ/kWh</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -9001,47 +8993,47 @@
           <t>max</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>No LD: the Contractor shall rectify until compliant (permit condition).</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>ER-03.11</t>
-        </is>
-      </c>
+      <c r="G27" s="4" t="n">
+        <v>6334.5</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>EUR per kJ/kWh excess</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>PG-18</t>
+          <t>PG-17</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Automatic fuel transfer gas to LDO without trip</t>
+          <t>NOx emission on LDO (as NO2)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>% successful transfers</t>
+          <t>mg/Nm3</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>max</t>
         </is>
       </c>
       <c r="G28" s="4" t="n"/>
@@ -9049,10 +9041,53 @@
       <c r="I28" s="4" t="n"/>
       <c r="J28" s="5" t="inlineStr">
         <is>
+          <t>No LD: the Contractor shall rectify until compliant (permit condition).</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>ER-03.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>PG-18</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Automatic fuel transfer gas to LDO without trip</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>% successful transfers</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
           <t>Must rectify; Taking-Over not issued before successful demonstration.</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>ER-03.10</t>
         </is>
@@ -9094,7 +9129,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T18:30:49Z by SETUP | data f8f7008e372ad5f4</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T18:48:59Z by SETUP | data 8e875a4b1e374b26</t>
         </is>
       </c>
     </row>
@@ -12880,7 +12915,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T18:30:49Z by SETUP | data f8f7008e372ad5f4</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T18:48:59Z by SETUP | data 8e875a4b1e374b26</t>
         </is>
       </c>
     </row>

--- a/output/requirements_matrix/ALP_requirements_matrix.xlsx
+++ b/output/requirements_matrix/ALP_requirements_matrix.xlsx
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T18:48:59Z by SETUP | data 8e875a4b1e374b26</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T03:17:05Z by SETUP | data 2b137c5df807778c</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,15 @@
 design_parameter/DP-CASE-0011
 design_parameter/DP-CASE-0012
 design_parameter/DP-CASE-0014
-hmb_case/SRC-NG-100</t>
+hmb_case/MAX-NG-100
+hmb_case/MIN-NG-100
+hmb_case/SRC-LDO-100
+hmb_case/SRC-NG-060
+hmb_case/SRC-NG-100
+hmb_case/SRC-NG-GT80
+hmb_case/SRC-NG-MEL
+hmb_case/SUM-NG-100
+hmb_case/WIN-NG-100</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1849,7 +1857,14 @@
 design_parameter/DP-CASE-0020
 design_parameter/DP-CASE-0021
 design_parameter/DP-OWNR-0024
-hmb_case/SRC-NG-100</t>
+hmb_case/MAX-NG-100
+hmb_case/MIN-NG-100
+hmb_case/SRC-NG-060
+hmb_case/SRC-NG-100
+hmb_case/SRC-NG-GT80
+hmb_case/SRC-NG-MEL
+hmb_case/SUM-NG-100
+hmb_case/WIN-NG-100</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -7961,7 +7976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7987,7 +8002,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T18:48:59Z by SETUP | data 8e875a4b1e374b26</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T03:17:05Z by SETUP | data 2b137c5df807778c</t>
         </is>
       </c>
     </row>
@@ -8296,63 +8311,47 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>PG-01</t>
+          <t>IG-08</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Net electrical output at Site Reference Conditions</t>
+          <t>GT minimum emissions-compliant load (natural gas)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>600</v>
+        <v>30</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>% GT load</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>582</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>EUR per kW shortfall</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>Below 97 % of the guaranteed value the Owner may reject the Works after the rectification period (Sub-Clause 12.5).</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>ER-04.01, ER-16.04</t>
-        </is>
-      </c>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>PG-02</t>
+          <t>IG-09</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Net heat rate (LHV) at Site Reference Conditions</t>
+          <t>Power island gross output on LDO at the generator terminals</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -8361,49 +8360,33 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5860</v>
+        <v>572</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>kJ/kWh</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>6035.8</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>400000</v>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>EUR per kJ/kWh excess</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>Above 103 % of the guaranteed value the Owner may reject the Works after the rectification period.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>ER-04.02</t>
-        </is>
-      </c>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>PG-03</t>
+          <t>IG-10</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Net heat rate (LHV) at 60 % plant load</t>
+          <t>Power island gross heat rate (LHV) on LDO</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -8412,7 +8395,7 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>6250</v>
+        <v>6020</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -8425,86 +8408,84 @@
         </is>
       </c>
       <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>EUR per kJ/kWh excess</t>
-        </is>
-      </c>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
       <c r="J14" s="5" t="n"/>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>ER-04.03</t>
-        </is>
-      </c>
+      <c r="K14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>PG-04</t>
+          <t>PG-01</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>NOx emission (as NO2)</t>
+          <t>Net electrical output at Site Reference Conditions</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>emissions</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>mg/Nm3</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>582</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>EUR per kW shortfall</t>
+        </is>
+      </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>No LD: the Contractor shall rectify at its cost until compliant; Taking-Over is not issued before compliance.</t>
+          <t>Below 97 % of the guaranteed value the Owner may reject the Works after the rectification period (Sub-Clause 12.5).</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>ER-06.03, ER-14.02, ER-16.05</t>
+          <t>ER-04.01, ER-16.04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>PG-05</t>
+          <t>PG-02</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>CO emission</t>
+          <t>Net heat rate (LHV) at Site Reference Conditions</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>emissions</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>30</v>
+        <v>5860</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>mg/Nm3</t>
+          <t>kJ/kWh</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -8512,38 +8493,50 @@
           <t>max</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
+      <c r="G16" s="4" t="n">
+        <v>6035.8</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>EUR per kJ/kWh excess</t>
+        </is>
+      </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Must rectify (as PG-04).</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr"/>
+          <t>Above 103 % of the guaranteed value the Owner may reject the Works after the rectification period.</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>ER-04.02</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>PG-06</t>
+          <t>PG-03</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Ammonia slip from the SCR</t>
+          <t>Net heat rate (LHV) at 60 % plant load</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>emissions</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5</v>
+        <v>6250</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>mg/Nm3</t>
+          <t>kJ/kWh</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -8552,37 +8545,43 @@
         </is>
       </c>
       <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>Must rectify.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>EUR per kJ/kWh excess</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>ER-04.03</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>PG-07</t>
+          <t>PG-04</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Near-field noise</t>
+          <t>NOx emission (as NO2)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>noise</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>dB(A)</t>
+          <t>mg/Nm3</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -8595,37 +8594,37 @@
       <c r="I18" s="4" t="n"/>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Must rectify.</t>
+          <t>No LD: the Contractor shall rectify at its cost until compliant; Taking-Over is not issued before compliance.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>ER-14.03</t>
+          <t>ER-06.03, ER-14.02, ER-16.05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>PG-08</t>
+          <t>PG-05</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Noise at nearest sensitive receptor (night)</t>
+          <t>CO emission</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>noise</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>dB(A)</t>
+          <t>mg/Nm3</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -8634,47 +8633,37 @@
         </is>
       </c>
       <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>EUR per dB(A) exceedance (after rectification attempts)</t>
-        </is>
-      </c>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Contractor to rectify first; LD only if rectification fails.</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>ER-14.04</t>
-        </is>
-      </c>
+          <t>Must rectify (as PG-04).</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>PG-09</t>
+          <t>PG-06</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Hot start time to base load</t>
+          <t>Ammonia slip from the SCR</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>mg/Nm3</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -8683,88 +8672,80 @@
         </is>
       </c>
       <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>EUR per minute exceedance</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>ER-04.04, ER-16.06</t>
-        </is>
-      </c>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Must rectify.</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>PG-10</t>
+          <t>PG-07</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Load ramp rate in combined cycle</t>
+          <t>Near-field noise</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>noise</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>MW/min</t>
+          <t>dB(A)</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>max</t>
         </is>
       </c>
       <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n">
-        <v>100000</v>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>EUR per MW/min shortfall</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Must rectify.</t>
+        </is>
+      </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>ER-04.05</t>
+          <t>ER-14.03</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>PG-11</t>
+          <t>PG-08</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Minimum environmental load</t>
+          <t>Noise at nearest sensitive receptor (night)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>noise</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>% of plant net output</t>
+          <t>dB(A)</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -8774,128 +8755,136 @@
       </c>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="4" t="n">
-        <v>300000</v>
+        <v>250000</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>EUR per percentage point exceedance</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="n"/>
+          <t>EUR per dB(A) exceedance (after rectification attempts)</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Contractor to rectify first; LD only if rectification fails.</t>
+        </is>
+      </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>ER-04.06</t>
+          <t>ER-14.04</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>PG-12</t>
+          <t>PG-09</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Reliability run availability</t>
+          <t>Hot start time to base load</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>reliability</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>min</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>max</t>
         </is>
       </c>
       <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>Failed run to be repeated from the start after rectification.</t>
-        </is>
-      </c>
+      <c r="H23" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>EUR per minute exceedance</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="n"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>ER-16.07</t>
+          <t>ER-04.04, ER-16.06</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>PG-13</t>
+          <t>PG-10</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Condenser cooling water temperature rise</t>
+          <t>Load ramp rate in combined cycle</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>environmental</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>MW/min</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>Must rectify (EIA permit condition).</t>
-        </is>
-      </c>
+      <c r="H24" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>EUR per MW/min shortfall</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="n"/>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>ER-07.04</t>
+          <t>ER-04.05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>PG-14</t>
+          <t>PG-11</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Thermal plume at edge of mixing zone</t>
+          <t>Minimum environmental load</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>environmental</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>% of plant net output</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -8904,41 +8893,43 @@
         </is>
       </c>
       <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>Must rectify (EIA permit condition).</t>
-        </is>
-      </c>
+      <c r="H25" s="4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>EUR per percentage point exceedance</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="n"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>ER-08.05</t>
+          <t>ER-04.06</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>PG-15</t>
+          <t>PG-12</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Net electrical output on LDO at Site Reference Conditions</t>
+          <t>Reliability run availability</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>reliability</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>560</v>
+        <v>98</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -8946,46 +8937,42 @@
           <t>min</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
-        <v>543.2</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>800</v>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>EUR per kW shortfall</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Failed run to be repeated from the start after rectification.</t>
+        </is>
+      </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>ER-16.08</t>
+          <t>ER-16.07</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>PG-16</t>
+          <t>PG-13</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Net heat rate (LHV) on LDO at Site Reference Conditions</t>
+          <t>Condenser cooling water temperature rise</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>environmental</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>6150</v>
+        <v>7</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>kJ/kWh</t>
+          <t>K</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -8993,42 +8980,42 @@
           <t>max</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
-        <v>6334.5</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>60000</v>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>EUR per kJ/kWh excess</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Must rectify (EIA permit condition).</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>ER-07.04</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>PG-17</t>
+          <t>PG-14</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>NOx emission on LDO (as NO2)</t>
+          <t>Thermal plume at edge of mixing zone</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>emissions</t>
+          <t>environmental</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>mg/Nm3</t>
+          <t>K</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -9041,53 +9028,186 @@
       <c r="I28" s="4" t="n"/>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>No LD: the Contractor shall rectify until compliant (permit condition).</t>
+          <t>Must rectify (EIA permit condition).</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>ER-03.11</t>
+          <t>ER-08.05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>PG-15</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Net electrical output on LDO at Site Reference Conditions</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>performance</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>560</v>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>543.2</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>800</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>EUR per kW shortfall</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>ER-16.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>PG-16</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Net heat rate (LHV) on LDO at Site Reference Conditions</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>performance</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>6150</v>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>kJ/kWh</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>6334.5</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>EUR per kJ/kWh excess</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>PG-17</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>NOx emission on LDO (as NO2)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>emissions</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>mg/Nm3</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>No LD: the Contractor shall rectify until compliant (permit condition).</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>ER-03.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
           <t>PG-18</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Automatic fuel transfer gas to LDO without trip</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>operational</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D32" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>% successful transfers</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Must rectify; Taking-Over not issued before successful demonstration.</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>ER-03.10</t>
         </is>
@@ -9129,7 +9249,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T18:48:59Z by SETUP | data 8e875a4b1e374b26</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T03:17:05Z by SETUP | data 2b137c5df807778c</t>
         </is>
       </c>
     </row>
@@ -12915,7 +13035,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-27T18:48:59Z by SETUP | data 8e875a4b1e374b26</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T03:17:05Z by SETUP | data 2b137c5df807778c</t>
         </is>
       </c>
     </row>

--- a/output/requirements_matrix/ALP_requirements_matrix.xlsx
+++ b/output/requirements_matrix/ALP_requirements_matrix.xlsx
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T03:17:05Z by SETUP | data 2b137c5df807778c</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T03:56:53Z by SETUP | data 5a092db99f236e4b</t>
         </is>
       </c>
     </row>
@@ -891,10 +891,14 @@
       <c r="G11" s="5" t="n"/>
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>permit/PMT-005</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1752,7 +1756,8 @@
       <c r="I28" s="4" t="inlineStr"/>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-OWNR-0045</t>
+          <t>design_parameter/DP-OWNR-0045
+permit/PMT-009</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -2172,7 +2177,8 @@
       <c r="I36" s="4" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-OWNR-0038</t>
+          <t>design_parameter/DP-OWNR-0038
+permit/PMT-015</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -3416,10 +3422,14 @@
       </c>
       <c r="H60" s="4" t="n"/>
       <c r="I60" s="4" t="inlineStr"/>
-      <c r="J60" s="5" t="inlineStr"/>
-      <c r="K60" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>permit/PMT-016</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -5107,10 +5117,14 @@
       </c>
       <c r="H95" s="4" t="n"/>
       <c r="I95" s="4" t="inlineStr"/>
-      <c r="J95" s="5" t="inlineStr"/>
-      <c r="K95" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>permit/PMT-020</t>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -5852,10 +5866,14 @@
       <c r="G111" s="5" t="n"/>
       <c r="H111" s="4" t="n"/>
       <c r="I111" s="4" t="inlineStr"/>
-      <c r="J111" s="5" t="inlineStr"/>
-      <c r="K111" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>permit/PMT-017</t>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -6366,10 +6384,14 @@
       </c>
       <c r="H122" s="4" t="n"/>
       <c r="I122" s="4" t="inlineStr"/>
-      <c r="J122" s="5" t="inlineStr"/>
-      <c r="K122" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>permit/PMT-018</t>
+        </is>
+      </c>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L122" s="4" t="inlineStr">
@@ -6603,10 +6625,14 @@
       <c r="G126" s="5" t="n"/>
       <c r="H126" s="4" t="n"/>
       <c r="I126" s="4" t="inlineStr"/>
-      <c r="J126" s="5" t="inlineStr"/>
-      <c r="K126" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t>permit/PMT-010</t>
+        </is>
+      </c>
+      <c r="K126" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L126" s="4" t="inlineStr">
@@ -6975,10 +7001,14 @@
       <c r="G134" s="5" t="n"/>
       <c r="H134" s="4" t="n"/>
       <c r="I134" s="4" t="inlineStr"/>
-      <c r="J134" s="5" t="inlineStr"/>
-      <c r="K134" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>permit/PMT-013</t>
+        </is>
+      </c>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L134" s="4" t="inlineStr">
@@ -7117,10 +7147,14 @@
       </c>
       <c r="H137" s="4" t="n"/>
       <c r="I137" s="4" t="inlineStr"/>
-      <c r="J137" s="5" t="inlineStr"/>
-      <c r="K137" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>permit/PMT-021</t>
+        </is>
+      </c>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -7229,10 +7263,14 @@
           <t>&lt;= 30 mg/Nm3</t>
         </is>
       </c>
-      <c r="J139" s="5" t="inlineStr"/>
-      <c r="K139" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J139" s="5" t="inlineStr">
+        <is>
+          <t>permit/PMT-019</t>
+        </is>
+      </c>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -7813,10 +7851,14 @@
       <c r="G151" s="5" t="n"/>
       <c r="H151" s="4" t="n"/>
       <c r="I151" s="4" t="inlineStr"/>
-      <c r="J151" s="5" t="inlineStr"/>
-      <c r="K151" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t>permit/PMT-004</t>
+        </is>
+      </c>
+      <c r="K151" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -7859,10 +7901,14 @@
       <c r="G152" s="5" t="n"/>
       <c r="H152" s="4" t="n"/>
       <c r="I152" s="4" t="inlineStr"/>
-      <c r="J152" s="5" t="inlineStr"/>
-      <c r="K152" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t>permit/PMT-014</t>
+        </is>
+      </c>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L152" s="4" t="inlineStr">
@@ -8002,7 +8048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T03:17:05Z by SETUP | data 2b137c5df807778c</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T03:56:53Z by SETUP | data 5a092db99f236e4b</t>
         </is>
       </c>
     </row>
@@ -9249,7 +9295,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T03:17:05Z by SETUP | data 2b137c5df807778c</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T03:56:53Z by SETUP | data 5a092db99f236e4b</t>
         </is>
       </c>
     </row>
@@ -13035,7 +13081,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T03:17:05Z by SETUP | data 2b137c5df807778c</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T03:56:53Z by SETUP | data 5a092db99f236e4b</t>
         </is>
       </c>
     </row>
@@ -13104,10 +13150,10 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -13274,10 +13320,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -13410,10 +13456,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F14" t="n">
         <v>7</v>
@@ -13478,10 +13524,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
@@ -13546,10 +13592,10 @@
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
@@ -13580,10 +13626,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -13614,10 +13660,10 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F20" t="n">
         <v>6</v>
@@ -13682,10 +13728,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -13713,10 +13759,10 @@
         <v>150</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>24.7</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/output/requirements_matrix/ALP_requirements_matrix.xlsx
+++ b/output/requirements_matrix/ALP_requirements_matrix.xlsx
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T03:56:53Z by SETUP | data 5a092db99f236e4b</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T04:17:36Z by SETUP | data a69e0245c2d18fe7</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T03:56:53Z by SETUP | data 5a092db99f236e4b</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T04:17:36Z by SETUP | data a69e0245c2d18fe7</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9295,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T03:56:53Z by SETUP | data 5a092db99f236e4b</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T04:17:36Z by SETUP | data a69e0245c2d18fe7</t>
         </is>
       </c>
     </row>
@@ -13081,7 +13081,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T03:56:53Z by SETUP | data 5a092db99f236e4b</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T04:17:36Z by SETUP | data a69e0245c2d18fe7</t>
         </is>
       </c>
     </row>

--- a/output/requirements_matrix/ALP_requirements_matrix.xlsx
+++ b/output/requirements_matrix/ALP_requirements_matrix.xlsx
@@ -54,7 +54,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -64,11 +64,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7D7"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -96,9 +91,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -493,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T04:17:36Z by SETUP | data a69e0245c2d18fe7</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T15:06:23Z by SETUP | data 7cb6f7f6cb17ec93</t>
         </is>
       </c>
     </row>
@@ -597,10 +589,14 @@
       </c>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-GE-DBR-0001</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -647,10 +643,14 @@
       </c>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-GE-DBR-0001</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -701,7 +701,9 @@
         <is>
           <t>design_parameter/DP-CASE-0034
 design_parameter/DP-CASE-0035
-design_parameter/DP-CASE-0036</t>
+design_parameter/DP-CASE-0036
+document/ALP-EPC-00000-GE-DBR-0001
+document/ALP-EPC-00000-PR-STU-0002</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -749,10 +751,14 @@
       <c r="G8" s="5" t="n"/>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-GE-DBR-0001</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -795,10 +801,14 @@
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="4" t="n"/>
       <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-GE-DBR-0001</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -845,10 +855,82 @@
       </c>
       <c r="H10" s="4" t="n"/>
       <c r="I10" s="4" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-GE-PRC-0001
+equipment/00ACA10
+equipment/00BBA10
+equipment/00BBA20
+equipment/00BFA10
+equipment/00BFA20
+equipment/00BFT10
+equipment/00BFT20
+equipment/00BMA10
+equipment/00BRA10
+equipment/00BTA10
+equipment/00CJA10
+equipment/00CQA10
+equipment/00EGA10
+equipment/00EGB10BB001
+equipment/00EGB10BB002
+equipment/00EGC10
+equipment/00EKA10
+equipment/00GBA10
+equipment/00GCA10
+equipment/00GHA10AP001
+equipment/00GHA10AP002
+equipment/00GHA10BB001
+equipment/00GHA10BB002
+equipment/00GKA10BB001
+equipment/00GNA10
+equipment/00GUA10
+equipment/00LDA10
+equipment/00PAA10AT001
+equipment/00PAA10AT002
+equipment/00PAC10AP001
+equipment/00PAC10AP002
+equipment/00PAH10
+equipment/00PBA10
+equipment/00PGA10AC001
+equipment/00PGA10AC002
+equipment/00PGA10AP001
+equipment/00PGA10AP002
+equipment/00PGA10BB001
+equipment/00QCA10
+equipment/00QEA10AN001
+equipment/00QEA10AN002
+equipment/00QEA10AT001
+equipment/00QEA10BB001
+equipment/00QHA10
+equipment/00QJA10
+equipment/00QJB10
+equipment/00QUA10
+equipment/00SAA10
+equipment/00SGA10AP001
+equipment/00SGA10AP002
+equipment/00SGA10AP003
+equipment/00SGA10BB001
+equipment/00SMA10
+equipment/00SMA20
+equipment/00XJA10
+equipment/10BBT10
+equipment/10HAN10BB001
+equipment/10HAN10BB002
+equipment/10HNE10
+equipment/10HSB10AP001
+equipment/10HSB10AP002
+equipment/10HSB10BB001
+equipment/10HSB10BB002
+equipment/10LAC10AP001
+equipment/10LAC10AP002
+equipment/20BBT10
+equipment/20LCB10AP001
+equipment/20LCB10AP002</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -893,7 +975,8 @@
       <c r="I11" s="4" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>permit/PMT-005</t>
+          <t>document/ALP-EPC-00000-GE-LST-0001
+permit/PMT-005</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -945,10 +1028,14 @@
       </c>
       <c r="H12" s="4" t="n"/>
       <c r="I12" s="4" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-10MBA-ME-DSH-0001</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -991,10 +1078,14 @@
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-GE-PLN-0001</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1041,10 +1132,14 @@
       </c>
       <c r="H14" s="4" t="n"/>
       <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-GE-PRC-0003</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1090,7 +1185,8 @@
       <c r="J15" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-CASE-0001
-design_parameter/DP-OWNR-0044</t>
+design_parameter/DP-OWNR-0044
+document/ALP-EPC-00000-GE-DBR-0001</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1142,7 +1238,8 @@
         <is>
           <t>design_parameter/DP-CASE-0007
 design_parameter/DP-CASE-0008
-design_parameter/DP-CASE-0009</t>
+design_parameter/DP-CASE-0009
+document/ALP-EPC-00000-GE-DBR-0001</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -1196,6 +1293,7 @@
 design_parameter/DP-CASE-0011
 design_parameter/DP-CASE-0012
 design_parameter/DP-CASE-0014
+document/ALP-EPC-00000-GE-DBR-0001
 hmb_case/MAX-NG-100
 hmb_case/MIN-NG-100
 hmb_case/SRC-LDO-100
@@ -1254,7 +1352,8 @@
       <c r="I18" s="4" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0013</t>
+          <t>design_parameter/DP-CASE-0013
+document/ALP-EPC-00PAA-PR-SDS-0001</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
@@ -1306,7 +1405,8 @@
         <is>
           <t>design_parameter/DP-CASE-0004
 design_parameter/DP-CASE-0005
-design_parameter/DP-CASE-0006</t>
+design_parameter/DP-CASE-0006
+document/ALP-EPC-00000-GE-DBR-0001</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1360,7 +1460,8 @@
       <c r="I20" s="4" t="inlineStr"/>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0002</t>
+          <t>design_parameter/DP-CASE-0002
+document/ALP-EPC-00000-CV-DBR-0001</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1408,10 +1509,14 @@
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-CV-RPT-0001</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1456,7 +1561,8 @@
       <c r="I22" s="4" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0003</t>
+          <t>design_parameter/DP-CASE-0003
+document/ALP-EPC-00000-ME-SPC-0002</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -1504,10 +1610,14 @@
       <c r="G23" s="5" t="n"/>
       <c r="H23" s="4" t="n"/>
       <c r="I23" s="4" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00UZC-CV-CVL-0001</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1558,7 +1668,8 @@
         <is>
           <t>design_parameter/DP-OWNR-0005
 design_parameter/DP-OWNR-0007
-design_parameter/DP-OWNR-0008</t>
+design_parameter/DP-OWNR-0008
+document/ALP-EPC-00ACA-EL-SPC-0001</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -1610,7 +1721,8 @@
         <is>
           <t>design_parameter/DP-OWNR-0001
 design_parameter/DP-OWNR-0002
-design_parameter/DP-OWNR-0010</t>
+design_parameter/DP-OWNR-0010
+document/ALP-EPC-00000-GE-DBR-0001</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -1660,7 +1772,8 @@
       <c r="I26" s="4" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-OWNR-0009</t>
+          <t>design_parameter/DP-OWNR-0009
+document/ALP-EPC-00000-EL-STU-0004</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -1708,10 +1821,14 @@
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="4" t="n"/>
       <c r="I27" s="4" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00UZC-CV-CVL-0001</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -1757,6 +1874,7 @@
       <c r="J28" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-OWNR-0045
+document/ALP-EPC-00000-ME-STU-0001
 permit/PMT-009</t>
         </is>
       </c>
@@ -1805,10 +1923,14 @@
       <c r="G29" s="5" t="n"/>
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="4" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-GE-DBR-0001</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -1835,7 +1957,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>The plant shall operate on the full natural gas range of ALP-OWN-FUL-001 sections 2 to 4: CH4 85.0 to 98.5 mol %, C2H6 up to 7.0 %, C3H8 up to 2.5 %, C4 up to 1.0 %, C5+ up to 0.2 %, N2 up to 4.0 %, CO2 up to 2.5 %, O2 up to 0.02 %; LHV 44.2 MJ/kg to 50.0 MJ/kg (emission limits apply over the whole range; performance guarantees at the reference gas); Wobbe index (GCV) 47.2 MJ/Sm3 to 51.8 MJ/Sm3 with rate of change up to 1 %/min. Hydrogen admixture up to 5 vol % without modification and with all guarantees; provisions for 10 vol % by future OEM retrofit (fuel system materials, gas detection, control system capacity). Reference composition for guarantees: CH4 93.0, C2H6 3.5, C3H8 0.8, i-C4 0.15, n-C4 0.15, C5+ 0.05, N2 1.55, CO2 0.8 mol %; LHV 48.4 MJ/kg.</t>
+          <t>The plant shall operate on the full natural gas range of ALP-OWN-FUL-001 sections 2 to 4: CH4 85.0 to 98.5 mol %, C2H6 up to 7.0 %, C3H8 up to 2.5 %, C4 up to 1.0 %, C5+ up to 0.2 %, N2 up to 4.0 %, CO2 up to 2.5 %, O2 up to 0.02 %; LHV 44.2 MJ/kg to 50.0 MJ/kg (emission limits apply over the whole range; performance guarantees at the reference gas); Wobbe index (GCV) 47.2 MJ/Sm3 to 51.8 MJ/Sm3 with rate of change up to 1 %/min. Hydrogen admixture up to 5 vol % without modification and with all guarantees; provisions for 10 vol % by future OEM retrofit (fuel system materials, gas detection, control system capacity). Reference composition for guarantees: CH4 93.0, C2H6 3.5, C3H8 0.8, i-C4 0.15, n-C4 0.15, C5+ 0.05, N2 1.55, CO2 0.8 mol %; LHV 47.48 MJ/kg (ISO 6976, combustion reference 25 degC, from the reference composition; 34.78 MJ/Sm3 at 15 degC).</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1862,6 +1984,7 @@
 design_parameter/DP-CASE-0020
 design_parameter/DP-CASE-0021
 design_parameter/DP-OWNR-0024
+document/ALP-EPC-00000-PR-HMB-0001
 hmb_case/MAX-NG-100
 hmb_case/MIN-NG-100
 hmb_case/SRC-NG-060
@@ -1920,7 +2043,8 @@
       <c r="J31" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-CASE-0022
-design_parameter/DP-CASE-0023</t>
+design_parameter/DP-CASE-0023
+document/ALP-EPC-00EKA-PR-SDS-0001</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -1968,10 +2092,14 @@
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="4" t="n"/>
       <c r="I32" s="4" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00EKA-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2014,10 +2142,14 @@
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="4" t="n"/>
       <c r="I33" s="4" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-10MBA-PR-PID-0001</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2070,7 +2202,8 @@
 design_parameter/DP-OWNR-0026
 design_parameter/DP-OWNR-0027
 design_parameter/DP-OWNR-0028
-design_parameter/DP-OWNR-0029</t>
+design_parameter/DP-OWNR-0029
+document/ALP-EPC-00EKA-ME-SPC-0001</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -2127,7 +2260,8 @@
           <t>design_parameter/DP-OWNR-0034
 design_parameter/DP-OWNR-0035
 design_parameter/DP-OWNR-0036
-design_parameter/DP-OWNR-0037</t>
+design_parameter/DP-OWNR-0037
+document/ALP-EPC-00EGC-PR-SDS-0001</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -2178,6 +2312,7 @@
       <c r="J36" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-OWNR-0038
+document/ALP-EPC-00EGB-PR-SDS-0001
 permit/PMT-015</t>
         </is>
       </c>
@@ -2226,10 +2361,14 @@
       <c r="G37" s="5" t="n"/>
       <c r="H37" s="4" t="n"/>
       <c r="I37" s="4" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr"/>
-      <c r="K37" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00EGC-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2284,10 +2423,14 @@
           <t>&gt;= 100 % successful transfers</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr"/>
-      <c r="K38" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-IC-CNR-0001</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2338,10 +2481,14 @@
           <t>&lt;= 50 mg/Nm3</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-10MBA-PR-PID-0001</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -2398,7 +2545,8 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0028</t>
+          <t>design_parameter/DP-CASE-0028
+document/ALP-EPC-00000-PR-CAL-0001</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -2460,7 +2608,8 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0029</t>
+          <t>design_parameter/DP-CASE-0029
+document/ALP-EPC-00000-PR-CAL-0001</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -2522,7 +2671,8 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0030</t>
+          <t>design_parameter/DP-CASE-0030
+document/ALP-EPC-00000-PR-CAL-0001</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -2586,7 +2736,8 @@
         <is>
           <t>design_parameter/DP-CASE-0037
 design_parameter/DP-CASE-0038
-design_parameter/DP-CASE-0039</t>
+design_parameter/DP-CASE-0039
+document/ALP-IEC-10MBY-IC-CNR-0001</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
@@ -2648,7 +2799,8 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0032</t>
+          <t>design_parameter/DP-CASE-0032
+document/ALP-IEC-10MBY-IC-CNR-0001</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
@@ -2710,7 +2862,8 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0033</t>
+          <t>design_parameter/DP-CASE-0033
+document/ALP-EPC-00000-PR-HMB-0001</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
@@ -2764,7 +2917,8 @@
       <c r="I46" s="4" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0026</t>
+          <t>design_parameter/DP-CASE-0026
+document/ALP-EPC-00000-EL-STU-0006</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
@@ -2814,7 +2968,8 @@
       <c r="I47" s="4" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0027</t>
+          <t>design_parameter/DP-CASE-0027
+document/ALP-EPC-00000-EL-STU-0006</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
@@ -2862,10 +3017,14 @@
       <c r="G48" s="5" t="n"/>
       <c r="H48" s="4" t="n"/>
       <c r="I48" s="4" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-IC-CNR-0001</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -2910,7 +3069,8 @@
       <c r="I49" s="4" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0031</t>
+          <t>design_parameter/DP-CASE-0031
+document/ALP-EPC-00000-EL-LST-0001</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -2958,10 +3118,14 @@
       <c r="G50" s="5" t="n"/>
       <c r="H50" s="4" t="n"/>
       <c r="I50" s="4" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr"/>
-      <c r="K50" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-PR-CAL-0001</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3004,10 +3168,14 @@
       <c r="G51" s="5" t="n"/>
       <c r="H51" s="4" t="n"/>
       <c r="I51" s="4" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr"/>
-      <c r="K51" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-PR-STU-0002</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -3050,10 +3218,14 @@
       <c r="G52" s="5" t="n"/>
       <c r="H52" s="4" t="n"/>
       <c r="I52" s="4" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr"/>
-      <c r="K52" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-10MBA-ME-DSH-0001</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3096,10 +3268,14 @@
       <c r="G53" s="5" t="n"/>
       <c r="H53" s="4" t="n"/>
       <c r="I53" s="4" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr"/>
-      <c r="K53" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-10MBA-PR-PID-0001</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3142,10 +3318,14 @@
       <c r="G54" s="5" t="n"/>
       <c r="H54" s="4" t="n"/>
       <c r="I54" s="4" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr"/>
-      <c r="K54" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-10MBA-ME-DSH-0001</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3188,10 +3368,14 @@
       <c r="G55" s="5" t="n"/>
       <c r="H55" s="4" t="n"/>
       <c r="I55" s="4" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr"/>
-      <c r="K55" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-10MBA-ME-DSH-0001</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -3234,10 +3418,14 @@
       <c r="G56" s="5" t="n"/>
       <c r="H56" s="4" t="n"/>
       <c r="I56" s="4" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr"/>
-      <c r="K56" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-10MBA-PR-PID-0001</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3280,10 +3468,14 @@
       <c r="G57" s="5" t="n"/>
       <c r="H57" s="4" t="n"/>
       <c r="I57" s="4" t="inlineStr"/>
-      <c r="J57" s="5" t="inlineStr"/>
-      <c r="K57" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-10MBY-IC-BLK-0001</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -3310,7 +3502,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Hot gas path inspection interval shall be not less than 25,000 EOH and major inspection not less than 50,000 EOH at the operating regime of ER-01.03.</t>
+          <t>Hot gas path inspection interval shall be not less than 25,000 EOH and major inspection not less than 50,000 EOH at the operating regime of ER-01.03. Intervals are counted in equivalent operating hours with the OEM start and trip factors (TQ-IEC-010); no calendar interval applies.</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -3326,10 +3518,14 @@
       <c r="G58" s="5" t="n"/>
       <c r="H58" s="4" t="n"/>
       <c r="I58" s="4" t="inlineStr"/>
-      <c r="J58" s="5" t="inlineStr"/>
-      <c r="K58" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-10MBA-ME-DSH-0001</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3372,10 +3568,14 @@
       <c r="G59" s="5" t="n"/>
       <c r="H59" s="4" t="n"/>
       <c r="I59" s="4" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr"/>
-      <c r="K59" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-10HAA-ME-DSH-0001</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3424,7 +3624,8 @@
       <c r="I60" s="4" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>permit/PMT-016</t>
+          <t>document/ALP-IEC-10HAA-ME-DSH-0001
+permit/PMT-016</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -3480,10 +3681,14 @@
           <t>&lt;= 30 mg/Nm3</t>
         </is>
       </c>
-      <c r="J61" s="5" t="inlineStr"/>
-      <c r="K61" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-10HAA-PR-PID-0001</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -3510,7 +3715,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Aqueous ammonia storage (2x7 days at base load), unloading, vaporisation and dosing with leak detection and bunding.</t>
+          <t>Aqueous ammonia (24.5 %) storage in 2 tanks, each for 7 days at base load on natural gas, together covering 72 h of LDO operation (2 x 30 m3), unloading from road tankers, vaporisation and dosing with leak detection and bunding (TQ-034).</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -3526,10 +3731,14 @@
       <c r="G62" s="5" t="n"/>
       <c r="H62" s="4" t="n"/>
       <c r="I62" s="4" t="inlineStr"/>
-      <c r="J62" s="5" t="inlineStr"/>
-      <c r="K62" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-10HSB-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3572,10 +3781,14 @@
       <c r="G63" s="5" t="n"/>
       <c r="H63" s="4" t="n"/>
       <c r="I63" s="4" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr"/>
-      <c r="K63" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-10HAA-ME-DSH-0001</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -3620,7 +3833,8 @@
       <c r="I64" s="4" t="inlineStr"/>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0043</t>
+          <t>design_parameter/DP-CASE-0043
+document/ALP-EPC-10HNE-SS-SPC-0001</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
@@ -3668,10 +3882,14 @@
       <c r="G65" s="5" t="n"/>
       <c r="H65" s="4" t="n"/>
       <c r="I65" s="4" t="inlineStr"/>
-      <c r="J65" s="5" t="inlineStr"/>
-      <c r="K65" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-10HAN-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -3714,10 +3932,14 @@
       <c r="G66" s="5" t="n"/>
       <c r="H66" s="4" t="n"/>
       <c r="I66" s="4" t="inlineStr"/>
-      <c r="J66" s="5" t="inlineStr"/>
-      <c r="K66" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00QJA-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -3760,10 +3982,14 @@
       <c r="G67" s="5" t="n"/>
       <c r="H67" s="4" t="n"/>
       <c r="I67" s="4" t="inlineStr"/>
-      <c r="J67" s="5" t="inlineStr"/>
-      <c r="K67" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-20MAA-ME-DSH-0001</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -3806,10 +4032,14 @@
       <c r="G68" s="5" t="n"/>
       <c r="H68" s="4" t="n"/>
       <c r="I68" s="4" t="inlineStr"/>
-      <c r="J68" s="5" t="inlineStr"/>
-      <c r="K68" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-20MAA-ME-DSH-0001</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -3852,10 +4082,14 @@
       <c r="G69" s="5" t="n"/>
       <c r="H69" s="4" t="n"/>
       <c r="I69" s="4" t="inlineStr"/>
-      <c r="J69" s="5" t="inlineStr"/>
-      <c r="K69" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00PAH-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -3912,7 +4146,8 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0015</t>
+          <t>design_parameter/DP-CASE-0015
+document/ALP-IEC-20MAG-ME-DSH-0001</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -3960,10 +4195,14 @@
       <c r="G71" s="5" t="n"/>
       <c r="H71" s="4" t="n"/>
       <c r="I71" s="4" t="inlineStr"/>
-      <c r="J71" s="5" t="inlineStr"/>
-      <c r="K71" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-20MAA-PR-PID-0001</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4006,10 +4245,14 @@
       <c r="G72" s="5" t="n"/>
       <c r="H72" s="4" t="n"/>
       <c r="I72" s="4" t="inlineStr"/>
-      <c r="J72" s="5" t="inlineStr"/>
-      <c r="K72" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-20MAA-PR-PID-0001</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
@@ -4059,7 +4302,8 @@
       <c r="J73" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-OWNR-0022
-design_parameter/DP-OWNR-0023</t>
+design_parameter/DP-OWNR-0023
+document/ALP-IEC-20MAG-ME-DSH-0001</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
@@ -4113,7 +4357,8 @@
       <c r="I74" s="4" t="inlineStr"/>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-OWNR-0021</t>
+          <t>design_parameter/DP-OWNR-0021
+document/ALP-IEC-20MAG-ME-DSH-0001</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
@@ -4161,10 +4406,14 @@
       <c r="G75" s="5" t="n"/>
       <c r="H75" s="4" t="n"/>
       <c r="I75" s="4" t="inlineStr"/>
-      <c r="J75" s="5" t="inlineStr"/>
-      <c r="K75" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-20MAN-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -4207,10 +4456,14 @@
       <c r="G76" s="5" t="n"/>
       <c r="H76" s="4" t="n"/>
       <c r="I76" s="4" t="inlineStr"/>
-      <c r="J76" s="5" t="inlineStr"/>
-      <c r="K76" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00QUA-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -4253,10 +4506,14 @@
       <c r="G77" s="5" t="n"/>
       <c r="H77" s="4" t="n"/>
       <c r="I77" s="4" t="inlineStr"/>
-      <c r="J77" s="5" t="inlineStr"/>
-      <c r="K77" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00PAC-ME-CAL-0001</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -4299,10 +4556,14 @@
       <c r="G78" s="5" t="n"/>
       <c r="H78" s="4" t="n"/>
       <c r="I78" s="4" t="inlineStr"/>
-      <c r="J78" s="5" t="inlineStr"/>
-      <c r="K78" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00PAB-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
@@ -4345,10 +4606,14 @@
       <c r="G79" s="5" t="n"/>
       <c r="H79" s="4" t="n"/>
       <c r="I79" s="4" t="inlineStr"/>
-      <c r="J79" s="5" t="inlineStr"/>
-      <c r="K79" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00PAA-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -4391,10 +4656,14 @@
       <c r="G80" s="5" t="n"/>
       <c r="H80" s="4" t="n"/>
       <c r="I80" s="4" t="inlineStr"/>
-      <c r="J80" s="5" t="inlineStr"/>
-      <c r="K80" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00PAC-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -4443,7 +4712,8 @@
       <c r="I81" s="4" t="inlineStr"/>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0017</t>
+          <t>design_parameter/DP-CASE-0017
+document/ALP-EPC-00PBA-PR-SDS-0001</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
@@ -4505,7 +4775,8 @@
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0016</t>
+          <t>design_parameter/DP-CASE-0016
+document/ALP-EPC-00000-PR-STU-0003</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
@@ -4553,10 +4824,14 @@
       <c r="G83" s="5" t="n"/>
       <c r="H83" s="4" t="n"/>
       <c r="I83" s="4" t="inlineStr"/>
-      <c r="J83" s="5" t="inlineStr"/>
-      <c r="K83" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00PGA-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -4601,7 +4876,8 @@
       <c r="I84" s="4" t="inlineStr"/>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-OWNR-0019</t>
+          <t>design_parameter/DP-OWNR-0019
+document/ALP-EPC-00PAA-PR-SDS-0001</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
@@ -4649,10 +4925,14 @@
       <c r="G85" s="5" t="n"/>
       <c r="H85" s="4" t="n"/>
       <c r="I85" s="4" t="inlineStr"/>
-      <c r="J85" s="5" t="inlineStr"/>
-      <c r="K85" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00GBA-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -4695,10 +4975,14 @@
       <c r="G86" s="5" t="n"/>
       <c r="H86" s="4" t="n"/>
       <c r="I86" s="4" t="inlineStr"/>
-      <c r="J86" s="5" t="inlineStr"/>
-      <c r="K86" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00GCA-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -4741,10 +5025,14 @@
       <c r="G87" s="5" t="n"/>
       <c r="H87" s="4" t="n"/>
       <c r="I87" s="4" t="inlineStr"/>
-      <c r="J87" s="5" t="inlineStr"/>
-      <c r="K87" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-PR-RPT-0001</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -4787,10 +5075,14 @@
       <c r="G88" s="5" t="n"/>
       <c r="H88" s="4" t="n"/>
       <c r="I88" s="4" t="inlineStr"/>
-      <c r="J88" s="5" t="inlineStr"/>
-      <c r="K88" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00LDA-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -4837,10 +5129,14 @@
       </c>
       <c r="H89" s="4" t="n"/>
       <c r="I89" s="4" t="inlineStr"/>
-      <c r="J89" s="5" t="inlineStr"/>
-      <c r="K89" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00GNA-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -4883,10 +5179,14 @@
       <c r="G90" s="5" t="n"/>
       <c r="H90" s="4" t="n"/>
       <c r="I90" s="4" t="inlineStr"/>
-      <c r="J90" s="5" t="inlineStr"/>
-      <c r="K90" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00UZC-CV-CVL-0001</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -4929,10 +5229,14 @@
       <c r="G91" s="5" t="n"/>
       <c r="H91" s="4" t="n"/>
       <c r="I91" s="4" t="inlineStr"/>
-      <c r="J91" s="5" t="inlineStr"/>
-      <c r="K91" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-10LAC-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -4975,10 +5279,14 @@
       <c r="G92" s="5" t="n"/>
       <c r="H92" s="4" t="n"/>
       <c r="I92" s="4" t="inlineStr"/>
-      <c r="J92" s="5" t="inlineStr"/>
-      <c r="K92" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-20LCB-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -5021,10 +5329,14 @@
       <c r="G93" s="5" t="n"/>
       <c r="H93" s="4" t="n"/>
       <c r="I93" s="4" t="inlineStr"/>
-      <c r="J93" s="5" t="inlineStr"/>
-      <c r="K93" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00QEA-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -5067,10 +5379,14 @@
       <c r="G94" s="5" t="n"/>
       <c r="H94" s="4" t="n"/>
       <c r="I94" s="4" t="inlineStr"/>
-      <c r="J94" s="5" t="inlineStr"/>
-      <c r="K94" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00QHA-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
@@ -5119,7 +5435,9 @@
       <c r="I95" s="4" t="inlineStr"/>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>permit/PMT-020</t>
+          <t>document/ALP-EPC-00000-HS-HAZ-0009
+document/ALP-EPC-00SGA-PR-SDS-0001
+permit/PMT-020</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
@@ -5167,10 +5485,14 @@
       <c r="G96" s="5" t="n"/>
       <c r="H96" s="4" t="n"/>
       <c r="I96" s="4" t="inlineStr"/>
-      <c r="J96" s="5" t="inlineStr"/>
-      <c r="K96" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00SAA-HV-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
@@ -5213,10 +5535,14 @@
       <c r="G97" s="5" t="n"/>
       <c r="H97" s="4" t="n"/>
       <c r="I97" s="4" t="inlineStr"/>
-      <c r="J97" s="5" t="inlineStr"/>
-      <c r="K97" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00SMA-ME-SPC-0001</t>
+        </is>
+      </c>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -5259,10 +5585,14 @@
       <c r="G98" s="5" t="n"/>
       <c r="H98" s="4" t="n"/>
       <c r="I98" s="4" t="inlineStr"/>
-      <c r="J98" s="5" t="inlineStr"/>
-      <c r="K98" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00QJA-PR-SDS-0001</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -5308,7 +5638,8 @@
       <c r="J99" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-CASE-0024
-design_parameter/DP-CASE-0025</t>
+design_parameter/DP-CASE-0025
+document/ALP-EPC-00ACA-EL-SPC-0001</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
@@ -5356,10 +5687,14 @@
       <c r="G100" s="5" t="n"/>
       <c r="H100" s="4" t="n"/>
       <c r="I100" s="4" t="inlineStr"/>
-      <c r="J100" s="5" t="inlineStr"/>
-      <c r="K100" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-10MKA-EL-DSH-0001</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
@@ -5402,10 +5737,14 @@
       <c r="G101" s="5" t="n"/>
       <c r="H101" s="4" t="n"/>
       <c r="I101" s="4" t="inlineStr"/>
-      <c r="J101" s="5" t="inlineStr"/>
-      <c r="K101" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-10BAT-EL-DSH-0001</t>
+        </is>
+      </c>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -5448,10 +5787,14 @@
       <c r="G102" s="5" t="n"/>
       <c r="H102" s="4" t="n"/>
       <c r="I102" s="4" t="inlineStr"/>
-      <c r="J102" s="5" t="inlineStr"/>
-      <c r="K102" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00BBA-EL-SLD-0001</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -5494,10 +5837,14 @@
       <c r="G103" s="5" t="n"/>
       <c r="H103" s="4" t="n"/>
       <c r="I103" s="4" t="inlineStr"/>
-      <c r="J103" s="5" t="inlineStr"/>
-      <c r="K103" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00XJA-EL-SPC-0001</t>
+        </is>
+      </c>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -5540,10 +5887,14 @@
       <c r="G104" s="5" t="n"/>
       <c r="H104" s="4" t="n"/>
       <c r="I104" s="4" t="inlineStr"/>
-      <c r="J104" s="5" t="inlineStr"/>
-      <c r="K104" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J104" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-EL-STU-0002</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -5586,10 +5937,14 @@
       <c r="G105" s="5" t="n"/>
       <c r="H105" s="4" t="n"/>
       <c r="I105" s="4" t="inlineStr"/>
-      <c r="J105" s="5" t="inlineStr"/>
-      <c r="K105" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-EL-STU-0003</t>
+        </is>
+      </c>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -5632,10 +5987,14 @@
       <c r="G106" s="5" t="n"/>
       <c r="H106" s="4" t="n"/>
       <c r="I106" s="4" t="inlineStr"/>
-      <c r="J106" s="5" t="inlineStr"/>
-      <c r="K106" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-EL-SPC-0001</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
@@ -5678,10 +6037,14 @@
       <c r="G107" s="5" t="n"/>
       <c r="H107" s="4" t="n"/>
       <c r="I107" s="4" t="inlineStr"/>
-      <c r="J107" s="5" t="inlineStr"/>
-      <c r="K107" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-EL-SPC-0003</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -5724,10 +6087,14 @@
       <c r="G108" s="5" t="n"/>
       <c r="H108" s="4" t="n"/>
       <c r="I108" s="4" t="inlineStr"/>
-      <c r="J108" s="5" t="inlineStr"/>
-      <c r="K108" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00CJA-IC-BLK-0001</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
@@ -5770,10 +6137,14 @@
       <c r="G109" s="5" t="n"/>
       <c r="H109" s="4" t="n"/>
       <c r="I109" s="4" t="inlineStr"/>
-      <c r="J109" s="5" t="inlineStr"/>
-      <c r="K109" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-IC-DBR-0001</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -5820,10 +6191,14 @@
       </c>
       <c r="H110" s="4" t="n"/>
       <c r="I110" s="4" t="inlineStr"/>
-      <c r="J110" s="5" t="inlineStr"/>
-      <c r="K110" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-HS-HAZ-0007</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L110" s="4" t="inlineStr">
@@ -5868,7 +6243,8 @@
       <c r="I111" s="4" t="inlineStr"/>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>permit/PMT-017</t>
+          <t>document/ALP-EPC-00CQA-IC-SPC-0001
+permit/PMT-017</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
@@ -5916,10 +6292,14 @@
       <c r="G112" s="5" t="n"/>
       <c r="H112" s="4" t="n"/>
       <c r="I112" s="4" t="inlineStr"/>
-      <c r="J112" s="5" t="inlineStr"/>
-      <c r="K112" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00CKA-IC-BLK-0001</t>
+        </is>
+      </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L112" s="4" t="inlineStr">
@@ -5962,10 +6342,14 @@
       <c r="G113" s="5" t="n"/>
       <c r="H113" s="4" t="n"/>
       <c r="I113" s="4" t="inlineStr"/>
-      <c r="J113" s="5" t="inlineStr"/>
-      <c r="K113" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00CKA-IC-BLK-0001</t>
+        </is>
+      </c>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -6012,10 +6396,14 @@
       </c>
       <c r="H114" s="4" t="n"/>
       <c r="I114" s="4" t="inlineStr"/>
-      <c r="J114" s="5" t="inlineStr"/>
-      <c r="K114" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-IC-RPT-0002</t>
+        </is>
+      </c>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L114" s="4" t="inlineStr">
@@ -6058,10 +6446,14 @@
       <c r="G115" s="5" t="n"/>
       <c r="H115" s="4" t="n"/>
       <c r="I115" s="4" t="inlineStr"/>
-      <c r="J115" s="5" t="inlineStr"/>
-      <c r="K115" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00CJA-IC-BLK-0001</t>
+        </is>
+      </c>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -6104,10 +6496,14 @@
       <c r="G116" s="5" t="n"/>
       <c r="H116" s="4" t="n"/>
       <c r="I116" s="4" t="inlineStr"/>
-      <c r="J116" s="5" t="inlineStr"/>
-      <c r="K116" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-CV-CAL-0001</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L116" s="4" t="inlineStr">
@@ -6150,10 +6546,14 @@
       <c r="G117" s="5" t="n"/>
       <c r="H117" s="4" t="n"/>
       <c r="I117" s="4" t="inlineStr"/>
-      <c r="J117" s="5" t="inlineStr"/>
-      <c r="K117" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-CV-DBR-0001</t>
+        </is>
+      </c>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -6196,10 +6596,14 @@
       <c r="G118" s="5" t="n"/>
       <c r="H118" s="4" t="n"/>
       <c r="I118" s="4" t="inlineStr"/>
-      <c r="J118" s="5" t="inlineStr"/>
-      <c r="K118" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-SS-SPC-0001</t>
+        </is>
+      </c>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L118" s="4" t="inlineStr">
@@ -6242,10 +6646,14 @@
       <c r="G119" s="5" t="n"/>
       <c r="H119" s="4" t="n"/>
       <c r="I119" s="4" t="inlineStr"/>
-      <c r="J119" s="5" t="inlineStr"/>
-      <c r="K119" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-CV-SPC-0001</t>
+        </is>
+      </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -6288,10 +6696,14 @@
       <c r="G120" s="5" t="n"/>
       <c r="H120" s="4" t="n"/>
       <c r="I120" s="4" t="inlineStr"/>
-      <c r="J120" s="5" t="inlineStr"/>
-      <c r="K120" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00UZA-CV-CVL-0002</t>
+        </is>
+      </c>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L120" s="4" t="inlineStr">
@@ -6334,10 +6746,14 @@
       <c r="G121" s="5" t="n"/>
       <c r="H121" s="4" t="n"/>
       <c r="I121" s="4" t="inlineStr"/>
-      <c r="J121" s="5" t="inlineStr"/>
-      <c r="K121" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00UPA-CV-CVL-0001</t>
+        </is>
+      </c>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -6386,7 +6802,8 @@
       <c r="I122" s="4" t="inlineStr"/>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>permit/PMT-018</t>
+          <t>document/ALP-EPC-00000-HS-RPT-0001
+permit/PMT-018</t>
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr">
@@ -6453,7 +6870,9 @@
 design_parameter/DP-CASE-0042
 design_parameter/DP-OWNR-0041
 design_parameter/DP-OWNR-0042
-design_parameter/DP-OWNR-0043</t>
+design_parameter/DP-OWNR-0043
+document/ALP-EPC-00000-HS-STU-0002
+document/ALP-EPC-00CQA-IC-SPC-0001</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
@@ -6515,7 +6934,8 @@
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0044</t>
+          <t>design_parameter/DP-CASE-0044
+document/ALP-EPC-00000-HS-STU-0001</t>
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr">
@@ -6577,7 +6997,8 @@
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>design_parameter/DP-CASE-0045</t>
+          <t>design_parameter/DP-CASE-0045
+document/ALP-EPC-00000-HS-STU-0001</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
@@ -6627,7 +7048,8 @@
       <c r="I126" s="4" t="inlineStr"/>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>permit/PMT-010</t>
+          <t>document/ALP-EPC-00000-HS-PLN-0001
+permit/PMT-010</t>
         </is>
       </c>
       <c r="K126" s="4" t="inlineStr">
@@ -6675,10 +7097,14 @@
       <c r="G127" s="5" t="n"/>
       <c r="H127" s="4" t="n"/>
       <c r="I127" s="4" t="inlineStr"/>
-      <c r="J127" s="5" t="inlineStr"/>
-      <c r="K127" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-HS-HAZ-0008</t>
+        </is>
+      </c>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -6725,10 +7151,15 @@
       </c>
       <c r="H128" s="4" t="n"/>
       <c r="I128" s="4" t="inlineStr"/>
-      <c r="J128" s="5" t="inlineStr"/>
-      <c r="K128" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-HS-HAZ-0002
+document/ALP-EPC-00000-HS-HAZ-0010</t>
+        </is>
+      </c>
+      <c r="K128" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L128" s="4" t="inlineStr">
@@ -6771,10 +7202,14 @@
       <c r="G129" s="5" t="n"/>
       <c r="H129" s="4" t="n"/>
       <c r="I129" s="4" t="inlineStr"/>
-      <c r="J129" s="5" t="inlineStr"/>
-      <c r="K129" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J129" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-PR-STU-0004</t>
+        </is>
+      </c>
+      <c r="K129" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -6817,10 +7252,14 @@
       <c r="G130" s="5" t="n"/>
       <c r="H130" s="4" t="n"/>
       <c r="I130" s="4" t="inlineStr"/>
-      <c r="J130" s="5" t="inlineStr"/>
-      <c r="K130" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J130" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-GE-PLN-0003</t>
+        </is>
+      </c>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L130" s="4" t="inlineStr">
@@ -6863,10 +7302,15 @@
       <c r="G131" s="5" t="n"/>
       <c r="H131" s="4" t="n"/>
       <c r="I131" s="4" t="inlineStr"/>
-      <c r="J131" s="5" t="inlineStr"/>
-      <c r="K131" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-10LAC-ME-ITP-0001
+document/ALP-IEC-10MBA-ME-ITP-0001</t>
+        </is>
+      </c>
+      <c r="K131" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -6909,10 +7353,14 @@
       <c r="G132" s="5" t="n"/>
       <c r="H132" s="4" t="n"/>
       <c r="I132" s="4" t="inlineStr"/>
-      <c r="J132" s="5" t="inlineStr"/>
-      <c r="K132" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-GE-PLN-0003</t>
+        </is>
+      </c>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L132" s="4" t="inlineStr">
@@ -6955,10 +7403,14 @@
       <c r="G133" s="5" t="n"/>
       <c r="H133" s="4" t="n"/>
       <c r="I133" s="4" t="inlineStr"/>
-      <c r="J133" s="5" t="inlineStr"/>
-      <c r="K133" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-PI-SPC-0003</t>
+        </is>
+      </c>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -7003,7 +7455,8 @@
       <c r="I134" s="4" t="inlineStr"/>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>permit/PMT-013</t>
+          <t>document/ALP-EPC-00000-PI-SPC-0003
+permit/PMT-013</t>
         </is>
       </c>
       <c r="K134" s="4" t="inlineStr">
@@ -7051,10 +7504,14 @@
       <c r="G135" s="5" t="n"/>
       <c r="H135" s="4" t="n"/>
       <c r="I135" s="4" t="inlineStr"/>
-      <c r="J135" s="5" t="inlineStr"/>
-      <c r="K135" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-CM-PLN-0001</t>
+        </is>
+      </c>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -7097,10 +7554,14 @@
       <c r="G136" s="5" t="n"/>
       <c r="H136" s="4" t="n"/>
       <c r="I136" s="4" t="inlineStr"/>
-      <c r="J136" s="5" t="inlineStr"/>
-      <c r="K136" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-CM-CMP-0001</t>
+        </is>
+      </c>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L136" s="4" t="inlineStr">
@@ -7149,7 +7610,8 @@
       <c r="I137" s="4" t="inlineStr"/>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>permit/PMT-021</t>
+          <t>document/ALP-EPC-00000-CM-CMP-0003
+permit/PMT-021</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
@@ -7209,10 +7671,14 @@
           <t>&gt;= 600 MW</t>
         </is>
       </c>
-      <c r="J138" s="5" t="inlineStr"/>
-      <c r="K138" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J138" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-CM-CMP-0002</t>
+        </is>
+      </c>
+      <c r="K138" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L138" s="4" t="inlineStr">
@@ -7265,7 +7731,8 @@
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>permit/PMT-019</t>
+          <t>document/ALP-EPC-00000-CM-CMP-0006
+permit/PMT-019</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
@@ -7321,10 +7788,14 @@
           <t>&lt;= 45 min</t>
         </is>
       </c>
-      <c r="J140" s="5" t="inlineStr"/>
-      <c r="K140" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J140" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-CM-CMP-0004</t>
+        </is>
+      </c>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L140" s="4" t="inlineStr">
@@ -7379,10 +7850,14 @@
           <t>&gt;= 98 %</t>
         </is>
       </c>
-      <c r="J141" s="5" t="inlineStr"/>
-      <c r="K141" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J141" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-CM-CMP-0004</t>
+        </is>
+      </c>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -7437,10 +7912,14 @@
           <t>&gt;= 560 MW</t>
         </is>
       </c>
-      <c r="J142" s="5" t="inlineStr"/>
-      <c r="K142" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J142" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-CM-CMP-0005</t>
+        </is>
+      </c>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L142" s="4" t="inlineStr">
@@ -7467,7 +7946,7 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>Documents submitted electronically with the Owner's numbering and a master document register; review period 14 days (21 days for the Basic Design Package).</t>
+          <t>Documents submitted electronically with the project numbering (consortium proposal adopted by the Owner in TQ-035: ALP-&lt;ORG&gt;-&lt;KKS&gt;-&lt;DISC&gt;-&lt;TYPE&gt;-&lt;NNNN&gt;) and a master document register; review period 14 days (21 days for the Basic Design Package).</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -7483,10 +7962,14 @@
       <c r="G143" s="5" t="n"/>
       <c r="H143" s="4" t="n"/>
       <c r="I143" s="4" t="inlineStr"/>
-      <c r="J143" s="5" t="inlineStr"/>
-      <c r="K143" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J143" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-GE-PRC-0002</t>
+        </is>
+      </c>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -7529,10 +8012,14 @@
       <c r="G144" s="5" t="n"/>
       <c r="H144" s="4" t="n"/>
       <c r="I144" s="4" t="inlineStr"/>
-      <c r="J144" s="5" t="inlineStr"/>
-      <c r="K144" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J144" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-PC-SCH-0001</t>
+        </is>
+      </c>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L144" s="4" t="inlineStr">
@@ -7575,10 +8062,14 @@
       <c r="G145" s="5" t="n"/>
       <c r="H145" s="4" t="n"/>
       <c r="I145" s="4" t="inlineStr"/>
-      <c r="J145" s="5" t="inlineStr"/>
-      <c r="K145" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J145" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-GE-PRC-0003</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -7621,10 +8112,15 @@
       <c r="G146" s="5" t="n"/>
       <c r="H146" s="4" t="n"/>
       <c r="I146" s="4" t="inlineStr"/>
-      <c r="J146" s="5" t="inlineStr"/>
-      <c r="K146" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J146" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-CM-OMM-0001
+document/ALP-IEC-10MBA-ME-OMM-0001</t>
+        </is>
+      </c>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L146" s="4" t="inlineStr">
@@ -7667,10 +8163,14 @@
       <c r="G147" s="5" t="n"/>
       <c r="H147" s="4" t="n"/>
       <c r="I147" s="4" t="inlineStr"/>
-      <c r="J147" s="5" t="inlineStr"/>
-      <c r="K147" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J147" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-CM-PLN-0002</t>
+        </is>
+      </c>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -7713,10 +8213,14 @@
       <c r="G148" s="5" t="n"/>
       <c r="H148" s="4" t="n"/>
       <c r="I148" s="4" t="inlineStr"/>
-      <c r="J148" s="5" t="inlineStr"/>
-      <c r="K148" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J148" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-CM-LST-0002</t>
+        </is>
+      </c>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L148" s="4" t="inlineStr">
@@ -7759,10 +8263,14 @@
       <c r="G149" s="5" t="n"/>
       <c r="H149" s="4" t="n"/>
       <c r="I149" s="4" t="inlineStr"/>
-      <c r="J149" s="5" t="inlineStr"/>
-      <c r="K149" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J149" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-IEC-10MBA-ME-RPT-0001</t>
+        </is>
+      </c>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -7805,10 +8313,14 @@
       <c r="G150" s="5" t="n"/>
       <c r="H150" s="4" t="n"/>
       <c r="I150" s="4" t="inlineStr"/>
-      <c r="J150" s="5" t="inlineStr"/>
-      <c r="K150" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J150" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-GE-LST-0003</t>
+        </is>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L150" s="4" t="inlineStr">
@@ -7853,7 +8365,8 @@
       <c r="I151" s="4" t="inlineStr"/>
       <c r="J151" s="5" t="inlineStr">
         <is>
-          <t>permit/PMT-004</t>
+          <t>document/ALP-EPC-00000-EL-STU-0006
+permit/PMT-004</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
@@ -7903,7 +8416,8 @@
       <c r="I152" s="4" t="inlineStr"/>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>permit/PMT-014</t>
+          <t>document/ALP-EPC-00EKA-ME-SPC-0001
+permit/PMT-014</t>
         </is>
       </c>
       <c r="K152" s="4" t="inlineStr">
@@ -7951,10 +8465,14 @@
       <c r="G153" s="5" t="n"/>
       <c r="H153" s="4" t="n"/>
       <c r="I153" s="4" t="inlineStr"/>
-      <c r="J153" s="5" t="inlineStr"/>
-      <c r="K153" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J153" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-GE-PRC-0003</t>
+        </is>
+      </c>
+      <c r="K153" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -7997,10 +8515,14 @@
       <c r="G154" s="5" t="n"/>
       <c r="H154" s="4" t="n"/>
       <c r="I154" s="4" t="inlineStr"/>
-      <c r="J154" s="5" t="inlineStr"/>
-      <c r="K154" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="J154" s="5" t="inlineStr">
+        <is>
+          <t>document/ALP-EPC-00000-GE-LST-0003</t>
+        </is>
+      </c>
+      <c r="K154" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="L154" s="4" t="inlineStr">
@@ -8048,7 +8570,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T04:17:36Z by SETUP | data a69e0245c2d18fe7</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T15:06:23Z by SETUP | data 7cb6f7f6cb17ec93</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9817,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T04:17:36Z by SETUP | data a69e0245c2d18fe7</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T15:06:23Z by SETUP | data 7cb6f7f6cb17ec93</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11808,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Stack 60 m with CEMS platform and silencer</t>
+          <t>Stack 65 m with CEMS platform and silencer</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -11366,7 +11888,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Power island control system (TCS/ST controls) integrated in plant DCS</t>
+          <t>Power island control system (TCS) by IEC, integrated with the plant DCS: native graphics and alarms on the DCS operator stations, one KKS tag database, common time synchronisation, separate IEC 62443 zone (IF-40)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -13081,7 +13603,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T04:17:36Z by SETUP | data a69e0245c2d18fe7</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T15:06:23Z by SETUP | data 7cb6f7f6cb17ec93</t>
         </is>
       </c>
     </row>
@@ -13150,10 +13672,10 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -13184,10 +13706,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>78.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -13218,10 +13740,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>45.5</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -13252,10 +13774,10 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
         <v>6</v>
@@ -13286,10 +13808,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -13320,10 +13842,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -13354,10 +13876,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>27.3</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -13388,10 +13910,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -13422,10 +13944,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
@@ -13456,10 +13978,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>12.5</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
         <v>7</v>
@@ -13490,10 +14012,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>11.1</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
         <v>8</v>
@@ -13524,10 +14046,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>12.5</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
@@ -13558,10 +14080,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -13592,10 +14114,10 @@
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
@@ -13626,10 +14148,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -13660,10 +14182,10 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F20" t="n">
         <v>6</v>
@@ -13694,10 +14216,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -13728,10 +14250,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -13750,19 +14272,19 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
+      <c r="B23" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="D23" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>32</v>
+      <c r="D23" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/output/requirements_matrix/ALP_requirements_matrix.xlsx
+++ b/output/requirements_matrix/ALP_requirements_matrix.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T15:06:23Z by SETUP | data 7cb6f7f6cb17ec93</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T17:23:32Z by SETUP | data 9c5db87d3bb3d7c9</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,227 @@
       <c r="I6" s="4" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-GE-DBR-0001</t>
+          <t>document/ALP-EPC-00000-GE-DBR-0001
+document/ALP-EPC-00000-PR-PFD-0002
+document/ALP-EPC-00EGA-ME-CAL-0001
+document/ALP-EPC-00EGA-PI-ISO-0001
+document/ALP-EPC-00EGA-PR-PID-0001
+document/ALP-EPC-00EGA-PR-SDS-0001
+document/ALP-EPC-00EGB-ME-CAL-0001
+document/ALP-EPC-00EGB-PI-ISO-0001
+document/ALP-EPC-00EGB-PR-PID-0001
+document/ALP-EPC-00EGB-PR-SDS-0001
+document/ALP-EPC-00EGC-ME-CAL-0001
+document/ALP-EPC-00EGC-PI-ISO-0001
+document/ALP-EPC-00EGC-PI-STR-0001
+document/ALP-EPC-00EGC-PR-PID-0001
+document/ALP-EPC-00EGC-PR-SDS-0001
+document/ALP-EPC-00EKA-ME-CAL-0001
+document/ALP-EPC-00EKA-PI-ISO-0001
+document/ALP-EPC-00EKA-PI-STR-0001
+document/ALP-EPC-00EKA-PR-PID-0001
+document/ALP-EPC-00EKA-PR-SDS-0001
+document/ALP-EPC-00EKC-ME-CAL-0001
+document/ALP-EPC-00EKC-PI-ISO-0001
+document/ALP-EPC-00EKC-PI-STR-0001
+document/ALP-EPC-00EKC-PR-PID-0001
+document/ALP-EPC-00EKC-PR-SDS-0001
+document/ALP-EPC-00GBA-ME-CAL-0001
+document/ALP-EPC-00GBA-PI-ISO-0001
+document/ALP-EPC-00GBA-PR-PID-0001
+document/ALP-EPC-00GBA-PR-SDS-0001
+document/ALP-EPC-00GCA-ME-CAL-0001
+document/ALP-EPC-00GCA-PI-ISO-0001
+document/ALP-EPC-00GCA-PR-PID-0001
+document/ALP-EPC-00GCA-PR-SDS-0001
+document/ALP-EPC-00GHA-ME-CAL-0001
+document/ALP-EPC-00GHA-PI-ISO-0001
+document/ALP-EPC-00GHA-PR-PID-0001
+document/ALP-EPC-00GHA-PR-SDS-0001
+document/ALP-EPC-00GKA-ME-CAL-0001
+document/ALP-EPC-00GKA-PI-ISO-0001
+document/ALP-EPC-00GKA-PR-PID-0001
+document/ALP-EPC-00GKA-PR-SDS-0001
+document/ALP-EPC-00GMA-ME-CAL-0001
+document/ALP-EPC-00GMA-PI-ISO-0001
+document/ALP-EPC-00GMA-PR-PID-0001
+document/ALP-EPC-00GMA-PR-SDS-0001
+document/ALP-EPC-00GNA-ME-CAL-0001
+document/ALP-EPC-00GNA-PI-ISO-0001
+document/ALP-EPC-00GNA-PR-PID-0001
+document/ALP-EPC-00GNA-PR-SDS-0001
+document/ALP-EPC-00GUA-ME-CAL-0001
+document/ALP-EPC-00GUA-PI-ISO-0001
+document/ALP-EPC-00GUA-PR-PID-0001
+document/ALP-EPC-00GUA-PR-SDS-0001
+document/ALP-EPC-00LBG-ME-CAL-0001
+document/ALP-EPC-00LBG-PI-ISO-0001
+document/ALP-EPC-00LBG-PI-STR-0001
+document/ALP-EPC-00LBG-PR-PID-0001
+document/ALP-EPC-00LBG-PR-SDS-0001
+document/ALP-EPC-00LDA-ME-CAL-0001
+document/ALP-EPC-00LDA-PI-ISO-0001
+document/ALP-EPC-00LDA-PR-PID-0001
+document/ALP-EPC-00LDA-PR-SDS-0001
+document/ALP-EPC-00PAA-ME-CAL-0001
+document/ALP-EPC-00PAA-PI-ISO-0001
+document/ALP-EPC-00PAA-PR-PID-0001
+document/ALP-EPC-00PAA-PR-SDS-0001
+document/ALP-EPC-00PAB-ME-CAL-0001
+document/ALP-EPC-00PAB-PI-ISO-0001
+document/ALP-EPC-00PAB-PI-STR-0001
+document/ALP-EPC-00PAB-PR-PID-0001
+document/ALP-EPC-00PAB-PR-SDS-0001
+document/ALP-EPC-00PAC-ME-CAL-0001
+document/ALP-EPC-00PAC-PI-ISO-0001
+document/ALP-EPC-00PAC-PR-PID-0001
+document/ALP-EPC-00PAC-PR-SDS-0001
+document/ALP-EPC-00PAH-ME-CAL-0001
+document/ALP-EPC-00PAH-PI-ISO-0001
+document/ALP-EPC-00PAH-PR-PID-0001
+document/ALP-EPC-00PAH-PR-SDS-0001
+document/ALP-EPC-00PBA-ME-CAL-0001
+document/ALP-EPC-00PBA-PI-ISO-0001
+document/ALP-EPC-00PBA-PR-PID-0001
+document/ALP-EPC-00PBA-PR-SDS-0001
+document/ALP-EPC-00PGA-ME-CAL-0001
+document/ALP-EPC-00PGA-PI-ISO-0001
+document/ALP-EPC-00PGA-PI-STR-0001
+document/ALP-EPC-00PGA-PR-PID-0001
+document/ALP-EPC-00PGA-PR-SDS-0001
+document/ALP-EPC-00QCA-ME-CAL-0001
+document/ALP-EPC-00QCA-PI-ISO-0001
+document/ALP-EPC-00QCA-PR-PID-0001
+document/ALP-EPC-00QCA-PR-SDS-0001
+document/ALP-EPC-00QEA-ME-CAL-0001
+document/ALP-EPC-00QEA-PI-ISO-0001
+document/ALP-EPC-00QEA-PR-PID-0001
+document/ALP-EPC-00QEA-PR-SDS-0001
+document/ALP-EPC-00QHA-ME-CAL-0001
+document/ALP-EPC-00QHA-PI-ISO-0001
+document/ALP-EPC-00QHA-PI-STR-0001
+document/ALP-EPC-00QHA-PR-PID-0001
+document/ALP-EPC-00QHA-PR-SDS-0001
+document/ALP-EPC-00QJA-ME-CAL-0001
+document/ALP-EPC-00QJA-PI-ISO-0001
+document/ALP-EPC-00QJA-PR-PID-0001
+document/ALP-EPC-00QJA-PR-SDS-0001
+document/ALP-EPC-00QJB-ME-CAL-0001
+document/ALP-EPC-00QJB-PI-ISO-0001
+document/ALP-EPC-00QJB-PR-PID-0001
+document/ALP-EPC-00QJB-PR-SDS-0001
+document/ALP-EPC-00QUA-ME-CAL-0001
+document/ALP-EPC-00QUA-PI-ISO-0001
+document/ALP-EPC-00QUA-PR-PID-0001
+document/ALP-EPC-00QUA-PR-SDS-0001
+document/ALP-EPC-00SAA-HV-CAL-0001
+document/ALP-EPC-00SAA-HV-PID-0001
+document/ALP-EPC-00SAA-HV-SDS-0001
+document/ALP-EPC-00SAA-PI-ISO-0001
+document/ALP-EPC-00SGA-ME-CAL-0001
+document/ALP-EPC-00SGA-PI-ISO-0001
+document/ALP-EPC-00SGA-PI-STR-0001
+document/ALP-EPC-00SGA-PR-PID-0001
+document/ALP-EPC-00SGA-PR-SDS-0001
+document/ALP-EPC-00SGC-ME-CAL-0001
+document/ALP-EPC-00SGC-PI-ISO-0001
+document/ALP-EPC-00SGC-PR-PID-0001
+document/ALP-EPC-00SGC-PR-SDS-0001
+document/ALP-EPC-00UAC-PI-LAY-0001
+document/ALP-EPC-00UBA-PI-LAY-0001
+document/ALP-EPC-00UBA-PI-PPL-0001
+document/ALP-EPC-00UCA-PI-LAY-0001
+document/ALP-EPC-00UCA-PI-PPL-0001
+document/ALP-EPC-00UEG-PI-LAY-0001
+document/ALP-EPC-00UEG-PI-PPL-0001
+document/ALP-EPC-00UEK-PI-LAY-0001
+document/ALP-EPC-00UEK-PI-PPL-0001
+document/ALP-EPC-00UGA-PI-LAY-0001
+document/ALP-EPC-00UGA-PI-PPL-0001
+document/ALP-EPC-00UPA-PI-LAY-0001
+document/ALP-EPC-00UPC-PI-LAY-0001
+document/ALP-EPC-00UPC-PI-PPL-0001
+document/ALP-EPC-00UQA-PI-LAY-0001
+document/ALP-EPC-00UQA-PI-PPL-0001
+document/ALP-EPC-00UQA-PI-PPL-0002
+document/ALP-EPC-00UQA-PI-PPL-0003
+document/ALP-EPC-00UZA-PI-LAY-0001
+document/ALP-EPC-00UZA-PI-PPL-0001
+document/ALP-EPC-10HAN-ME-CAL-0001
+document/ALP-EPC-10HAN-PI-ISO-0001
+document/ALP-EPC-10HAN-PI-STR-0001
+document/ALP-EPC-10HAN-PR-PID-0001
+document/ALP-EPC-10HAN-PR-SDS-0001
+document/ALP-EPC-10HSB-ME-CAL-0001
+document/ALP-EPC-10HSB-PI-ISO-0001
+document/ALP-EPC-10HSB-PR-PID-0001
+document/ALP-EPC-10HSB-PR-SDS-0001
+document/ALP-EPC-10LAB-ME-CAL-0001
+document/ALP-EPC-10LAB-PI-ISO-0001
+document/ALP-EPC-10LAB-PI-STR-0001
+document/ALP-EPC-10LAB-PR-PID-0001
+document/ALP-EPC-10LAB-PR-SDS-0001
+document/ALP-EPC-10LAC-ME-CAL-0001
+document/ALP-EPC-10LAC-PI-ISO-0001
+document/ALP-EPC-10LAC-PI-STR-0001
+document/ALP-EPC-10LAC-PR-PID-0001
+document/ALP-EPC-10LAC-PR-SDS-0001
+document/ALP-EPC-10LAE-ME-CAL-0001
+document/ALP-EPC-10LAE-PI-ISO-0001
+document/ALP-EPC-10LAE-PI-STR-0001
+document/ALP-EPC-10LAE-PR-PID-0001
+document/ALP-EPC-10LAE-PR-SDS-0001
+document/ALP-EPC-10LAF-ME-CAL-0001
+document/ALP-EPC-10LAF-PI-ISO-0001
+document/ALP-EPC-10LAF-PI-STR-0001
+document/ALP-EPC-10LAF-PR-PID-0001
+document/ALP-EPC-10LAF-PR-SDS-0001
+document/ALP-EPC-10LBA-ME-CAL-0001
+document/ALP-EPC-10LBA-PI-ISO-0001
+document/ALP-EPC-10LBA-PI-STR-0001
+document/ALP-EPC-10LBA-PR-PID-0001
+document/ALP-EPC-10LBA-PR-SDS-0001
+document/ALP-EPC-10LBB-ME-CAL-0001
+document/ALP-EPC-10LBB-PI-ISO-0001
+document/ALP-EPC-10LBB-PI-STR-0001
+document/ALP-EPC-10LBB-PR-PID-0001
+document/ALP-EPC-10LBB-PR-SDS-0001
+document/ALP-EPC-10LBC-ME-CAL-0001
+document/ALP-EPC-10LBC-PI-ISO-0001
+document/ALP-EPC-10LBC-PI-STR-0001
+document/ALP-EPC-10LBC-PR-PID-0001
+document/ALP-EPC-10LBC-PR-SDS-0001
+document/ALP-EPC-10LBD-ME-CAL-0001
+document/ALP-EPC-10LBD-PI-ISO-0001
+document/ALP-EPC-10LBD-PI-STR-0001
+document/ALP-EPC-10LBD-PR-PID-0001
+document/ALP-EPC-10LBD-PR-SDS-0001
+document/ALP-EPC-10UMA-PI-LAY-0001
+document/ALP-EPC-10UMA-PI-PPL-0001
+document/ALP-EPC-20LCA-ME-CAL-0001
+document/ALP-EPC-20LCA-PI-ISO-0001
+document/ALP-EPC-20LCA-PI-STR-0001
+document/ALP-EPC-20LCA-PR-PID-0001
+document/ALP-EPC-20LCA-PR-SDS-0001
+document/ALP-EPC-20LCB-ME-CAL-0001
+document/ALP-EPC-20LCB-PI-ISO-0001
+document/ALP-EPC-20LCB-PI-STR-0001
+document/ALP-EPC-20LCB-PR-PID-0001
+document/ALP-EPC-20LCB-PR-SDS-0001
+document/ALP-EPC-20MAN-ME-CAL-0001
+document/ALP-EPC-20MAN-PI-ISO-0001
+document/ALP-EPC-20MAN-PI-STR-0001
+document/ALP-EPC-20MAN-PR-PID-0001
+document/ALP-EPC-20MAN-PR-SDS-0001
+document/ALP-EPC-20UMB-PI-LAY-0001
+document/ALP-EPC-20UMB-PI-PPL-0001
+mdl_rule/DL-ME-CAL
+mdl_rule/DL-PI-ISO
+mdl_rule/DL-PI-LAY
+mdl_rule/DL-PI-PPL
+mdl_rule/DL-PI-STR
+mdl_rule/DL-PR-PID
+mdl_rule/DL-PR-SDS</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -703,6 +923,7 @@
 design_parameter/DP-CASE-0035
 design_parameter/DP-CASE-0036
 document/ALP-EPC-00000-GE-DBR-0001
+document/ALP-EPC-00000-PR-RPT-0004
 document/ALP-EPC-00000-PR-STU-0002</t>
         </is>
       </c>
@@ -863,57 +1084,217 @@
 equipment/00BBA20
 equipment/00BFA10
 equipment/00BFA20
+equipment/00BFA30
+equipment/00BFA40
+equipment/00BFA50
+equipment/00BFA60
+equipment/00BFA70
+equipment/00BFA80
 equipment/00BFT10
 equipment/00BFT20
+equipment/00BFT30
+equipment/00BFT40
 equipment/00BMA10
+equipment/00BMA20
 equipment/00BRA10
+equipment/00BRA20
 equipment/00BTA10
 equipment/00CJA10
+equipment/00CJA20
+equipment/00CJA30
+equipment/00CJA40
+equipment/00CJA50
+equipment/00CJA60
+equipment/00CJG10
+equipment/00CKA10
 equipment/00CQA10
+equipment/00CYA10
 equipment/00EGA10
+equipment/00EGA10AP001
+equipment/00EGA10AP002
+equipment/00EGA10AP003
+equipment/00EGA10AP004
+equipment/00EGA10AT001
+equipment/00EGA10AT002
+equipment/00EGA10BB001
 equipment/00EGB10BB001
 equipment/00EGB10BB002
+equipment/00EGB10BB003
 equipment/00EGC10
+equipment/00EGC10AP001
+equipment/00EGC10AP002
+equipment/00EGC10AP003
+equipment/00EGC10AT001
+equipment/00EGC10AT002
+equipment/00EGC10AT003
 equipment/00EKA10
+equipment/00EKA10AC001
+equipment/00EKA10AC002
+equipment/00EKA10AT001
+equipment/00EKA10AT002
+equipment/00EKA10BB001
 equipment/00GBA10
+equipment/00GBA10AP001
+equipment/00GBA10AP002
+equipment/00GBA10AP003
+equipment/00GBA10AP004
+equipment/00GBA10AT001
+equipment/00GBA10AT002
+equipment/00GBA10AT003
+equipment/00GBA10AT004
+equipment/00GBA10AT005
+equipment/00GBA10BB001
 equipment/00GCA10
+equipment/00GCA10AP001
+equipment/00GCA10AP002
+equipment/00GCA10AT001
+equipment/00GCA10AT002
+equipment/00GCA10AT003
+equipment/00GCA10AT004
 equipment/00GHA10AP001
 equipment/00GHA10AP002
 equipment/00GHA10BB001
 equipment/00GHA10BB002
+equipment/00GKA10AP001
+equipment/00GKA10AP002
+equipment/00GKA10AT001
 equipment/00GKA10BB001
+equipment/00GMA10AP001
+equipment/00GMA10AP002
+equipment/00GMA10AP003
+equipment/00GMA10AP004
+equipment/00GMA10AP005
+equipment/00GMA10AP006
+equipment/00GMA10AT001
+equipment/00GMA10BB001
 equipment/00GNA10
+equipment/00GNA10AP001
+equipment/00GNA10AP002
+equipment/00GNA10AP003
+equipment/00GNA10AP004
+equipment/00GNA10BB001
+equipment/00GNA10BB002
 equipment/00GUA10
+equipment/00GUA10AP001
+equipment/00GUA10AP002
 equipment/00LDA10
+equipment/00LDA10AT001
+equipment/00LDA10AT002
+equipment/00PAA10AA001
+equipment/00PAA10AA002
+equipment/00PAA10AP001
+equipment/00PAA10AP002
 equipment/00PAA10AT001
 equipment/00PAA10AT002
+equipment/00PAA10AT003
+equipment/00PAA10AT004
+equipment/00PAB10AA001
+equipment/00PAB10AA002
 equipment/00PAC10AP001
 equipment/00PAC10AP002
 equipment/00PAH10
+equipment/00PAH10AP001
+equipment/00PAH10AP002
+equipment/00PAH10AT001
+equipment/00PAH10AT002
 equipment/00PBA10
+equipment/00PBA10AN001
+equipment/00PBA10AN002
+equipment/00PBA10AP001
+equipment/00PBA10AP002
+equipment/00PBA10AP003
+equipment/00PBA10AP004
+equipment/00PBA10AT001
+equipment/00PBA10AT002
+equipment/00PBA10BB001
+equipment/00PBA10BB002
 equipment/00PGA10AC001
 equipment/00PGA10AC002
 equipment/00PGA10AP001
 equipment/00PGA10AP002
+equipment/00PGA10AT001
 equipment/00PGA10BB001
+equipment/00PGA10BB002
 equipment/00QCA10
+equipment/00QCA10AP001
+equipment/00QCA10AP002
+equipment/00QCA10AP003
+equipment/00QCA10AP004
+equipment/00QCA10AP005
+equipment/00QCA10AP006
+equipment/00QCA10BB001
+equipment/00QCA10BB002
+equipment/00QCA10BB003
 equipment/00QEA10AN001
 equipment/00QEA10AN002
+equipment/00QEA10AN003
 equipment/00QEA10AT001
+equipment/00QEA10AT003
 equipment/00QEA10BB001
+equipment/00QEA10BB002
 equipment/00QHA10
+equipment/00QHA10AN001
+equipment/00QHA10AP001
+equipment/00QHA10AP002
+equipment/00QHA10BB001
+equipment/00QHA10BB002
 equipment/00QJA10
+equipment/00QJA10BB001
 equipment/00QJB10
 equipment/00QUA10
+equipment/00QUA10AC001
 equipment/00SAA10
+equipment/00SAA10AN001
+equipment/00SAA10AN002
+equipment/00SAA10AN003
+equipment/00SAA10AP001
+equipment/00SAA10AP002
+equipment/00SAA11AN001
+equipment/00SAA11AN002
+equipment/00SAA11AN003
+equipment/00SAA11AN004
+equipment/00SAA11AN005
+equipment/00SAA11AN006
+equipment/00SAA11AN007
+equipment/00SAA11AN008
+equipment/00SAA12AN001
+equipment/00SAA12AN002
+equipment/00SAA12AN003
+equipment/00SAA12AN004
+equipment/00SAA13AN001
+equipment/00SAA13AN002
+equipment/00SAA13AN003
+equipment/00SAA13AN004
+equipment/00SAA14AN001
+equipment/00SAA14AN002
 equipment/00SGA10AP001
 equipment/00SGA10AP002
 equipment/00SGA10AP003
 equipment/00SGA10BB001
+equipment/00SGA10BB002
+equipment/00SGC10AA001
+equipment/00SGC10AA002
+equipment/00SGC10AA003
+equipment/00SGC10AA004
+equipment/00SGC10AA005
+equipment/00SGC10AA006
+equipment/00SGC10AA007
+equipment/00SGC10AA008
+equipment/00SGC10AA009
+equipment/00SGC10AA010
+equipment/00SGC10BB001
+equipment/00SGY10
 equipment/00SMA10
 equipment/00SMA20
+equipment/00SMA30
+equipment/00SMA40
+equipment/00SMA50
+equipment/00SMA60
 equipment/00XJA10
+equipment/00XJA10BB001
 equipment/10BBT10
+equipment/10HAN10AP001
+equipment/10HAN10AP002
 equipment/10HAN10BB001
 equipment/10HAN10BB002
 equipment/10HNE10
@@ -1134,7 +1515,8 @@
       <c r="I14" s="4" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-GE-PRC-0003</t>
+          <t>document/ALP-EPC-00000-GE-PRC-0003
+document/ALP-EPC-00000-PI-M3D-0004</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
@@ -1186,6 +1568,7 @@
         <is>
           <t>design_parameter/DP-CASE-0001
 design_parameter/DP-OWNR-0044
+document/ALP-EPC-00000-CV-RPT-0003
 document/ALP-EPC-00000-GE-DBR-0001</t>
         </is>
       </c>
@@ -1461,7 +1844,8 @@
       <c r="J20" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-CASE-0002
-document/ALP-EPC-00000-CV-DBR-0001</t>
+document/ALP-EPC-00000-CV-DBR-0001
+document/ALP-EPC-00000-CV-STU-0001</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1562,7 +1946,11 @@
       <c r="J22" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-CASE-0003
-document/ALP-EPC-00000-ME-SPC-0002</t>
+document/ALP-EPC-00000-EL-CAL-0005
+document/ALP-EPC-00000-ME-RPT-0002
+document/ALP-EPC-00000-ME-SPC-0002
+mr/MR-EL-010
+mr/MR-ME-022</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -1875,6 +2263,8 @@
         <is>
           <t>design_parameter/DP-OWNR-0045
 document/ALP-EPC-00000-ME-STU-0001
+document/ALP-EPC-00UZF-CV-RPT-0001
+mr/MR-ME-024
 permit/PMT-009</t>
         </is>
       </c>
@@ -2800,6 +3190,7 @@
       <c r="J44" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-CASE-0032
+document/ALP-EPC-00000-PR-RPT-0002
 document/ALP-IEC-10MBY-IC-CNR-0001</t>
         </is>
       </c>
@@ -3120,7 +3511,8 @@
       <c r="I50" s="4" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-PR-CAL-0001</t>
+          <t>document/ALP-EPC-00000-PR-CAL-0001
+document/ALP-EPC-00000-PR-CAL-0002</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -4508,7 +4900,8 @@
       <c r="I77" s="4" t="inlineStr"/>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00PAC-ME-CAL-0001</t>
+          <t>document/ALP-EPC-00PAB-PR-STU-0001
+document/ALP-EPC-00PAC-ME-CAL-0001</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
@@ -4558,7 +4951,8 @@
       <c r="I78" s="4" t="inlineStr"/>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00PAB-PR-SDS-0001</t>
+          <t>document/ALP-EPC-00PAB-PR-SDS-0001
+document/ALP-EPC-00UPA-CV-CAL-0002</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
@@ -4608,7 +5002,8 @@
       <c r="I79" s="4" t="inlineStr"/>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00PAA-PR-SDS-0001</t>
+          <t>document/ALP-EPC-00PAA-PR-SDS-0001
+document/ALP-EPC-00PAA-PR-STU-0001</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
@@ -4877,7 +5272,8 @@
       <c r="J84" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-OWNR-0019
-document/ALP-EPC-00PAA-PR-SDS-0001</t>
+document/ALP-EPC-00PAA-PR-SDS-0001
+document/ALP-EPC-00PAA-PR-STU-0001</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
@@ -5231,7 +5627,96 @@
       <c r="I91" s="4" t="inlineStr"/>
       <c r="J91" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-10LAC-PR-SDS-0001</t>
+          <t>document/ALP-EPC-00EGA-ME-DSH-0001
+document/ALP-EPC-00EGA-ME-DSH-0002
+document/ALP-EPC-00EGA-ME-DSH-0003
+document/ALP-EPC-00EGA-ME-DSH-0004
+document/ALP-EPC-00EGB-ME-DSH-0001
+document/ALP-EPC-00EGC-ME-DSH-0001
+document/ALP-EPC-00EGC-ME-DSH-0002
+document/ALP-EPC-00EGC-ME-DSH-0003
+document/ALP-EPC-00EKA-ME-DSH-0001
+document/ALP-EPC-00EKA-ME-DSH-0002
+document/ALP-EPC-00EKA-ME-DSH-0003
+document/ALP-EPC-00EKA-ME-DSH-0004
+document/ALP-EPC-00GBA-ME-DSH-0001
+document/ALP-EPC-00GBA-ME-DSH-0002
+document/ALP-EPC-00GBA-ME-DSH-0003
+document/ALP-EPC-00GBA-ME-DSH-0004
+document/ALP-EPC-00GCA-ME-DSH-0001
+document/ALP-EPC-00GCA-ME-DSH-0002
+document/ALP-EPC-00GCA-ME-DSH-0003
+document/ALP-EPC-00GHA-ME-DSH-0001
+document/ALP-EPC-00GHA-ME-DSH-0002
+document/ALP-EPC-00GKA-ME-DSH-0001
+document/ALP-EPC-00GKA-ME-DSH-0002
+document/ALP-EPC-00GKA-ME-DSH-0003
+document/ALP-EPC-00GMA-ME-DSH-0001
+document/ALP-EPC-00GMA-ME-DSH-0002
+document/ALP-EPC-00GMA-ME-DSH-0003
+document/ALP-EPC-00GMA-ME-DSH-0004
+document/ALP-EPC-00GMA-ME-DSH-0005
+document/ALP-EPC-00GMA-ME-DSH-0006
+document/ALP-EPC-00GNA-ME-DSH-0001
+document/ALP-EPC-00GNA-ME-DSH-0002
+document/ALP-EPC-00GNA-ME-DSH-0003
+document/ALP-EPC-00GUA-ME-DSH-0001
+document/ALP-EPC-00GUA-ME-DSH-0002
+document/ALP-EPC-00LDA-ME-DSH-0001
+document/ALP-EPC-00LDA-ME-DSH-0002
+document/ALP-EPC-00PAA-ME-DSH-0001
+document/ALP-EPC-00PAA-ME-DSH-0002
+document/ALP-EPC-00PAA-ME-DSH-0003
+document/ALP-EPC-00PAB-ME-DSH-0001
+document/ALP-EPC-00PAC-ME-DSH-0001
+document/ALP-EPC-00PAH-ME-DSH-0001
+document/ALP-EPC-00PAH-ME-DSH-0002
+document/ALP-EPC-00PAH-ME-DSH-0003
+document/ALP-EPC-00PBA-ME-DSH-0001
+document/ALP-EPC-00PBA-ME-DSH-0002
+document/ALP-EPC-00PBA-ME-DSH-0003
+document/ALP-EPC-00PBA-ME-DSH-0004
+document/ALP-EPC-00PBA-ME-DSH-0005
+document/ALP-EPC-00PGA-ME-DSH-0001
+document/ALP-EPC-00PGA-ME-DSH-0002
+document/ALP-EPC-00PGA-ME-DSH-0003
+document/ALP-EPC-00PGA-ME-DSH-0004
+document/ALP-EPC-00QCA-ME-DSH-0001
+document/ALP-EPC-00QCA-ME-DSH-0002
+document/ALP-EPC-00QCA-ME-DSH-0003
+document/ALP-EPC-00QEA-ME-DSH-0001
+document/ALP-EPC-00QEA-ME-DSH-0002
+document/ALP-EPC-00QEA-ME-DSH-0003
+document/ALP-EPC-00QHA-ME-DSH-0001
+document/ALP-EPC-00QHA-ME-DSH-0002
+document/ALP-EPC-00QHA-ME-DSH-0003
+document/ALP-EPC-00QHA-ME-DSH-0004
+document/ALP-EPC-00QJA-ME-DSH-0001
+document/ALP-EPC-00QJA-ME-DSH-0002
+document/ALP-EPC-00QJB-ME-DSH-0001
+document/ALP-EPC-00QUA-ME-DSH-0001
+document/ALP-EPC-00QUA-ME-DSH-0002
+document/ALP-EPC-00SAA-HV-DSH-0001
+document/ALP-EPC-00SAA-ME-DSH-0001
+document/ALP-EPC-00SAA-ME-DSH-0002
+document/ALP-EPC-00SAA-ME-DSH-0003
+document/ALP-EPC-00SGA-ME-DSH-0001
+document/ALP-EPC-00SGA-ME-DSH-0002
+document/ALP-EPC-00SGA-ME-DSH-0003
+document/ALP-EPC-00SGC-ME-DSH-0001
+document/ALP-EPC-00SGC-ME-DSH-0002
+document/ALP-EPC-00SMA-ME-DSH-0001
+document/ALP-EPC-00XJA-ME-DSH-0001
+document/ALP-EPC-10HAN-ME-DSH-0001
+document/ALP-EPC-10HAN-ME-DSH-0002
+document/ALP-EPC-10HNE-ME-DSH-0001
+document/ALP-EPC-10HSB-ME-DSH-0001
+document/ALP-EPC-10HSB-ME-DSH-0002
+document/ALP-EPC-10LAC-ME-DSH-0001
+document/ALP-EPC-10LAC-PR-SDS-0001
+document/ALP-EPC-20LCB-ME-DSH-0001
+mdl_rule/DL-ME-DSH
+mr/MR-PI-006</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
@@ -5435,8 +5920,47 @@
       <c r="I95" s="4" t="inlineStr"/>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-HS-HAZ-0009
+          <t>document/ALP-EPC-00000-CM-TRP-0007
+document/ALP-EPC-00000-HS-HAZ-0009
+document/ALP-EPC-00000-HS-STU-0003
+document/ALP-EPC-00SGA-PR-CAL-0001
 document/ALP-EPC-00SGA-PR-SDS-0001
+document/ALP-EPC-00UAC-HS-GAD-0001
+document/ALP-EPC-00UAC-HS-LAY-0001
+document/ALP-EPC-00UAC-IC-ELY-0001
+document/ALP-EPC-00UBA-HS-GAD-0001
+document/ALP-EPC-00UBA-HS-LAY-0001
+document/ALP-EPC-00UBA-IC-ELY-0001
+document/ALP-EPC-00UCA-HS-GAD-0001
+document/ALP-EPC-00UCA-HS-LAY-0001
+document/ALP-EPC-00UCA-IC-ELY-0002
+document/ALP-EPC-00UEK-HS-GAD-0001
+document/ALP-EPC-00UEK-HS-LAY-0001
+document/ALP-EPC-00UEK-IC-ELY-0002
+document/ALP-EPC-00UGA-HS-GAD-0001
+document/ALP-EPC-00UGA-HS-LAY-0001
+document/ALP-EPC-00UGA-IC-ELY-0002
+document/ALP-EPC-00UPC-HS-GAD-0001
+document/ALP-EPC-00UPC-HS-LAY-0001
+document/ALP-EPC-00UPC-IC-ELY-0002
+document/ALP-EPC-00UQA-HS-GAD-0001
+document/ALP-EPC-00UQA-HS-LAY-0001
+document/ALP-EPC-00UQA-IC-ELY-0002
+document/ALP-EPC-00USA-HS-GAD-0001
+document/ALP-EPC-00USA-HS-LAY-0001
+document/ALP-EPC-00USA-IC-ELY-0001
+document/ALP-EPC-00UYA-HS-GAD-0001
+document/ALP-EPC-00UYA-HS-LAY-0001
+document/ALP-EPC-00UYA-IC-ELY-0001
+document/ALP-EPC-10UMA-HS-GAD-0001
+document/ALP-EPC-10UMA-HS-LAY-0001
+document/ALP-EPC-10UMA-IC-ELY-0002
+document/ALP-EPC-20UMB-HS-GAD-0001
+document/ALP-EPC-20UMB-HS-LAY-0001
+document/ALP-EPC-20UMB-IC-ELY-0002
+mdl_rule/DL-HS-ESC
+mdl_rule/DL-IC-FDL
+mr/MR-IC-006
 permit/PMT-020</t>
         </is>
       </c>
@@ -5487,7 +6011,23 @@
       <c r="I96" s="4" t="inlineStr"/>
       <c r="J96" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00SAA-HV-SDS-0001</t>
+          <t>document/ALP-EPC-00SAA-HV-SDS-0001
+document/ALP-EPC-00UAC-HV-GAD-0001
+document/ALP-EPC-00UBA-HV-GAD-0001
+document/ALP-EPC-00UBA-HV-GAD-0002
+document/ALP-EPC-00UCA-HV-GAD-0001
+document/ALP-EPC-00UCA-HV-GAD-0002
+document/ALP-EPC-00UEK-HV-GAD-0001
+document/ALP-EPC-00UGA-HV-GAD-0001
+document/ALP-EPC-00UPC-HV-GAD-0001
+document/ALP-EPC-00UQA-HV-GAD-0001
+document/ALP-EPC-00USA-HV-GAD-0001
+document/ALP-EPC-00UYA-HV-GAD-0001
+document/ALP-EPC-10UMA-HV-GAD-0001
+document/ALP-EPC-10UMA-HV-GAD-0002
+document/ALP-EPC-20UMB-HV-GAD-0001
+mdl_rule/DL-HV-HVL
+mdl_rule/DL-HV-SRV</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
@@ -5537,7 +6077,8 @@
       <c r="I97" s="4" t="inlineStr"/>
       <c r="J97" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00SMA-ME-SPC-0001</t>
+          <t>document/ALP-EPC-00000-ME-STU-0002
+document/ALP-EPC-00SMA-ME-SPC-0001</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
@@ -5789,7 +6330,36 @@
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00BBA-EL-SLD-0001</t>
+          <t>document/ALP-EPC-00000-EL-RPT-0001
+document/ALP-EPC-00ACA-EL-DSH-0001
+document/ALP-EPC-00BBA-EL-DSH-0001
+document/ALP-EPC-00BBA-EL-SLD-0001
+document/ALP-EPC-00BBA-EL-WIR-0001
+document/ALP-EPC-00BFA-EL-DSH-0001
+document/ALP-EPC-00BFA-EL-WIR-0001
+document/ALP-EPC-00BFA-EL-WIR-0002
+document/ALP-EPC-00BFA-EL-WIR-0003
+document/ALP-EPC-00BFA-EL-WIR-0004
+document/ALP-EPC-00BFA-EL-WIR-0005
+document/ALP-EPC-00BFA-EL-WIR-0006
+document/ALP-EPC-00BFA-EL-WIR-0007
+document/ALP-EPC-00BFA-EL-WIR-0008
+document/ALP-EPC-00BFA-EL-WIR-0009
+document/ALP-EPC-00BFA-EL-WIR-0010
+document/ALP-EPC-00BFA-EL-WIR-0011
+document/ALP-EPC-00BFA-EL-WIR-0012
+document/ALP-EPC-00BFA-EL-WIR-0013
+document/ALP-EPC-00BFT-EL-DSH-0001
+document/ALP-EPC-00BMA-EL-DSH-0001
+document/ALP-EPC-00BRA-EL-DSH-0001
+document/ALP-EPC-00BRA-EL-DSH-0002
+document/ALP-EPC-00BTA-EL-DSH-0001
+document/ALP-EPC-00XJA-EL-DSH-0001
+document/ALP-EPC-10BBT-EL-DSH-0001
+document/ALP-EPC-20BBT-EL-DSH-0001
+mdl_rule/DL-EL-DSH
+mdl_rule/DL-EL-WLV
+mdl_rule/DL-EL-WMV</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
@@ -5839,7 +6409,9 @@
       <c r="I103" s="4" t="inlineStr"/>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00XJA-EL-SPC-0001</t>
+          <t>document/ALP-EPC-00000-EL-CAL-0002
+document/ALP-EPC-00000-EL-CAL-0003
+document/ALP-EPC-00XJA-EL-SPC-0001</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
@@ -5889,7 +6461,8 @@
       <c r="I104" s="4" t="inlineStr"/>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-EL-STU-0002</t>
+          <t>document/ALP-EPC-00000-EL-LST-0003
+document/ALP-EPC-00000-EL-STU-0002</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
@@ -5939,7 +6512,43 @@
       <c r="I105" s="4" t="inlineStr"/>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-EL-STU-0003</t>
+          <t>document/ALP-EPC-00000-EL-STU-0003
+document/ALP-EPC-00UAC-EL-ELY-0001
+document/ALP-EPC-00UAC-EL-ELY-0003
+document/ALP-EPC-00UBA-EL-ELY-0001
+document/ALP-EPC-00UBA-EL-ELY-0003
+document/ALP-EPC-00UBF-EL-ELY-0001
+document/ALP-EPC-00UCA-EL-ELY-0001
+document/ALP-EPC-00UCA-EL-ELY-0003
+document/ALP-EPC-00UEG-EL-ELY-0001
+document/ALP-EPC-00UEG-EL-ELY-0003
+document/ALP-EPC-00UEK-EL-ELY-0001
+document/ALP-EPC-00UEK-EL-ELY-0003
+document/ALP-EPC-00UGA-EL-ELY-0001
+document/ALP-EPC-00UGA-EL-ELY-0003
+document/ALP-EPC-00UPA-EL-ELY-0001
+document/ALP-EPC-00UPA-EL-ELY-0002
+document/ALP-EPC-00UPC-EL-ELY-0001
+document/ALP-EPC-00UPC-EL-ELY-0003
+document/ALP-EPC-00UQA-EL-ELY-0001
+document/ALP-EPC-00UQA-EL-ELY-0003
+document/ALP-EPC-00USA-EL-ELY-0001
+document/ALP-EPC-00UYA-EL-ELY-0001
+document/ALP-EPC-00UZA-EL-ELY-0001
+document/ALP-EPC-00UZA-EL-ELY-0003
+document/ALP-EPC-00UZB-EL-ELY-0001
+document/ALP-EPC-00UZC-EL-ELY-0001
+document/ALP-EPC-00UZD-EL-ELY-0001
+document/ALP-EPC-00UZE-EL-ELY-0001
+document/ALP-EPC-00UZF-EL-ELY-0001
+document/ALP-EPC-10UHA-EL-ELY-0001
+document/ALP-EPC-10UHN-EL-ELY-0001
+document/ALP-EPC-10UMA-EL-ELY-0001
+document/ALP-EPC-10UMA-EL-ELY-0003
+document/ALP-EPC-20UMB-EL-ELY-0001
+document/ALP-EPC-20UMB-EL-ELY-0003
+mdl_rule/DL-EL-EAR
+mdl_rule/DL-EL-ELY</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
@@ -5989,7 +6598,36 @@
       <c r="I106" s="4" t="inlineStr"/>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-EL-SPC-0001</t>
+          <t>document/ALP-EPC-00000-EL-BLK-0001
+document/ALP-EPC-00000-EL-BLK-0002
+document/ALP-EPC-00000-EL-CAL-0004
+document/ALP-EPC-00000-EL-SPC-0001
+document/ALP-EPC-00UAC-EL-CBL-0001
+document/ALP-EPC-00UAC-EL-ELY-0002
+document/ALP-EPC-00UBA-EL-CBL-0001
+document/ALP-EPC-00UBA-EL-ELY-0002
+document/ALP-EPC-00UCA-EL-CBL-0001
+document/ALP-EPC-00UCA-EL-ELY-0002
+document/ALP-EPC-00UEG-EL-CBL-0001
+document/ALP-EPC-00UEG-EL-ELY-0002
+document/ALP-EPC-00UEK-EL-CBL-0001
+document/ALP-EPC-00UEK-EL-ELY-0002
+document/ALP-EPC-00UGA-EL-CBL-0001
+document/ALP-EPC-00UGA-EL-ELY-0002
+document/ALP-EPC-00UPC-EL-CBL-0001
+document/ALP-EPC-00UPC-EL-ELY-0002
+document/ALP-EPC-00UQA-EL-CBL-0001
+document/ALP-EPC-00UQA-EL-ELY-0002
+document/ALP-EPC-00UZA-EL-CBL-0001
+document/ALP-EPC-00UZA-EL-ELY-0002
+document/ALP-EPC-10UMA-EL-CBL-0001
+document/ALP-EPC-10UMA-EL-ELY-0002
+document/ALP-EPC-20UMB-EL-CBL-0001
+document/ALP-EPC-20UMB-EL-ELY-0002
+mdl_rule/DL-EL-CBD
+mdl_rule/DL-EL-CBL
+mdl_rule/DL-EL-CRT
+mr/MR-EL-012</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
@@ -6039,7 +6677,8 @@
       <c r="I107" s="4" t="inlineStr"/>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-EL-SPC-0003</t>
+          <t>document/ALP-EPC-00000-EL-SPC-0003
+document/ALP-EPC-00000-EL-TRP-0001</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
@@ -6089,7 +6728,149 @@
       <c r="I108" s="4" t="inlineStr"/>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00CJA-IC-BLK-0001</t>
+          <t>document/ALP-EPC-00000-IC-SPC-0005
+document/ALP-EPC-00000-IC-TST-0001
+document/ALP-EPC-00ACA-IC-DSH-0001
+document/ALP-EPC-00CJA-IC-BLK-0001
+document/ALP-EPC-00CJA-IC-DSH-0001
+document/ALP-EPC-00CJG-IC-BLK-0001
+document/ALP-EPC-00CJG-IC-DSH-0001
+document/ALP-EPC-00CKA-IC-BLK-0001
+document/ALP-EPC-00CKA-IC-DSH-0001
+document/ALP-EPC-00CQA-IC-BLK-0001
+document/ALP-EPC-00CQA-IC-DSH-0001
+document/ALP-EPC-00CQA-IC-DSH-0002
+document/ALP-EPC-00CYA-IC-BLK-0001
+document/ALP-EPC-00CYA-IC-DSH-0001
+document/ALP-EPC-00EGA-IC-DSH-0001
+document/ALP-EPC-00EGA-IC-DSH-0002
+document/ALP-EPC-00EGB-IC-DSH-0001
+document/ALP-EPC-00EGC-IC-DSH-0001
+document/ALP-EPC-00EGC-IC-DSH-0002
+document/ALP-EPC-00EKA-IC-DSH-0001
+document/ALP-EPC-00EKA-IC-DSH-0002
+document/ALP-EPC-00EKC-IC-DSH-0001
+document/ALP-EPC-00EKC-IC-DSH-0002
+document/ALP-EPC-00GBA-IC-DSH-0001
+document/ALP-EPC-00GBA-IC-DSH-0002
+document/ALP-EPC-00GCA-IC-DSH-0001
+document/ALP-EPC-00GCA-IC-DSH-0002
+document/ALP-EPC-00GHA-IC-DSH-0001
+document/ALP-EPC-00GHA-IC-DSH-0002
+document/ALP-EPC-00GKA-IC-DSH-0001
+document/ALP-EPC-00GMA-IC-DSH-0001
+document/ALP-EPC-00GNA-IC-DSH-0001
+document/ALP-EPC-00GNA-IC-DSH-0002
+document/ALP-EPC-00GUA-IC-DSH-0001
+document/ALP-EPC-00LBG-IC-DSH-0001
+document/ALP-EPC-00LBG-IC-DSH-0002
+document/ALP-EPC-00LDA-IC-DSH-0001
+document/ALP-EPC-00LDA-IC-DSH-0002
+document/ALP-EPC-00PAA-IC-DSH-0001
+document/ALP-EPC-00PAB-IC-DSH-0001
+document/ALP-EPC-00PAC-IC-DSH-0001
+document/ALP-EPC-00PAH-IC-DSH-0001
+document/ALP-EPC-00PBA-IC-DSH-0001
+document/ALP-EPC-00PBA-IC-DSH-0002
+document/ALP-EPC-00PGA-IC-DSH-0001
+document/ALP-EPC-00PGA-IC-DSH-0002
+document/ALP-EPC-00QCA-IC-DSH-0001
+document/ALP-EPC-00QEA-IC-DSH-0001
+document/ALP-EPC-00QEA-IC-DSH-0002
+document/ALP-EPC-00QHA-IC-DSH-0001
+document/ALP-EPC-00QHA-IC-DSH-0002
+document/ALP-EPC-00QJA-IC-DSH-0001
+document/ALP-EPC-00QJA-IC-DSH-0002
+document/ALP-EPC-00QJB-IC-DSH-0001
+document/ALP-EPC-00QJB-IC-DSH-0002
+document/ALP-EPC-00QUA-IC-DSH-0001
+document/ALP-EPC-00SAA-IC-DSH-0001
+document/ALP-EPC-00SAA-IC-DSH-0002
+document/ALP-EPC-00SGA-IC-DSH-0001
+document/ALP-EPC-00SGC-IC-DSH-0001
+document/ALP-EPC-00SGY-IC-BLK-0001
+document/ALP-EPC-00SGY-IC-DSH-0001
+document/ALP-EPC-00UAC-IC-ELY-0002
+document/ALP-EPC-00UAC-IC-HUP-0001
+document/ALP-EPC-00UAC-IC-LOP-0001
+document/ALP-EPC-00UAC-IC-LOP-0002
+document/ALP-EPC-00UBA-IC-ELY-0002
+document/ALP-EPC-00UBA-IC-HUP-0001
+document/ALP-EPC-00UBA-IC-LOP-0001
+document/ALP-EPC-00UBA-IC-LOP-0002
+document/ALP-EPC-00UCA-IC-ELY-0001
+document/ALP-EPC-00UCA-IC-HUP-0001
+document/ALP-EPC-00UCA-IC-LOP-0001
+document/ALP-EPC-00UCA-IC-LOP-0002
+document/ALP-EPC-00UEG-IC-ELY-0001
+document/ALP-EPC-00UEG-IC-HUP-0001
+document/ALP-EPC-00UEG-IC-LOP-0001
+document/ALP-EPC-00UEG-IC-LOP-0002
+document/ALP-EPC-00UEK-IC-ELY-0001
+document/ALP-EPC-00UEK-IC-HUP-0001
+document/ALP-EPC-00UEK-IC-LOP-0001
+document/ALP-EPC-00UEK-IC-LOP-0002
+document/ALP-EPC-00UGA-IC-ELY-0001
+document/ALP-EPC-00UGA-IC-HUP-0001
+document/ALP-EPC-00UGA-IC-LOP-0001
+document/ALP-EPC-00UGA-IC-LOP-0002
+document/ALP-EPC-00UPC-IC-ELY-0001
+document/ALP-EPC-00UPC-IC-HUP-0001
+document/ALP-EPC-00UPC-IC-LOP-0001
+document/ALP-EPC-00UPC-IC-LOP-0002
+document/ALP-EPC-00UQA-IC-ELY-0001
+document/ALP-EPC-00UQA-IC-HUP-0001
+document/ALP-EPC-00UQA-IC-LOP-0001
+document/ALP-EPC-00UQA-IC-LOP-0002
+document/ALP-EPC-00UQA-IC-LOP-0003
+document/ALP-EPC-00UZA-IC-ELY-0001
+document/ALP-EPC-00UZA-IC-HUP-0001
+document/ALP-EPC-00UZA-IC-LOP-0001
+document/ALP-EPC-00UZA-IC-LOP-0002
+document/ALP-EPC-00XJA-IC-DSH-0001
+document/ALP-EPC-10BBT-IC-DSH-0001
+document/ALP-EPC-10HAN-IC-DSH-0001
+document/ALP-EPC-10HAN-IC-DSH-0002
+document/ALP-EPC-10HNE-IC-DSH-0001
+document/ALP-EPC-10HSB-IC-DSH-0001
+document/ALP-EPC-10HSB-IC-DSH-0002
+document/ALP-EPC-10LAB-IC-DSH-0001
+document/ALP-EPC-10LAB-IC-DSH-0002
+document/ALP-EPC-10LAC-IC-DSH-0001
+document/ALP-EPC-10LAC-IC-DSH-0002
+document/ALP-EPC-10LAE-IC-DSH-0001
+document/ALP-EPC-10LAE-IC-DSH-0002
+document/ALP-EPC-10LAF-IC-DSH-0001
+document/ALP-EPC-10LAF-IC-DSH-0002
+document/ALP-EPC-10LBA-IC-DSH-0001
+document/ALP-EPC-10LBB-IC-DSH-0001
+document/ALP-EPC-10LBC-IC-DSH-0001
+document/ALP-EPC-10LBD-IC-DSH-0001
+document/ALP-EPC-10UMA-IC-ELY-0001
+document/ALP-EPC-10UMA-IC-HUP-0001
+document/ALP-EPC-10UMA-IC-LOP-0001
+document/ALP-EPC-10UMA-IC-LOP-0002
+document/ALP-EPC-10UMA-IC-LOP-0003
+document/ALP-EPC-20BBT-IC-DSH-0001
+document/ALP-EPC-20LCA-IC-DSH-0001
+document/ALP-EPC-20LCA-IC-DSH-0002
+document/ALP-EPC-20LCB-IC-DSH-0001
+document/ALP-EPC-20LCB-IC-DSH-0002
+document/ALP-EPC-20MAN-IC-DSH-0001
+document/ALP-EPC-20MAN-IC-DSH-0002
+document/ALP-EPC-20UMB-IC-ELY-0001
+document/ALP-EPC-20UMB-IC-HUP-0001
+document/ALP-EPC-20UMB-IC-LOP-0001
+document/ALP-EPC-20UMB-IC-LOP-0002
+mdl_rule/DL-IC-BLK
+mdl_rule/DL-IC-DSH
+mdl_rule/DL-IC-HUP
+mdl_rule/DL-IC-IDS
+mdl_rule/DL-IC-ILY
+mdl_rule/DL-IC-JBW
+mdl_rule/DL-IC-LOP
+mdl_rule/DL-PR-CVD
+mr/MR-IC-010</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr">
@@ -6139,7 +6920,168 @@
       <c r="I109" s="4" t="inlineStr"/>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-IC-DBR-0001</t>
+          <t>document/ALP-EPC-00000-IC-DBR-0001
+document/ALP-EPC-00000-IC-LST-0002
+document/ALP-EPC-00ACA-IC-LOG-0001
+document/ALP-EPC-00BLA-IC-LOG-0001
+document/ALP-EPC-00BMA-IC-LOG-0001
+document/ALP-EPC-00BRA-IC-LOG-0001
+document/ALP-EPC-00BTA-IC-LOG-0001
+document/ALP-EPC-00CJA-IC-LOG-0001
+document/ALP-EPC-00CJG-IC-LOG-0001
+document/ALP-EPC-00CJG-IC-LOG-0002
+document/ALP-EPC-00CKA-IC-LOG-0001
+document/ALP-EPC-00CQA-IC-LOG-0001
+document/ALP-EPC-00CYA-IC-LOG-0001
+document/ALP-EPC-00EGA-IC-CNR-0001
+document/ALP-EPC-00EGA-IC-HMI-0001
+document/ALP-EPC-00EGA-IC-LOG-0001
+document/ALP-EPC-00EGB-IC-CNR-0001
+document/ALP-EPC-00EGB-IC-HMI-0001
+document/ALP-EPC-00EGB-IC-LOG-0001
+document/ALP-EPC-00EGC-IC-CNR-0001
+document/ALP-EPC-00EGC-IC-HMI-0001
+document/ALP-EPC-00EGC-IC-LOG-0001
+document/ALP-EPC-00EKA-IC-CNR-0001
+document/ALP-EPC-00EKA-IC-HMI-0001
+document/ALP-EPC-00EKA-IC-LOG-0001
+document/ALP-EPC-00EKC-IC-CNR-0001
+document/ALP-EPC-00EKC-IC-HMI-0001
+document/ALP-EPC-00EKC-IC-LOG-0001
+document/ALP-EPC-00GBA-IC-CNR-0001
+document/ALP-EPC-00GBA-IC-HMI-0001
+document/ALP-EPC-00GBA-IC-LOG-0001
+document/ALP-EPC-00GCA-IC-CNR-0001
+document/ALP-EPC-00GCA-IC-HMI-0001
+document/ALP-EPC-00GCA-IC-LOG-0001
+document/ALP-EPC-00GHA-IC-CNR-0001
+document/ALP-EPC-00GHA-IC-HMI-0001
+document/ALP-EPC-00GHA-IC-LOG-0001
+document/ALP-EPC-00GKA-IC-CNR-0001
+document/ALP-EPC-00GKA-IC-HMI-0001
+document/ALP-EPC-00GKA-IC-LOG-0001
+document/ALP-EPC-00GMA-IC-CNR-0001
+document/ALP-EPC-00GMA-IC-HMI-0001
+document/ALP-EPC-00GMA-IC-LOG-0001
+document/ALP-EPC-00GNA-IC-CNR-0001
+document/ALP-EPC-00GNA-IC-HMI-0001
+document/ALP-EPC-00GNA-IC-LOG-0001
+document/ALP-EPC-00GUA-IC-CNR-0001
+document/ALP-EPC-00GUA-IC-HMI-0001
+document/ALP-EPC-00GUA-IC-LOG-0001
+document/ALP-EPC-00LBG-IC-CNR-0001
+document/ALP-EPC-00LBG-IC-HMI-0001
+document/ALP-EPC-00LBG-IC-LOG-0001
+document/ALP-EPC-00LDA-IC-CNR-0001
+document/ALP-EPC-00LDA-IC-HMI-0001
+document/ALP-EPC-00LDA-IC-LOG-0001
+document/ALP-EPC-00PAA-IC-CNR-0001
+document/ALP-EPC-00PAA-IC-HMI-0001
+document/ALP-EPC-00PAA-IC-LOG-0001
+document/ALP-EPC-00PAB-IC-CNR-0001
+document/ALP-EPC-00PAB-IC-HMI-0001
+document/ALP-EPC-00PAB-IC-LOG-0001
+document/ALP-EPC-00PAC-IC-CNR-0001
+document/ALP-EPC-00PAC-IC-HMI-0001
+document/ALP-EPC-00PAC-IC-LOG-0001
+document/ALP-EPC-00PAH-IC-CNR-0001
+document/ALP-EPC-00PAH-IC-HMI-0001
+document/ALP-EPC-00PAH-IC-LOG-0001
+document/ALP-EPC-00PBA-IC-CNR-0001
+document/ALP-EPC-00PBA-IC-HMI-0001
+document/ALP-EPC-00PBA-IC-LOG-0001
+document/ALP-EPC-00PGA-IC-CNR-0001
+document/ALP-EPC-00PGA-IC-HMI-0001
+document/ALP-EPC-00PGA-IC-LOG-0001
+document/ALP-EPC-00QCA-IC-CNR-0001
+document/ALP-EPC-00QCA-IC-HMI-0001
+document/ALP-EPC-00QCA-IC-LOG-0001
+document/ALP-EPC-00QEA-IC-CNR-0001
+document/ALP-EPC-00QEA-IC-HMI-0001
+document/ALP-EPC-00QEA-IC-LOG-0001
+document/ALP-EPC-00QHA-IC-CNR-0001
+document/ALP-EPC-00QHA-IC-HMI-0001
+document/ALP-EPC-00QHA-IC-LOG-0001
+document/ALP-EPC-00QJA-IC-CNR-0001
+document/ALP-EPC-00QJA-IC-HMI-0001
+document/ALP-EPC-00QJA-IC-LOG-0001
+document/ALP-EPC-00QJB-IC-CNR-0001
+document/ALP-EPC-00QJB-IC-HMI-0001
+document/ALP-EPC-00QJB-IC-LOG-0001
+document/ALP-EPC-00QUA-IC-CNR-0001
+document/ALP-EPC-00QUA-IC-HMI-0001
+document/ALP-EPC-00QUA-IC-LOG-0001
+document/ALP-EPC-00SAA-IC-CNR-0001
+document/ALP-EPC-00SAA-IC-HMI-0001
+document/ALP-EPC-00SAA-IC-LOG-0001
+document/ALP-EPC-00SAA-IC-LOG-0002
+document/ALP-EPC-00SGA-IC-CNR-0001
+document/ALP-EPC-00SGA-IC-HMI-0001
+document/ALP-EPC-00SGA-IC-LOG-0001
+document/ALP-EPC-00SGC-IC-CNR-0001
+document/ALP-EPC-00SGC-IC-HMI-0001
+document/ALP-EPC-00SGC-IC-LOG-0001
+document/ALP-EPC-00SGY-IC-LOG-0001
+document/ALP-EPC-00SMA-IC-LOG-0001
+document/ALP-EPC-00XJA-IC-LOG-0001
+document/ALP-EPC-10BBT-IC-LOG-0001
+document/ALP-EPC-10HAN-IC-CNR-0001
+document/ALP-EPC-10HAN-IC-HMI-0001
+document/ALP-EPC-10HAN-IC-LOG-0001
+document/ALP-EPC-10HNE-IC-LOG-0001
+document/ALP-EPC-10HSB-IC-CNR-0001
+document/ALP-EPC-10HSB-IC-HMI-0001
+document/ALP-EPC-10HSB-IC-LOG-0001
+document/ALP-EPC-10LAB-IC-CNR-0001
+document/ALP-EPC-10LAB-IC-HMI-0001
+document/ALP-EPC-10LAB-IC-LOG-0001
+document/ALP-EPC-10LAC-IC-CNR-0001
+document/ALP-EPC-10LAC-IC-HMI-0001
+document/ALP-EPC-10LAC-IC-LOG-0001
+document/ALP-EPC-10LAE-IC-CNR-0001
+document/ALP-EPC-10LAE-IC-HMI-0001
+document/ALP-EPC-10LAE-IC-LOG-0001
+document/ALP-EPC-10LAF-IC-CNR-0001
+document/ALP-EPC-10LAF-IC-HMI-0001
+document/ALP-EPC-10LAF-IC-LOG-0001
+document/ALP-EPC-10LBA-IC-CNR-0001
+document/ALP-EPC-10LBA-IC-HMI-0001
+document/ALP-EPC-10LBA-IC-LOG-0001
+document/ALP-EPC-10LBB-IC-CNR-0001
+document/ALP-EPC-10LBB-IC-HMI-0001
+document/ALP-EPC-10LBB-IC-LOG-0001
+document/ALP-EPC-10LBC-IC-CNR-0001
+document/ALP-EPC-10LBC-IC-HMI-0001
+document/ALP-EPC-10LBC-IC-LOG-0001
+document/ALP-EPC-10LBD-IC-CNR-0001
+document/ALP-EPC-10LBD-IC-HMI-0001
+document/ALP-EPC-10LBD-IC-LOG-0001
+document/ALP-EPC-20BBT-IC-LOG-0001
+document/ALP-EPC-20LCA-IC-CNR-0001
+document/ALP-EPC-20LCA-IC-HMI-0001
+document/ALP-EPC-20LCA-IC-LOG-0001
+document/ALP-EPC-20LCB-IC-CNR-0001
+document/ALP-EPC-20LCB-IC-HMI-0001
+document/ALP-EPC-20LCB-IC-LOG-0001
+document/ALP-EPC-20MAN-IC-CNR-0001
+document/ALP-EPC-20MAN-IC-HMI-0001
+document/ALP-EPC-20MAN-IC-LOG-0001
+document/ALP-I08-00CJG-IC-LOG-0001
+document/ALP-IEC-10MBY-IC-LOG-0001
+document/ALP-IEC-10MBY-IC-LOG-0002
+document/ALP-IEC-10MBY-IC-LOG-0003
+document/ALP-IEC-10MBY-IC-LOG-0004
+document/ALP-IEC-10MBY-IC-LOG-0005
+document/ALP-IEC-10MBY-IC-LOG-0006
+document/ALP-M05-00PBA-IC-LOG-0001
+document/ALP-M08-00QEA-IC-LOG-0001
+document/ALP-M09-00QHA-IC-LOG-0001
+document/ALP-M12-00GBA-IC-LOG-0001
+document/ALP-M14-00GNA-IC-LOG-0001
+mdl_rule/DL-IC-CNR
+mdl_rule/DL-IC-HMI
+mdl_rule/DL-IC-LOG
+mdl_rule/DL-V-LOG</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
@@ -6193,7 +7135,38 @@
       <c r="I110" s="4" t="inlineStr"/>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-HS-HAZ-0007</t>
+          <t>document/ALP-EPC-00000-HS-HAZ-0007
+document/ALP-EPC-00000-IC-LST-0003
+document/ALP-EPC-00000-IC-SPC-0006
+document/ALP-EPC-00EGA-IC-CEM-0001
+document/ALP-EPC-00EGB-IC-CEM-0001
+document/ALP-EPC-00EGC-IC-CEM-0001
+document/ALP-EPC-00EKA-IC-CEM-0001
+document/ALP-EPC-00EKC-IC-CEM-0001
+document/ALP-EPC-00LBG-IC-CEM-0001
+document/ALP-EPC-00QCA-IC-CEM-0001
+document/ALP-EPC-00QEA-IC-CEM-0001
+document/ALP-EPC-00QHA-IC-CEM-0001
+document/ALP-EPC-00QJA-IC-CEM-0001
+document/ALP-EPC-00QJB-IC-CEM-0001
+document/ALP-EPC-00QUA-IC-CEM-0001
+document/ALP-EPC-00SGA-IC-CEM-0001
+document/ALP-EPC-00SGC-IC-CEM-0001
+document/ALP-EPC-10HAN-IC-CEM-0001
+document/ALP-EPC-10HSB-IC-CEM-0001
+document/ALP-EPC-10LAB-IC-CEM-0001
+document/ALP-EPC-10LAC-IC-CEM-0001
+document/ALP-EPC-10LAE-IC-CEM-0001
+document/ALP-EPC-10LAF-IC-CEM-0001
+document/ALP-EPC-10LBA-IC-CEM-0001
+document/ALP-EPC-10LBB-IC-CEM-0001
+document/ALP-EPC-10LBC-IC-CEM-0001
+document/ALP-EPC-10LBD-IC-CEM-0001
+document/ALP-EPC-20LCA-IC-CEM-0001
+document/ALP-EPC-20LCB-IC-CEM-0001
+document/ALP-EPC-20MAN-IC-CEM-0001
+mdl_rule/DL-IC-CEM
+mr/MR-IC-008</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr">
@@ -6244,6 +7217,7 @@
       <c r="J111" s="5" t="inlineStr">
         <is>
           <t>document/ALP-EPC-00CQA-IC-SPC-0001
+document/ALP-EPC-00CQA-IC-TRP-0001
 permit/PMT-017</t>
         </is>
       </c>
@@ -6344,7 +7318,9 @@
       <c r="I113" s="4" t="inlineStr"/>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00CKA-IC-BLK-0001</t>
+          <t>document/ALP-EPC-00000-IC-SPC-0007
+document/ALP-EPC-00CKA-IC-BLK-0001
+mr/MR-IC-009</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
@@ -6398,7 +7374,10 @@
       <c r="I114" s="4" t="inlineStr"/>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-IC-RPT-0002</t>
+          <t>document/ALP-EPC-00000-IC-RPT-0002
+document/ALP-EPC-00000-IC-TRP-0001
+document/ALP-EPC-00000-IC-TST-0002
+mr/MR-IC-007</t>
         </is>
       </c>
       <c r="K114" s="4" t="inlineStr">
@@ -6498,7 +7477,72 @@
       <c r="I116" s="4" t="inlineStr"/>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CV-CAL-0001</t>
+          <t>document/ALP-EPC-00000-CV-CAL-0001
+document/ALP-EPC-00000-CV-TRP-0001
+document/ALP-EPC-00000-CV-TST-0001
+document/ALP-EPC-00UAC-CV-CAL-0001
+document/ALP-EPC-00UAC-CV-EFD-0001
+document/ALP-EPC-00UAC-CV-FND-0001
+document/ALP-EPC-00UBA-CV-CAL-0001
+document/ALP-EPC-00UBA-CV-EFD-0001
+document/ALP-EPC-00UBA-CV-FND-0001
+document/ALP-EPC-00UBF-CV-CAL-0001
+document/ALP-EPC-00UBF-CV-EFD-0001
+document/ALP-EPC-00UBF-CV-FND-0001
+document/ALP-EPC-00UBF-CV-FND-0002
+document/ALP-EPC-00UCA-CV-CAL-0001
+document/ALP-EPC-00UCA-CV-FND-0001
+document/ALP-EPC-00UEG-CV-CAL-0001
+document/ALP-EPC-00UEG-CV-EFD-0001
+document/ALP-EPC-00UEG-CV-FND-0001
+document/ALP-EPC-00UEK-CV-CAL-0001
+document/ALP-EPC-00UEK-CV-EFD-0001
+document/ALP-EPC-00UEK-CV-FND-0001
+document/ALP-EPC-00UGA-CV-CAL-0001
+document/ALP-EPC-00UGA-CV-EFD-0001
+document/ALP-EPC-00UGA-CV-FND-0001
+document/ALP-EPC-00UPA-CV-CAL-0001
+document/ALP-EPC-00UPC-CV-CAL-0001
+document/ALP-EPC-00UPC-CV-EFD-0001
+document/ALP-EPC-00UPC-CV-FND-0001
+document/ALP-EPC-00UPC-CV-FND-0002
+document/ALP-EPC-00UQA-CV-CAL-0001
+document/ALP-EPC-00UQA-CV-EFD-0001
+document/ALP-EPC-00UQA-CV-FND-0001
+document/ALP-EPC-00USA-CV-CAL-0001
+document/ALP-EPC-00USA-CV-FND-0001
+document/ALP-EPC-00UYA-CV-CAL-0001
+document/ALP-EPC-00UYA-CV-FND-0001
+document/ALP-EPC-00UZA-CV-CAL-0001
+document/ALP-EPC-00UZB-CV-CAL-0001
+document/ALP-EPC-00UZC-CV-CAL-0001
+document/ALP-EPC-00UZD-CV-CAL-0001
+document/ALP-EPC-00UZD-CV-FND-0001
+document/ALP-EPC-00UZD-CV-FND-0002
+document/ALP-EPC-00UZE-CV-CAL-0001
+document/ALP-EPC-00UZF-CV-CAL-0001
+document/ALP-EPC-00UZF-CV-FND-0001
+document/ALP-EPC-00UZF-CV-FND-0002
+document/ALP-EPC-10UHA-CV-CAL-0001
+document/ALP-EPC-10UHA-CV-EFD-0001
+document/ALP-EPC-10UHA-CV-FND-0001
+document/ALP-EPC-10UHA-CV-FND-0002
+document/ALP-EPC-10UHN-CV-CAL-0001
+document/ALP-EPC-10UHN-CV-EFD-0001
+document/ALP-EPC-10UHN-CV-FND-0001
+document/ALP-EPC-10UHN-CV-FND-0002
+document/ALP-EPC-10UMA-CV-CAL-0001
+document/ALP-EPC-10UMA-CV-EFD-0001
+document/ALP-EPC-10UMA-CV-FND-0001
+document/ALP-EPC-10UMA-CV-FND-0002
+document/ALP-EPC-20UMB-CV-CAL-0001
+document/ALP-EPC-20UMB-CV-EFD-0001
+document/ALP-EPC-20UMB-CV-FND-0001
+document/ALP-EPC-20UMB-CV-FND-0002
+mdl_rule/DL-CV-CAL
+mdl_rule/DL-CV-EFD
+mdl_rule/DL-CV-FND
+mdl_rule/DL-CV-PIL</t>
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr">
@@ -6548,7 +7592,26 @@
       <c r="I117" s="4" t="inlineStr"/>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CV-DBR-0001</t>
+          <t>document/ALP-EPC-00000-CV-DBR-0001
+document/ALP-EPC-00UAC-CV-ARC-0001
+document/ALP-EPC-00UAC-SS-STL-0001
+document/ALP-EPC-00UBA-CV-ARC-0001
+document/ALP-EPC-00UBA-SS-STL-0001
+document/ALP-EPC-00UCA-CV-ARC-0001
+document/ALP-EPC-00UCA-SS-STL-0001
+document/ALP-EPC-00UEK-CV-ARC-0001
+document/ALP-EPC-00UGA-CV-ARC-0001
+document/ALP-EPC-00UGA-SS-STL-0001
+document/ALP-EPC-00UPC-CV-ARC-0001
+document/ALP-EPC-00UQA-CV-ARC-0001
+document/ALP-EPC-00USA-CV-ARC-0001
+document/ALP-EPC-00USA-SS-STL-0001
+document/ALP-EPC-00UYA-CV-ARC-0001
+document/ALP-EPC-00UYA-SS-STL-0001
+document/ALP-EPC-10UMA-CV-ARC-0001
+document/ALP-EPC-20UMB-CV-ARC-0001
+mdl_rule/DL-CV-ARC
+mdl_rule/DL-SS-BLD</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
@@ -6598,7 +7661,85 @@
       <c r="I118" s="4" t="inlineStr"/>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-SS-SPC-0001</t>
+          <t>document/ALP-EPC-00000-SS-SPC-0001
+document/ALP-EPC-00EGA-PI-SUP-0001
+document/ALP-EPC-00EGB-PI-SUP-0001
+document/ALP-EPC-00EGC-PI-SUP-0001
+document/ALP-EPC-00EKA-PI-SUP-0001
+document/ALP-EPC-00EKC-PI-SUP-0001
+document/ALP-EPC-00GBA-PI-SUP-0001
+document/ALP-EPC-00GCA-PI-SUP-0001
+document/ALP-EPC-00GHA-PI-SUP-0001
+document/ALP-EPC-00GKA-PI-SUP-0001
+document/ALP-EPC-00GMA-PI-SUP-0001
+document/ALP-EPC-00GNA-PI-SUP-0001
+document/ALP-EPC-00GUA-PI-SUP-0001
+document/ALP-EPC-00LBG-PI-SUP-0001
+document/ALP-EPC-00LDA-PI-SUP-0001
+document/ALP-EPC-00PAA-PI-SUP-0001
+document/ALP-EPC-00PAB-PI-SUP-0001
+document/ALP-EPC-00PAC-PI-SUP-0001
+document/ALP-EPC-00PAH-PI-SUP-0001
+document/ALP-EPC-00PBA-PI-SUP-0001
+document/ALP-EPC-00PGA-PI-SUP-0001
+document/ALP-EPC-00QCA-PI-SUP-0001
+document/ALP-EPC-00QEA-PI-SUP-0001
+document/ALP-EPC-00QHA-PI-SUP-0001
+document/ALP-EPC-00QJA-PI-SUP-0001
+document/ALP-EPC-00QJB-PI-SUP-0001
+document/ALP-EPC-00QUA-PI-SUP-0001
+document/ALP-EPC-00SAA-PI-SUP-0001
+document/ALP-EPC-00SGA-PI-SUP-0001
+document/ALP-EPC-00SGC-PI-SUP-0001
+document/ALP-EPC-00UAC-SS-STL-0002
+document/ALP-EPC-00UBA-SS-STL-0002
+document/ALP-EPC-00UBF-SS-STL-0001
+document/ALP-EPC-00UCA-SS-STL-0002
+document/ALP-EPC-00UEG-SS-STL-0001
+document/ALP-EPC-00UEK-SS-STL-0001
+document/ALP-EPC-00UGA-SS-STL-0002
+document/ALP-EPC-00UPC-SS-STL-0001
+document/ALP-EPC-00UQA-SS-STL-0001
+document/ALP-EPC-00USA-SS-STL-0002
+document/ALP-EPC-00UYA-SS-STL-0002
+document/ALP-EPC-00UZD-SS-STL-0001
+document/ALP-EPC-00UZF-SS-STL-0001
+document/ALP-EPC-10HAN-PI-SUP-0001
+document/ALP-EPC-10HSB-PI-SUP-0001
+document/ALP-EPC-10LAB-PI-SUP-0001
+document/ALP-EPC-10LAC-PI-SUP-0001
+document/ALP-EPC-10LAE-PI-SUP-0001
+document/ALP-EPC-10LAF-PI-SUP-0001
+document/ALP-EPC-10LBA-PI-SUP-0001
+document/ALP-EPC-10LBB-PI-SUP-0001
+document/ALP-EPC-10LBC-PI-SUP-0001
+document/ALP-EPC-10LBD-PI-SUP-0001
+document/ALP-EPC-10UMA-SS-STL-0001
+document/ALP-EPC-20LCA-PI-SUP-0001
+document/ALP-EPC-20LCB-PI-SUP-0001
+document/ALP-EPC-20MAN-PI-SUP-0001
+document/ALP-EPC-20UMB-SS-STL-0001
+document/ALP-S01-00UAC-SS-STL-0001
+document/ALP-S01-00UBA-SS-STL-0001
+document/ALP-S01-00UBF-SS-STL-0001
+document/ALP-S01-00UCA-SS-STL-0001
+document/ALP-S01-00UEG-SS-STL-0001
+document/ALP-S01-00UEK-SS-STL-0001
+document/ALP-S01-00UGA-SS-STL-0001
+document/ALP-S01-00UPC-SS-STL-0001
+document/ALP-S01-00UQA-SS-STL-0001
+document/ALP-S01-00USA-SS-STL-0001
+document/ALP-S01-00UYA-SS-STL-0001
+document/ALP-S01-00UZD-SS-STL-0001
+document/ALP-S01-00UZD-SS-STL-0002
+document/ALP-S01-00UZF-SS-STL-0001
+document/ALP-S01-10UMA-SS-STL-0001
+document/ALP-S01-20UMB-SS-STL-0001
+mdl_rule/DL-PI-SUP
+mdl_rule/DL-S-SHP
+mdl_rule/DL-SS-STL
+mr/MR-ME-023
+mr/MR-PI-005</t>
         </is>
       </c>
       <c r="K118" s="4" t="inlineStr">
@@ -6648,7 +7789,28 @@
       <c r="I119" s="4" t="inlineStr"/>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CV-SPC-0001</t>
+          <t>document/ALP-EPC-00000-CV-SPC-0001
+document/ALP-EPC-00UAC-CV-RBR-0001
+document/ALP-EPC-00UBA-CV-RBR-0001
+document/ALP-EPC-00UBF-CV-RBR-0001
+document/ALP-EPC-00UCA-CV-RBR-0001
+document/ALP-EPC-00UEG-CV-RBR-0001
+document/ALP-EPC-00UEK-CV-RBR-0001
+document/ALP-EPC-00UGA-CV-RBR-0001
+document/ALP-EPC-00UPA-CV-RBR-0001
+document/ALP-EPC-00UPC-CV-RBR-0001
+document/ALP-EPC-00UQA-CV-RBR-0001
+document/ALP-EPC-00USA-CV-RBR-0001
+document/ALP-EPC-00UYA-CV-RBR-0001
+document/ALP-EPC-00UZC-CV-RBR-0001
+document/ALP-EPC-00UZD-CV-RBR-0001
+document/ALP-EPC-00UZE-CV-RBR-0001
+document/ALP-EPC-00UZF-CV-RBR-0001
+document/ALP-EPC-10UHA-CV-RBR-0001
+document/ALP-EPC-10UHN-CV-RBR-0001
+document/ALP-EPC-10UMA-CV-RBR-0001
+document/ALP-EPC-20UMB-CV-RBR-0001
+mdl_rule/DL-CV-RBR</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
@@ -6698,7 +7860,17 @@
       <c r="I120" s="4" t="inlineStr"/>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00UZA-CV-CVL-0002</t>
+          <t>document/ALP-EPC-00GKA-PI-PPL-0001
+document/ALP-EPC-00GMA-PI-PPL-0001
+document/ALP-EPC-00PAB-PI-PPL-0001
+document/ALP-EPC-00SGA-PI-PPL-0001
+document/ALP-EPC-00UPA-CV-CVL-0001
+document/ALP-EPC-00UZA-CV-CVL-0002
+document/ALP-EPC-00UZB-CV-CVL-0001
+document/ALP-EPC-00UZC-CV-CVL-0001
+document/ALP-EPC-00UZE-CV-CVL-0001
+mdl_rule/DL-CV-CVL
+mdl_rule/DL-PI-UGP</t>
         </is>
       </c>
       <c r="K120" s="4" t="inlineStr">
@@ -6802,7 +7974,10 @@
       <c r="I122" s="4" t="inlineStr"/>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-HS-RPT-0001
+          <t>document/ALP-EPC-00000-HS-PLN-0003
+document/ALP-EPC-00000-HS-PLN-0004
+document/ALP-EPC-00000-HS-RPT-0001
+document/ALP-EPC-00000-PR-LST-0003
 permit/PMT-018</t>
         </is>
       </c>
@@ -7048,7 +8223,71 @@
       <c r="I126" s="4" t="inlineStr"/>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-HS-PLN-0001
+          <t>document/ALP-C01-00000-GE-MOS-0001
+document/ALP-C01-00000-GE-MOS-0002
+document/ALP-C01-00000-GE-MOS-0003
+document/ALP-C01-00000-GE-MOS-0004
+document/ALP-C01-00000-GE-MOS-0005
+document/ALP-C01-00000-GE-MOS-0006
+document/ALP-C02-00000-GE-MOS-0001
+document/ALP-C02-00000-GE-MOS-0002
+document/ALP-C02-00000-GE-MOS-0003
+document/ALP-C02-00000-GE-MOS-0004
+document/ALP-C02-00000-GE-MOS-0005
+document/ALP-C02-00000-GE-MOS-0006
+document/ALP-C03-00UPA-GE-MOS-0001
+document/ALP-C03-00UPA-GE-MOS-0002
+document/ALP-C03-00UPA-GE-MOS-0003
+document/ALP-C03-00UPA-GE-MOS-0004
+document/ALP-C03-00UPA-GE-MOS-0005
+document/ALP-C03-00UPA-GE-MOS-0006
+document/ALP-E12-00000-GE-MOS-0001
+document/ALP-E12-00000-GE-MOS-0002
+document/ALP-E12-00000-GE-MOS-0003
+document/ALP-E12-00000-GE-MOS-0004
+document/ALP-E12-00000-GE-MOS-0005
+document/ALP-E12-00000-GE-MOS-0006
+document/ALP-EPC-00000-HS-PLN-0001
+document/ALP-EPC-00000-HS-PLN-0002
+document/ALP-EPC-00000-HS-PLN-0005
+document/ALP-EPC-00000-HS-RPT-0006
+document/ALP-M17-00EGB-GE-MOS-0001
+document/ALP-M17-00EGB-GE-MOS-0002
+document/ALP-M17-00EGB-GE-MOS-0003
+document/ALP-M17-00EGB-GE-MOS-0004
+document/ALP-M17-00EGB-GE-MOS-0005
+document/ALP-M17-00EGB-GE-MOS-0006
+document/ALP-M22-00000-GE-MOS-0001
+document/ALP-M22-00000-GE-MOS-0002
+document/ALP-M22-00000-GE-MOS-0003
+document/ALP-M22-00000-GE-MOS-0004
+document/ALP-M22-00000-GE-MOS-0005
+document/ALP-M22-00000-GE-MOS-0006
+document/ALP-M23-00000-GE-MOS-0001
+document/ALP-M23-00000-GE-MOS-0002
+document/ALP-M23-00000-GE-MOS-0003
+document/ALP-M23-00000-GE-MOS-0004
+document/ALP-M23-00000-GE-MOS-0005
+document/ALP-M23-00000-GE-MOS-0006
+document/ALP-M24-00UZF-GE-MOS-0001
+document/ALP-M24-00UZF-GE-MOS-0002
+document/ALP-M24-00UZF-GE-MOS-0003
+document/ALP-M24-00UZF-GE-MOS-0004
+document/ALP-M24-00UZF-GE-MOS-0005
+document/ALP-M24-00UZF-GE-MOS-0006
+document/ALP-S01-00000-GE-MOS-0001
+document/ALP-S01-00000-GE-MOS-0002
+document/ALP-S01-00000-GE-MOS-0003
+document/ALP-S01-00000-GE-MOS-0004
+document/ALP-S01-00000-GE-MOS-0005
+document/ALP-S01-00000-GE-MOS-0006
+document/ALP-S02-10HNE-GE-MOS-0001
+document/ALP-S02-10HNE-GE-MOS-0002
+document/ALP-S02-10HNE-GE-MOS-0003
+document/ALP-S02-10HNE-GE-MOS-0004
+document/ALP-S02-10HNE-GE-MOS-0005
+document/ALP-S02-10HNE-GE-MOS-0006
+mdl_rule/DL-S-MOS
 permit/PMT-010</t>
         </is>
       </c>
@@ -7099,7 +8338,9 @@
       <c r="I127" s="4" t="inlineStr"/>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-HS-HAZ-0008</t>
+          <t>document/ALP-EPC-00000-EL-LST-0004
+document/ALP-EPC-00000-HS-HAZ-0008
+document/ALP-EPC-00000-HS-RPT-0005</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
@@ -7154,7 +8395,9 @@
       <c r="J128" s="5" t="inlineStr">
         <is>
           <t>document/ALP-EPC-00000-HS-HAZ-0002
-document/ALP-EPC-00000-HS-HAZ-0010</t>
+document/ALP-EPC-00000-HS-HAZ-0010
+document/ALP-EPC-00000-HS-RPT-0004
+document/ALP-EPC-00000-PR-RPT-0003</t>
         </is>
       </c>
       <c r="K128" s="4" t="inlineStr">
@@ -7254,7 +8497,8 @@
       <c r="I130" s="4" t="inlineStr"/>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-GE-PLN-0003</t>
+          <t>document/ALP-EPC-00000-GE-PLN-0003
+document/ALP-EPC-00000-GE-PLN-0005</t>
         </is>
       </c>
       <c r="K130" s="4" t="inlineStr">
@@ -7304,8 +8548,236 @@
       <c r="I131" s="4" t="inlineStr"/>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-10LAC-ME-ITP-0001
-document/ALP-IEC-10MBA-ME-ITP-0001</t>
+          <t>document/ALP-C01-00000-GE-ITP-0001
+document/ALP-C02-00000-GE-ITP-0001
+document/ALP-C03-00UPA-GE-ITP-0001
+document/ALP-E12-00000-GE-ITP-0001
+document/ALP-EPC-00000-CV-MRQ-0001
+document/ALP-EPC-00000-CV-MRQ-0002
+document/ALP-EPC-00000-CV-MRQ-0003
+document/ALP-EPC-00000-CV-SPC-0003
+document/ALP-EPC-00000-CV-SPC-0004
+document/ALP-EPC-00000-CV-SPC-0005
+document/ALP-EPC-00000-EL-MRQ-0001
+document/ALP-EPC-00000-EL-MRQ-0002
+document/ALP-EPC-00000-EL-SPC-0004
+document/ALP-EPC-00000-EL-SPC-0005
+document/ALP-EPC-00000-GE-ITP-0001
+document/ALP-EPC-00000-GE-MRQ-0001
+document/ALP-EPC-00000-GE-MRQ-0002
+document/ALP-EPC-00000-GE-MRQ-0003
+document/ALP-EPC-00000-GE-MRQ-0004
+document/ALP-EPC-00000-GE-MRQ-0005
+document/ALP-EPC-00000-GE-MRQ-0006
+document/ALP-EPC-00000-GE-MRQ-0007
+document/ALP-EPC-00000-GE-MRQ-0008
+document/ALP-EPC-00000-GE-RPT-0001
+document/ALP-EPC-00000-GE-RPT-0002
+document/ALP-EPC-00000-GE-RPT-0003
+document/ALP-EPC-00000-GE-RPT-0004
+document/ALP-EPC-00000-GE-RPT-0005
+document/ALP-EPC-00000-GE-RPT-0006
+document/ALP-EPC-00000-GE-RPT-0007
+document/ALP-EPC-00000-GE-RPT-0008
+document/ALP-EPC-00000-GE-RPT-0009
+document/ALP-EPC-00000-GE-RPT-0010
+document/ALP-EPC-00000-GE-RPT-0011
+document/ALP-EPC-00000-GE-RPT-0012
+document/ALP-EPC-00000-GE-RPT-0013
+document/ALP-EPC-00000-GE-RPT-0014
+document/ALP-EPC-00000-GE-RPT-0015
+document/ALP-EPC-00000-GE-RPT-0016
+document/ALP-EPC-00000-GE-SPC-0001
+document/ALP-EPC-00000-GE-SPC-0002
+document/ALP-EPC-00000-GE-SPC-0003
+document/ALP-EPC-00000-GE-SPC-0004
+document/ALP-EPC-00000-GE-SPC-0005
+document/ALP-EPC-00000-GE-SPC-0006
+document/ALP-EPC-00000-GE-SPC-0007
+document/ALP-EPC-00000-GE-SPC-0008
+document/ALP-EPC-00000-IC-MRQ-0001
+document/ALP-EPC-00000-IC-MRQ-0002
+document/ALP-EPC-00000-IC-SPC-0003
+document/ALP-EPC-00000-IC-SPC-0004
+document/ALP-EPC-00000-PI-MRQ-0001
+document/ALP-EPC-00000-PI-MRQ-0002
+document/ALP-EPC-00000-PI-MRQ-0003
+document/ALP-EPC-00000-PI-MRQ-0004
+document/ALP-EPC-00000-PI-SPC-0004
+document/ALP-EPC-00000-PI-SPC-0005
+document/ALP-EPC-00000-PI-SPC-0006
+document/ALP-EPC-00000-PI-SPC-0007
+document/ALP-EPC-00000-SS-MRQ-0001
+document/ALP-EPC-00000-SS-SPC-0002
+document/ALP-EPC-00ACA-EL-ITP-0001
+document/ALP-EPC-00ACA-EL-MRQ-0001
+document/ALP-EPC-00ACA-EL-SPC-0001
+document/ALP-EPC-00ACA-GE-RPT-0001
+document/ALP-EPC-00BBA-EL-ITP-0001
+document/ALP-EPC-00BBA-EL-MRQ-0001
+document/ALP-EPC-00BBA-EL-SPC-0001
+document/ALP-EPC-00BBA-GE-RPT-0001
+document/ALP-EPC-00BFA-EL-ITP-0001
+document/ALP-EPC-00BFA-EL-MRQ-0001
+document/ALP-EPC-00BFA-EL-SPC-0001
+document/ALP-EPC-00BFA-GE-RPT-0001
+document/ALP-EPC-00BFT-EL-ITP-0001
+document/ALP-EPC-00BFT-EL-MRQ-0001
+document/ALP-EPC-00BFT-EL-SPC-0001
+document/ALP-EPC-00BFT-GE-RPT-0001
+document/ALP-EPC-00BLA-GE-RPT-0001
+document/ALP-EPC-00BRA-EL-ITP-0001
+document/ALP-EPC-00BRA-EL-MRQ-0001
+document/ALP-EPC-00BRA-EL-SPC-0001
+document/ALP-EPC-00BRA-GE-RPT-0001
+document/ALP-EPC-00BXA-GE-ITP-0001
+document/ALP-EPC-00BXA-GE-MRQ-0001
+document/ALP-EPC-00BXA-GE-RPT-0001
+document/ALP-EPC-00BXA-GE-SPC-0001
+document/ALP-EPC-00CJA-GE-RPT-0001
+document/ALP-EPC-00CJA-IC-ITP-0001
+document/ALP-EPC-00CJA-IC-MRQ-0001
+document/ALP-EPC-00CJA-IC-SPC-0001
+document/ALP-EPC-00CJG-GE-ITP-0001
+document/ALP-EPC-00CJG-GE-MRQ-0001
+document/ALP-EPC-00CJG-GE-RPT-0001
+document/ALP-EPC-00CJG-GE-SPC-0001
+document/ALP-EPC-00CKA-GE-ITP-0001
+document/ALP-EPC-00CKA-GE-MRQ-0001
+document/ALP-EPC-00CKA-GE-RPT-0001
+document/ALP-EPC-00CKA-GE-SPC-0001
+document/ALP-EPC-00CQA-GE-RPT-0001
+document/ALP-EPC-00CQA-IC-ITP-0001
+document/ALP-EPC-00CQA-IC-MRQ-0001
+document/ALP-EPC-00CQA-IC-SPC-0001
+document/ALP-EPC-00CYA-GE-ITP-0001
+document/ALP-EPC-00CYA-GE-MRQ-0001
+document/ALP-EPC-00CYA-GE-RPT-0001
+document/ALP-EPC-00CYA-GE-SPC-0001
+document/ALP-EPC-00EGA-GE-RPT-0001
+document/ALP-EPC-00EGA-ME-ITP-0001
+document/ALP-EPC-00EGA-ME-MRQ-0001
+document/ALP-EPC-00EGA-ME-SPC-0001
+document/ALP-EPC-00EGB-GE-RPT-0001
+document/ALP-EPC-00EGB-ME-MRQ-0001
+document/ALP-EPC-00EGB-ME-SPC-0001
+document/ALP-EPC-00EKA-GE-RPT-0001
+document/ALP-EPC-00EKA-ME-ITP-0001
+document/ALP-EPC-00EKA-ME-MRQ-0001
+document/ALP-EPC-00EKA-ME-SPC-0001
+document/ALP-EPC-00GBA-GE-RPT-0001
+document/ALP-EPC-00GHA-GE-RPT-0001
+document/ALP-EPC-00GHA-ME-ITP-0001
+document/ALP-EPC-00GHA-ME-MRQ-0001
+document/ALP-EPC-00GHA-ME-SPC-0001
+document/ALP-EPC-00GNA-GE-RPT-0001
+document/ALP-EPC-00GNA-ME-ITP-0001
+document/ALP-EPC-00GNA-ME-MRQ-0001
+document/ALP-EPC-00GNA-ME-SPC-0001
+document/ALP-EPC-00LDA-ME-ITP-0001
+document/ALP-EPC-00LDA-ME-MRQ-0001
+document/ALP-EPC-00LDA-ME-SPC-0001
+document/ALP-EPC-00PAA-GE-RPT-0001
+document/ALP-EPC-00PAA-ME-ITP-0001
+document/ALP-EPC-00PAA-ME-MRQ-0001
+document/ALP-EPC-00PAA-ME-SPC-0001
+document/ALP-EPC-00PAB-GE-RPT-0001
+document/ALP-EPC-00PAC-GE-RPT-0001
+document/ALP-EPC-00PAC-ME-ITP-0001
+document/ALP-EPC-00PAC-ME-MRQ-0001
+document/ALP-EPC-00PAC-ME-SPC-0001
+document/ALP-EPC-00PAH-GE-RPT-0001
+document/ALP-EPC-00PAH-ME-ITP-0001
+document/ALP-EPC-00PAH-ME-MRQ-0001
+document/ALP-EPC-00PAH-ME-SPC-0001
+document/ALP-EPC-00PBA-GE-RPT-0001
+document/ALP-EPC-00PBA-ME-ITP-0001
+document/ALP-EPC-00PBA-ME-MRQ-0001
+document/ALP-EPC-00PBA-ME-SPC-0001
+document/ALP-EPC-00PGA-GE-RPT-0001
+document/ALP-EPC-00PGA-ME-ITP-0001
+document/ALP-EPC-00PGA-ME-MRQ-0001
+document/ALP-EPC-00PGA-ME-SPC-0001
+document/ALP-EPC-00QCA-GE-RPT-0001
+document/ALP-EPC-00QCA-ME-ITP-0001
+document/ALP-EPC-00QCA-ME-MRQ-0001
+document/ALP-EPC-00QCA-ME-SPC-0001
+document/ALP-EPC-00QEA-GE-RPT-0001
+document/ALP-EPC-00QEA-ME-ITP-0001
+document/ALP-EPC-00QEA-ME-MRQ-0001
+document/ALP-EPC-00QEA-ME-SPC-0001
+document/ALP-EPC-00QHA-GE-RPT-0001
+document/ALP-EPC-00QHA-ME-ITP-0001
+document/ALP-EPC-00QHA-ME-MRQ-0001
+document/ALP-EPC-00QHA-ME-SPC-0001
+document/ALP-EPC-00QJA-GE-RPT-0001
+document/ALP-EPC-00QJA-ME-ITP-0001
+document/ALP-EPC-00QJA-ME-MRQ-0001
+document/ALP-EPC-00QJA-ME-SPC-0001
+document/ALP-EPC-00QUA-GE-RPT-0001
+document/ALP-EPC-00QUA-IC-ITP-0001
+document/ALP-EPC-00QUA-IC-MRQ-0001
+document/ALP-EPC-00QUA-IC-SPC-0001
+document/ALP-EPC-00SAA-GE-RPT-0001
+document/ALP-EPC-00SAA-HV-ITP-0001
+document/ALP-EPC-00SAA-HV-MRQ-0001
+document/ALP-EPC-00SAA-HV-SPC-0001
+document/ALP-EPC-00SGA-GE-RPT-0001
+document/ALP-EPC-00SGA-ME-ITP-0001
+document/ALP-EPC-00SGA-ME-MRQ-0001
+document/ALP-EPC-00SGA-ME-SPC-0001
+document/ALP-EPC-00SGY-GE-ITP-0001
+document/ALP-EPC-00SGY-GE-MRQ-0001
+document/ALP-EPC-00SGY-GE-RPT-0001
+document/ALP-EPC-00SGY-GE-SPC-0001
+document/ALP-EPC-00SMA-GE-RPT-0001
+document/ALP-EPC-00SMA-ME-ITP-0001
+document/ALP-EPC-00SMA-ME-MRQ-0001
+document/ALP-EPC-00SMA-ME-SPC-0001
+document/ALP-EPC-00UPA-GE-RPT-0001
+document/ALP-EPC-00UZF-GE-MRQ-0001
+document/ALP-EPC-00UZF-GE-RPT-0001
+document/ALP-EPC-00UZF-GE-SPC-0001
+document/ALP-EPC-00XJA-EL-ITP-0001
+document/ALP-EPC-00XJA-EL-MRQ-0001
+document/ALP-EPC-00XJA-EL-SPC-0001
+document/ALP-EPC-00XJA-GE-RPT-0001
+document/ALP-EPC-10BBT-EL-ITP-0001
+document/ALP-EPC-10BBT-EL-MRQ-0001
+document/ALP-EPC-10BBT-EL-SPC-0001
+document/ALP-EPC-10BBT-GE-RPT-0001
+document/ALP-EPC-10HAN-GE-RPT-0001
+document/ALP-EPC-10HAN-ME-ITP-0001
+document/ALP-EPC-10HAN-ME-MRQ-0001
+document/ALP-EPC-10HAN-ME-SPC-0001
+document/ALP-EPC-10HNE-GE-RPT-0001
+document/ALP-EPC-10HNE-SS-MRQ-0001
+document/ALP-EPC-10HNE-SS-SPC-0001
+document/ALP-EPC-10HSB-GE-RPT-0001
+document/ALP-EPC-10HSB-ME-ITP-0001
+document/ALP-EPC-10HSB-ME-MRQ-0001
+document/ALP-EPC-10HSB-ME-SPC-0001
+document/ALP-EPC-10LAC-GE-RPT-0001
+document/ALP-EPC-10LAC-ME-ITP-0001
+document/ALP-EPC-10LAC-ME-MRQ-0001
+document/ALP-EPC-10LAC-ME-SPC-0001
+document/ALP-EPC-10LBA-GE-RPT-0001
+document/ALP-EPC-20LCB-GE-RPT-0001
+document/ALP-EPC-20LCB-ME-ITP-0001
+document/ALP-EPC-20LCB-ME-MRQ-0001
+document/ALP-EPC-20LCB-ME-SPC-0001
+document/ALP-IEC-10MBA-ME-ITP-0001
+document/ALP-M17-00EGB-GE-ITP-0001
+document/ALP-M22-00000-GE-ITP-0001
+document/ALP-M23-00000-GE-ITP-0001
+document/ALP-M24-00UZF-GE-ITP-0001
+document/ALP-S01-00000-GE-ITP-0001
+document/ALP-S02-10HNE-GE-ITP-0001
+mdl_rule/DL-MR-ITP
+mdl_rule/DL-MR-MRQ
+mdl_rule/DL-MR-SPC
+mdl_rule/DL-MR-TBE
+mdl_rule/DL-S-ITP</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
@@ -7355,7 +8827,95 @@
       <c r="I132" s="4" t="inlineStr"/>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-GE-PLN-0003</t>
+          <t>document/ALP-E01-00ACA-ME-TRP-0001
+document/ALP-E01-00ACA-ME-TST-0001
+document/ALP-E02-10BBT-ME-TRP-0001
+document/ALP-E02-10BBT-ME-TST-0001
+document/ALP-E03-00BBA-ME-TRP-0001
+document/ALP-E03-00BBA-ME-TST-0001
+document/ALP-E04-00BFT-ME-TRP-0001
+document/ALP-E04-00BFT-ME-TST-0001
+document/ALP-E05-00BFA-ME-TRP-0001
+document/ALP-E05-00BFA-ME-TST-0001
+document/ALP-E06-00XJA-ME-TRP-0001
+document/ALP-E06-00XJA-ME-TST-0001
+document/ALP-E07-00BRA-ME-TRP-0001
+document/ALP-E07-00BRA-ME-TST-0001
+document/ALP-E10-00BXA-ME-TRP-0001
+document/ALP-E10-00BXA-ME-TST-0001
+document/ALP-E11-00000-ME-TRP-0001
+document/ALP-E11-00000-ME-TST-0001
+document/ALP-EPC-00000-GE-PLN-0003
+document/ALP-H01-00SAA-ME-TRP-0001
+document/ALP-H01-00SAA-ME-TST-0001
+document/ALP-I01-00CJA-ME-TRP-0001
+document/ALP-I01-00CJA-ME-TST-0001
+document/ALP-I02-00CQA-ME-TRP-0001
+document/ALP-I02-00CQA-ME-TST-0001
+document/ALP-I03-00QUA-ME-TRP-0001
+document/ALP-I03-00QUA-ME-TST-0001
+document/ALP-I06-00SGY-ME-TRP-0001
+document/ALP-I06-00SGY-ME-TST-0001
+document/ALP-I07-00CYA-ME-TRP-0001
+document/ALP-I07-00CYA-ME-TST-0001
+document/ALP-I08-00CJG-ME-TRP-0001
+document/ALP-I08-00CJG-ME-TST-0001
+document/ALP-I09-00CKA-ME-TRP-0001
+document/ALP-I09-00CKA-ME-TST-0001
+document/ALP-IEC-10BAT-ME-TRP-0001
+document/ALP-IEC-10BAT-ME-TST-0001
+document/ALP-IEC-10HAA-ME-TRP-0001
+document/ALP-IEC-10HAA-ME-TST-0001
+document/ALP-IEC-10MBA-ME-TRP-0001
+document/ALP-IEC-10MBA-ME-TST-0001
+document/ALP-IEC-10MBY-ME-TRP-0001
+document/ALP-IEC-10MBY-ME-TST-0001
+document/ALP-IEC-10MKA-ME-TRP-0001
+document/ALP-IEC-10MKA-ME-TST-0001
+document/ALP-IEC-20MAA-ME-TRP-0001
+document/ALP-IEC-20MAA-ME-TST-0001
+document/ALP-M01-10LAC-ME-TRP-0001
+document/ALP-M01-10LAC-ME-TST-0001
+document/ALP-M02-20LCB-ME-TRP-0001
+document/ALP-M02-20LCB-ME-TST-0001
+document/ALP-M03-00PAC-ME-TRP-0001
+document/ALP-M03-00PAC-ME-TST-0001
+document/ALP-M04-00PAA-ME-TRP-0001
+document/ALP-M04-00PAA-ME-TST-0001
+document/ALP-M05-00PBA-ME-TRP-0001
+document/ALP-M05-00PBA-ME-TST-0001
+document/ALP-M06-00PAH-ME-TRP-0001
+document/ALP-M06-00PAH-ME-TST-0001
+document/ALP-M07-00PGA-ME-TRP-0001
+document/ALP-M07-00PGA-ME-TST-0001
+document/ALP-M08-00QEA-ME-TRP-0001
+document/ALP-M08-00QEA-ME-TST-0001
+document/ALP-M09-00QHA-ME-TRP-0001
+document/ALP-M09-00QHA-ME-TST-0001
+document/ALP-M10-00QJA-ME-TRP-0001
+document/ALP-M10-00QJA-ME-TST-0001
+document/ALP-M11-00QCA-ME-TRP-0001
+document/ALP-M11-00QCA-ME-TST-0001
+document/ALP-M12-00GBA-ME-TRP-0001
+document/ALP-M12-00GBA-ME-TST-0001
+document/ALP-M13-00GHA-ME-TRP-0001
+document/ALP-M13-00GHA-ME-TST-0001
+document/ALP-M14-00GNA-ME-TRP-0001
+document/ALP-M14-00GNA-ME-TST-0001
+document/ALP-M15-00EKA-ME-TRP-0001
+document/ALP-M15-00EKA-ME-TST-0001
+document/ALP-M16-00EGA-ME-TRP-0001
+document/ALP-M16-00EGA-ME-TST-0001
+document/ALP-M18-10HSB-ME-TRP-0001
+document/ALP-M18-10HSB-ME-TST-0001
+document/ALP-M19-10HAN-ME-TRP-0001
+document/ALP-M19-10HAN-ME-TST-0001
+document/ALP-M20-00SGA-ME-TRP-0001
+document/ALP-M20-00SGA-ME-TST-0001
+document/ALP-M21-00SMA-ME-TRP-0001
+document/ALP-M21-00SMA-ME-TST-0001
+mdl_rule/DL-V-FAT
+mdl_rule/DL-V-FTR</t>
         </is>
       </c>
       <c r="K132" s="4" t="inlineStr">
@@ -7405,7 +8965,89 @@
       <c r="I133" s="4" t="inlineStr"/>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-PI-SPC-0003</t>
+          <t>document/ALP-E01-00ACA-ME-MDB-0001
+document/ALP-E02-10BBT-ME-MDB-0001
+document/ALP-E03-00BBA-ME-MDB-0001
+document/ALP-E04-00BFT-ME-MDB-0001
+document/ALP-E05-00BFA-ME-MDB-0001
+document/ALP-E06-00XJA-ME-MDB-0001
+document/ALP-E07-00BRA-ME-MDB-0001
+document/ALP-E08-00000-ME-MDB-0001
+document/ALP-E09-00BLA-ME-MDB-0001
+document/ALP-E10-00BXA-ME-MDB-0001
+document/ALP-E11-00000-ME-MDB-0001
+document/ALP-EPC-00000-PI-SPC-0003
+document/ALP-EPC-00EGA-PR-DSH-0001
+document/ALP-EPC-00EGB-PR-DSH-0001
+document/ALP-EPC-00EGC-PR-DSH-0001
+document/ALP-EPC-00EKA-PR-DSH-0001
+document/ALP-EPC-00EKC-PR-DSH-0001
+document/ALP-EPC-00GBA-PR-DSH-0001
+document/ALP-EPC-00GCA-PR-DSH-0001
+document/ALP-EPC-00GHA-PR-DSH-0001
+document/ALP-EPC-00LBG-PR-DSH-0001
+document/ALP-EPC-00LDA-PR-DSH-0001
+document/ALP-EPC-00PGA-PR-DSH-0001
+document/ALP-EPC-00QCA-PR-DSH-0001
+document/ALP-EPC-00QEA-PR-DSH-0001
+document/ALP-EPC-00QHA-PR-DSH-0001
+document/ALP-EPC-00QJA-PR-DSH-0001
+document/ALP-EPC-00QJB-PR-DSH-0001
+document/ALP-EPC-00SAA-PR-DSH-0001
+document/ALP-EPC-00SGA-PR-DSH-0001
+document/ALP-EPC-10HAN-PR-DSH-0001
+document/ALP-EPC-10HSB-PR-DSH-0001
+document/ALP-EPC-10LAB-PR-DSH-0001
+document/ALP-EPC-10LAC-PR-DSH-0001
+document/ALP-EPC-20LCA-PR-DSH-0001
+document/ALP-EPC-20MAN-PR-DSH-0001
+document/ALP-H01-00SAA-ME-MDB-0001
+document/ALP-I01-00CJA-ME-MDB-0001
+document/ALP-I02-00CQA-ME-MDB-0001
+document/ALP-I03-00QUA-ME-MDB-0001
+document/ALP-I04-00000-ME-MDB-0001
+document/ALP-I05-00000-ME-MDB-0001
+document/ALP-I06-00SGY-ME-MDB-0001
+document/ALP-I07-00CYA-ME-MDB-0001
+document/ALP-I08-00CJG-ME-MDB-0001
+document/ALP-I09-00CKA-ME-MDB-0001
+document/ALP-I10-00000-ME-MDB-0001
+document/ALP-IEC-10BAT-ME-MDB-0001
+document/ALP-IEC-10HAA-ME-MDB-0001
+document/ALP-IEC-10MBA-ME-MDB-0001
+document/ALP-IEC-10MBY-ME-MDB-0001
+document/ALP-IEC-10MKA-ME-MDB-0001
+document/ALP-IEC-20MAA-ME-MDB-0001
+document/ALP-M01-10LAC-ME-MDB-0001
+document/ALP-M02-20LCB-ME-MDB-0001
+document/ALP-M03-00PAC-ME-MDB-0001
+document/ALP-M04-00PAA-ME-MDB-0001
+document/ALP-M05-00PBA-ME-MDB-0001
+document/ALP-M06-00PAH-ME-MDB-0001
+document/ALP-M07-00PGA-ME-MDB-0001
+document/ALP-M08-00QEA-ME-MDB-0001
+document/ALP-M09-00QHA-ME-MDB-0001
+document/ALP-M10-00QJA-ME-MDB-0001
+document/ALP-M11-00QCA-ME-MDB-0001
+document/ALP-M12-00GBA-ME-MDB-0001
+document/ALP-M13-00GHA-ME-MDB-0001
+document/ALP-M14-00GNA-ME-MDB-0001
+document/ALP-M15-00EKA-ME-MDB-0001
+document/ALP-M16-00EGA-ME-MDB-0001
+document/ALP-M18-10HSB-ME-MDB-0001
+document/ALP-M19-10HAN-ME-MDB-0001
+document/ALP-M20-00SGA-ME-MDB-0001
+document/ALP-M21-00SMA-ME-MDB-0001
+document/ALP-P01-00000-ME-MDB-0001
+document/ALP-P02-10LBA-ME-MDB-0001
+document/ALP-P03-00000-ME-MDB-0001
+document/ALP-P04-00PAB-ME-MDB-0001
+document/ALP-P05-00000-ME-MDB-0001
+document/ALP-P06-00000-ME-MDB-0001
+document/ALP-P07-00000-ME-MDB-0001
+mdl_rule/DL-PR-PSV
+mdl_rule/DL-V-MDB
+mr/MR-PI-007</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
@@ -7506,7 +9148,141 @@
       <c r="I135" s="4" t="inlineStr"/>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CM-PLN-0001</t>
+          <t>document/ALP-EPC-00000-CM-PLN-0001
+document/ALP-EPC-00000-CM-PRC-0002
+document/ALP-EPC-00ACA-CM-CMP-0001
+document/ALP-EPC-00ACA-CM-MDB-0001
+document/ALP-EPC-00BBA-CM-CMP-0001
+document/ALP-EPC-00BBA-CM-MDB-0001
+document/ALP-EPC-00BFA-CM-CMP-0001
+document/ALP-EPC-00BFA-CM-MDB-0001
+document/ALP-EPC-00BFT-CM-CMP-0001
+document/ALP-EPC-00BFT-CM-MDB-0001
+document/ALP-EPC-00BLA-CM-CMP-0001
+document/ALP-EPC-00BLA-CM-MDB-0001
+document/ALP-EPC-00BMA-CM-CMP-0001
+document/ALP-EPC-00BMA-CM-MDB-0001
+document/ALP-EPC-00BRA-CM-CMP-0001
+document/ALP-EPC-00BRA-CM-MDB-0001
+document/ALP-EPC-00BTA-CM-CMP-0001
+document/ALP-EPC-00BTA-CM-MDB-0001
+document/ALP-EPC-00BXA-CM-CMP-0001
+document/ALP-EPC-00BXA-CM-MDB-0001
+document/ALP-EPC-00CJA-CM-CMP-0001
+document/ALP-EPC-00CJA-CM-MDB-0001
+document/ALP-EPC-00CJG-CM-CMP-0001
+document/ALP-EPC-00CJG-CM-MDB-0001
+document/ALP-EPC-00CKA-CM-CMP-0001
+document/ALP-EPC-00CKA-CM-MDB-0001
+document/ALP-EPC-00CQA-CM-CMP-0001
+document/ALP-EPC-00CQA-CM-MDB-0001
+document/ALP-EPC-00CYA-CM-CMP-0001
+document/ALP-EPC-00CYA-CM-MDB-0001
+document/ALP-EPC-00EGA-CM-CMP-0001
+document/ALP-EPC-00EGA-CM-MDB-0001
+document/ALP-EPC-00EGB-CM-CMP-0001
+document/ALP-EPC-00EGB-CM-MDB-0001
+document/ALP-EPC-00EGC-CM-CMP-0001
+document/ALP-EPC-00EGC-CM-MDB-0001
+document/ALP-EPC-00EKA-CM-CMP-0001
+document/ALP-EPC-00EKA-CM-MDB-0001
+document/ALP-EPC-00EKC-CM-CMP-0001
+document/ALP-EPC-00EKC-CM-MDB-0001
+document/ALP-EPC-00GBA-CM-CMP-0001
+document/ALP-EPC-00GBA-CM-MDB-0001
+document/ALP-EPC-00GCA-CM-CMP-0001
+document/ALP-EPC-00GCA-CM-MDB-0001
+document/ALP-EPC-00GHA-CM-CMP-0001
+document/ALP-EPC-00GHA-CM-MDB-0001
+document/ALP-EPC-00GKA-CM-CMP-0001
+document/ALP-EPC-00GKA-CM-MDB-0001
+document/ALP-EPC-00GMA-CM-CMP-0001
+document/ALP-EPC-00GMA-CM-MDB-0001
+document/ALP-EPC-00GNA-CM-CMP-0001
+document/ALP-EPC-00GNA-CM-MDB-0001
+document/ALP-EPC-00GUA-CM-CMP-0001
+document/ALP-EPC-00GUA-CM-MDB-0001
+document/ALP-EPC-00LBG-CM-CMP-0001
+document/ALP-EPC-00LBG-CM-MDB-0001
+document/ALP-EPC-00LDA-CM-CMP-0001
+document/ALP-EPC-00LDA-CM-MDB-0001
+document/ALP-EPC-00PAA-CM-CMP-0001
+document/ALP-EPC-00PAA-CM-MDB-0001
+document/ALP-EPC-00PAB-CM-CMP-0001
+document/ALP-EPC-00PAB-CM-MDB-0001
+document/ALP-EPC-00PAC-CM-CMP-0001
+document/ALP-EPC-00PAC-CM-MDB-0001
+document/ALP-EPC-00PAH-CM-CMP-0001
+document/ALP-EPC-00PAH-CM-MDB-0001
+document/ALP-EPC-00PBA-CM-CMP-0001
+document/ALP-EPC-00PBA-CM-MDB-0001
+document/ALP-EPC-00PGA-CM-CMP-0001
+document/ALP-EPC-00PGA-CM-MDB-0001
+document/ALP-EPC-00QCA-CM-CMP-0001
+document/ALP-EPC-00QCA-CM-MDB-0001
+document/ALP-EPC-00QEA-CM-CMP-0001
+document/ALP-EPC-00QEA-CM-MDB-0001
+document/ALP-EPC-00QHA-CM-CMP-0001
+document/ALP-EPC-00QHA-CM-MDB-0001
+document/ALP-EPC-00QJA-CM-CMP-0001
+document/ALP-EPC-00QJA-CM-MDB-0001
+document/ALP-EPC-00QJB-CM-CMP-0001
+document/ALP-EPC-00QJB-CM-MDB-0001
+document/ALP-EPC-00QUA-CM-CMP-0001
+document/ALP-EPC-00QUA-CM-MDB-0001
+document/ALP-EPC-00SAA-CM-CMP-0001
+document/ALP-EPC-00SAA-CM-MDB-0001
+document/ALP-EPC-00SGA-CM-CMP-0001
+document/ALP-EPC-00SGA-CM-MDB-0001
+document/ALP-EPC-00SGC-CM-CMP-0001
+document/ALP-EPC-00SGC-CM-MDB-0001
+document/ALP-EPC-00SGY-CM-CMP-0001
+document/ALP-EPC-00SGY-CM-MDB-0001
+document/ALP-EPC-00SMA-CM-CMP-0001
+document/ALP-EPC-00SMA-CM-MDB-0001
+document/ALP-EPC-00XJA-CM-CMP-0001
+document/ALP-EPC-00XJA-CM-MDB-0001
+document/ALP-EPC-10BBT-CM-CMP-0001
+document/ALP-EPC-10BBT-CM-MDB-0001
+document/ALP-EPC-10HAN-CM-CMP-0001
+document/ALP-EPC-10HAN-CM-MDB-0001
+document/ALP-EPC-10HNE-CM-CMP-0001
+document/ALP-EPC-10HNE-CM-MDB-0001
+document/ALP-EPC-10HSB-CM-CMP-0001
+document/ALP-EPC-10HSB-CM-MDB-0001
+document/ALP-EPC-10LAB-CM-CMP-0001
+document/ALP-EPC-10LAB-CM-MDB-0001
+document/ALP-EPC-10LAC-CM-CMP-0001
+document/ALP-EPC-10LAC-CM-MDB-0001
+document/ALP-EPC-10LAE-CM-CMP-0001
+document/ALP-EPC-10LAE-CM-MDB-0001
+document/ALP-EPC-10LAF-CM-CMP-0001
+document/ALP-EPC-10LAF-CM-MDB-0001
+document/ALP-EPC-10LBA-CM-CMP-0001
+document/ALP-EPC-10LBA-CM-MDB-0001
+document/ALP-EPC-10LBB-CM-CMP-0001
+document/ALP-EPC-10LBB-CM-MDB-0001
+document/ALP-EPC-10LBC-CM-CMP-0001
+document/ALP-EPC-10LBC-CM-MDB-0001
+document/ALP-EPC-10LBD-CM-CMP-0001
+document/ALP-EPC-10LBD-CM-MDB-0001
+document/ALP-EPC-20BBT-CM-CMP-0001
+document/ALP-EPC-20BBT-CM-MDB-0001
+document/ALP-EPC-20LCA-CM-CMP-0001
+document/ALP-EPC-20LCA-CM-MDB-0001
+document/ALP-EPC-20LCB-CM-CMP-0001
+document/ALP-EPC-20LCB-CM-MDB-0001
+document/ALP-EPC-20MAN-CM-CMP-0001
+document/ALP-EPC-20MAN-CM-MDB-0001
+document/ALP-IEC-10BAT-CM-CMP-0001
+document/ALP-IEC-10HAA-CM-CMP-0001
+document/ALP-IEC-10MBA-CM-CMP-0001
+document/ALP-IEC-10MBY-CM-CMP-0001
+document/ALP-IEC-10MKA-CM-CMP-0001
+document/ALP-IEC-20MAA-CM-CMP-0001
+mdl_rule/DL-CM-CMP
+mdl_rule/DL-CM-TOD
+mdl_rule/DL-V-CMP</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
@@ -7556,7 +9332,8 @@
       <c r="I136" s="4" t="inlineStr"/>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CM-CMP-0001</t>
+          <t>document/ALP-EPC-00000-CM-CMP-0001
+document/ALP-EPC-00000-CM-TRP-0001</t>
         </is>
       </c>
       <c r="K136" s="4" t="inlineStr">
@@ -7611,6 +9388,7 @@
       <c r="J137" s="5" t="inlineStr">
         <is>
           <t>document/ALP-EPC-00000-CM-CMP-0003
+document/ALP-EPC-00000-CM-TRP-0003
 permit/PMT-021</t>
         </is>
       </c>
@@ -7673,7 +9451,8 @@
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CM-CMP-0002</t>
+          <t>document/ALP-EPC-00000-CM-CMP-0002
+document/ALP-EPC-00000-CM-TRP-0002</t>
         </is>
       </c>
       <c r="K138" s="4" t="inlineStr">
@@ -7732,6 +9511,7 @@
       <c r="J139" s="5" t="inlineStr">
         <is>
           <t>document/ALP-EPC-00000-CM-CMP-0006
+document/ALP-EPC-00000-CM-TRP-0006
 permit/PMT-019</t>
         </is>
       </c>
@@ -7790,7 +9570,8 @@
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CM-CMP-0004</t>
+          <t>document/ALP-EPC-00000-CM-CMP-0004
+document/ALP-EPC-00000-CM-TRP-0004</t>
         </is>
       </c>
       <c r="K140" s="4" t="inlineStr">
@@ -7852,7 +9633,8 @@
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CM-CMP-0004</t>
+          <t>document/ALP-EPC-00000-CM-CMP-0004
+document/ALP-EPC-00000-CM-TRP-0004</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
@@ -7914,7 +9696,8 @@
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CM-CMP-0005</t>
+          <t>document/ALP-EPC-00000-CM-CMP-0005
+document/ALP-EPC-00000-CM-TRP-0005</t>
         </is>
       </c>
       <c r="K142" s="4" t="inlineStr">
@@ -8064,7 +9847,9 @@
       <c r="I145" s="4" t="inlineStr"/>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-GE-PRC-0003</t>
+          <t>document/ALP-EPC-00000-GE-LST-0005
+document/ALP-EPC-00000-GE-PRC-0003
+document/ALP-EPC-00000-PI-M3D-0004</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
@@ -8114,8 +9899,111 @@
       <c r="I146" s="4" t="inlineStr"/>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CM-OMM-0001
-document/ALP-IEC-10MBA-ME-OMM-0001</t>
+          <t>document/ALP-E01-00ACA-ME-OMM-0001
+document/ALP-E02-10BBT-ME-OMM-0001
+document/ALP-E03-00BBA-ME-OMM-0001
+document/ALP-E04-00BFT-ME-OMM-0001
+document/ALP-E05-00BFA-ME-OMM-0001
+document/ALP-E06-00XJA-ME-OMM-0001
+document/ALP-E07-00BRA-ME-OMM-0001
+document/ALP-E10-00BXA-ME-OMM-0001
+document/ALP-E11-00000-ME-OMM-0001
+document/ALP-EPC-00000-CM-OMM-0001
+document/ALP-EPC-00ACA-CM-OMM-0001
+document/ALP-EPC-00BBA-CM-OMM-0001
+document/ALP-EPC-00BFA-CM-OMM-0001
+document/ALP-EPC-00BFT-CM-OMM-0001
+document/ALP-EPC-00BLA-CM-OMM-0001
+document/ALP-EPC-00BMA-CM-OMM-0001
+document/ALP-EPC-00BRA-CM-OMM-0001
+document/ALP-EPC-00BTA-CM-OMM-0001
+document/ALP-EPC-00CJA-CM-OMM-0001
+document/ALP-EPC-00CJG-CM-OMM-0001
+document/ALP-EPC-00CKA-CM-OMM-0001
+document/ALP-EPC-00CQA-CM-OMM-0001
+document/ALP-EPC-00CYA-CM-OMM-0001
+document/ALP-EPC-00EGA-CM-OMM-0001
+document/ALP-EPC-00EGB-CM-OMM-0001
+document/ALP-EPC-00EGC-CM-OMM-0001
+document/ALP-EPC-00EKA-CM-OMM-0001
+document/ALP-EPC-00EKC-CM-OMM-0001
+document/ALP-EPC-00GBA-CM-OMM-0001
+document/ALP-EPC-00GCA-CM-OMM-0001
+document/ALP-EPC-00GHA-CM-OMM-0001
+document/ALP-EPC-00GKA-CM-OMM-0001
+document/ALP-EPC-00GMA-CM-OMM-0001
+document/ALP-EPC-00GNA-CM-OMM-0001
+document/ALP-EPC-00GUA-CM-OMM-0001
+document/ALP-EPC-00LBG-CM-OMM-0001
+document/ALP-EPC-00LDA-CM-OMM-0001
+document/ALP-EPC-00PAA-CM-OMM-0001
+document/ALP-EPC-00PAB-CM-OMM-0001
+document/ALP-EPC-00PAC-CM-OMM-0001
+document/ALP-EPC-00PAH-CM-OMM-0001
+document/ALP-EPC-00PBA-CM-OMM-0001
+document/ALP-EPC-00PGA-CM-OMM-0001
+document/ALP-EPC-00QCA-CM-OMM-0001
+document/ALP-EPC-00QEA-CM-OMM-0001
+document/ALP-EPC-00QHA-CM-OMM-0001
+document/ALP-EPC-00QJA-CM-OMM-0001
+document/ALP-EPC-00QJB-CM-OMM-0001
+document/ALP-EPC-00QUA-CM-OMM-0001
+document/ALP-EPC-00SAA-CM-OMM-0001
+document/ALP-EPC-00SGA-CM-OMM-0001
+document/ALP-EPC-00SGC-CM-OMM-0001
+document/ALP-EPC-00SGY-CM-OMM-0001
+document/ALP-EPC-00XJA-CM-OMM-0001
+document/ALP-EPC-10BBT-CM-OMM-0001
+document/ALP-EPC-10HAN-CM-OMM-0001
+document/ALP-EPC-10HSB-CM-OMM-0001
+document/ALP-EPC-10LAB-CM-OMM-0001
+document/ALP-EPC-10LAC-CM-OMM-0001
+document/ALP-EPC-10LAE-CM-OMM-0001
+document/ALP-EPC-10LAF-CM-OMM-0001
+document/ALP-EPC-10LBA-CM-OMM-0001
+document/ALP-EPC-10LBB-CM-OMM-0001
+document/ALP-EPC-10LBC-CM-OMM-0001
+document/ALP-EPC-10LBD-CM-OMM-0001
+document/ALP-EPC-20BBT-CM-OMM-0001
+document/ALP-EPC-20LCA-CM-OMM-0001
+document/ALP-EPC-20LCB-CM-OMM-0001
+document/ALP-EPC-20MAN-CM-OMM-0001
+document/ALP-H01-00SAA-ME-OMM-0001
+document/ALP-I01-00CJA-ME-OMM-0001
+document/ALP-I02-00CQA-ME-OMM-0001
+document/ALP-I03-00QUA-ME-OMM-0001
+document/ALP-I06-00SGY-ME-OMM-0001
+document/ALP-I07-00CYA-ME-OMM-0001
+document/ALP-I08-00CJG-ME-OMM-0001
+document/ALP-I09-00CKA-ME-OMM-0001
+document/ALP-IEC-10BAT-ME-OMM-0001
+document/ALP-IEC-10HAA-ME-OMM-0001
+document/ALP-IEC-10MBA-ME-OMM-0001
+document/ALP-IEC-10MBY-ME-OMM-0001
+document/ALP-IEC-10MKA-ME-OMM-0001
+document/ALP-IEC-20MAA-ME-OMM-0001
+document/ALP-M01-10LAC-ME-OMM-0001
+document/ALP-M02-20LCB-ME-OMM-0001
+document/ALP-M03-00PAC-ME-OMM-0001
+document/ALP-M04-00PAA-ME-OMM-0001
+document/ALP-M05-00PBA-ME-OMM-0001
+document/ALP-M06-00PAH-ME-OMM-0001
+document/ALP-M07-00PGA-ME-OMM-0001
+document/ALP-M08-00QEA-ME-OMM-0001
+document/ALP-M09-00QHA-ME-OMM-0001
+document/ALP-M10-00QJA-ME-OMM-0001
+document/ALP-M11-00QCA-ME-OMM-0001
+document/ALP-M12-00GBA-ME-OMM-0001
+document/ALP-M13-00GHA-ME-OMM-0001
+document/ALP-M14-00GNA-ME-OMM-0001
+document/ALP-M15-00EKA-ME-OMM-0001
+document/ALP-M16-00EGA-ME-OMM-0001
+document/ALP-M18-10HSB-ME-OMM-0001
+document/ALP-M19-10HAN-ME-OMM-0001
+document/ALP-M20-00SGA-ME-OMM-0001
+document/ALP-M21-00SMA-ME-OMM-0001
+mdl_rule/DL-CM-OPR
+mdl_rule/DL-V-OMM</t>
         </is>
       </c>
       <c r="K146" s="4" t="inlineStr">
@@ -8165,7 +10053,8 @@
       <c r="I147" s="4" t="inlineStr"/>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CM-PLN-0002</t>
+          <t>document/ALP-EPC-00000-CM-OMM-0002
+document/ALP-EPC-00000-CM-PLN-0002</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
@@ -8215,7 +10104,52 @@
       <c r="I148" s="4" t="inlineStr"/>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CM-LST-0002</t>
+          <t>document/ALP-E01-00ACA-ME-LST-0001
+document/ALP-E02-10BBT-ME-LST-0001
+document/ALP-E03-00BBA-ME-LST-0001
+document/ALP-E04-00BFT-ME-LST-0001
+document/ALP-E05-00BFA-ME-LST-0001
+document/ALP-E06-00XJA-ME-LST-0001
+document/ALP-E07-00BRA-ME-LST-0001
+document/ALP-E10-00BXA-ME-LST-0001
+document/ALP-E11-00000-ME-LST-0001
+document/ALP-EPC-00000-CM-LST-0002
+document/ALP-EPC-00000-CM-LST-0004
+document/ALP-H01-00SAA-ME-LST-0001
+document/ALP-I01-00CJA-ME-LST-0001
+document/ALP-I02-00CQA-ME-LST-0001
+document/ALP-I03-00QUA-ME-LST-0001
+document/ALP-I06-00SGY-ME-LST-0001
+document/ALP-I07-00CYA-ME-LST-0001
+document/ALP-I08-00CJG-ME-LST-0001
+document/ALP-I09-00CKA-ME-LST-0001
+document/ALP-IEC-10BAT-ME-LST-0001
+document/ALP-IEC-10HAA-ME-LST-0001
+document/ALP-IEC-10MBA-ME-LST-0001
+document/ALP-IEC-10MBY-ME-LST-0001
+document/ALP-IEC-10MKA-ME-LST-0001
+document/ALP-IEC-20MAA-ME-LST-0001
+document/ALP-M01-10LAC-ME-LST-0001
+document/ALP-M02-20LCB-ME-LST-0001
+document/ALP-M03-00PAC-ME-LST-0001
+document/ALP-M04-00PAA-ME-LST-0001
+document/ALP-M05-00PBA-ME-LST-0001
+document/ALP-M06-00PAH-ME-LST-0001
+document/ALP-M07-00PGA-ME-LST-0001
+document/ALP-M08-00QEA-ME-LST-0001
+document/ALP-M09-00QHA-ME-LST-0001
+document/ALP-M10-00QJA-ME-LST-0001
+document/ALP-M11-00QCA-ME-LST-0001
+document/ALP-M12-00GBA-ME-LST-0001
+document/ALP-M13-00GHA-ME-LST-0001
+document/ALP-M14-00GNA-ME-LST-0001
+document/ALP-M15-00EKA-ME-LST-0001
+document/ALP-M16-00EGA-ME-LST-0001
+document/ALP-M18-10HSB-ME-LST-0001
+document/ALP-M19-10HAN-ME-LST-0001
+document/ALP-M20-00SGA-ME-LST-0001
+document/ALP-M21-00SMA-ME-LST-0001
+mdl_rule/DL-V-SPL</t>
         </is>
       </c>
       <c r="K148" s="4" t="inlineStr">
@@ -8570,7 +10504,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T15:06:23Z by SETUP | data 7cb6f7f6cb17ec93</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T17:23:32Z by SETUP | data 9c5db87d3bb3d7c9</t>
         </is>
       </c>
     </row>
@@ -9817,7 +11751,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T15:06:23Z by SETUP | data 7cb6f7f6cb17ec93</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T17:23:32Z by SETUP | data 9c5db87d3bb3d7c9</t>
         </is>
       </c>
     </row>
@@ -13603,7 +15537,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T15:06:23Z by SETUP | data 7cb6f7f6cb17ec93</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T17:23:32Z by SETUP | data 9c5db87d3bb3d7c9</t>
         </is>
       </c>
     </row>

--- a/output/requirements_matrix/ALP_requirements_matrix.xlsx
+++ b/output/requirements_matrix/ALP_requirements_matrix.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T17:23:32Z by SETUP | data 9c5db87d3bb3d7c9</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T18:43:04Z by SETUP | data 320a8d5c2b38b7e8</t>
         </is>
       </c>
     </row>
@@ -646,6 +646,7 @@
       <c r="J6" s="5" t="inlineStr">
         <is>
           <t>document/ALP-EPC-00000-GE-DBR-0001
+document/ALP-EPC-00000-PR-DBR-0001
 document/ALP-EPC-00000-PR-PFD-0002
 document/ALP-EPC-00EGA-ME-CAL-0001
 document/ALP-EPC-00EGA-PI-ISO-0001
@@ -859,6 +860,8 @@
 document/ALP-EPC-20MAN-PR-SDS-0001
 document/ALP-EPC-20UMB-PI-LAY-0001
 document/ALP-EPC-20UMB-PI-PPL-0001
+mdl_rule/DL-DBR-GE
+mdl_rule/DL-DBR-PR
 mdl_rule/DL-ME-CAL
 mdl_rule/DL-PI-ISO
 mdl_rule/DL-PI-LAY
@@ -1569,7 +1572,9 @@
           <t>design_parameter/DP-CASE-0001
 design_parameter/DP-OWNR-0044
 document/ALP-EPC-00000-CV-RPT-0003
-document/ALP-EPC-00000-GE-DBR-0001</t>
+document/ALP-EPC-00000-GE-DBR-0001
+document/ALP-EPC-00000-PR-DBR-0001
+mdl_rule/DL-DBR-PR</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1947,8 +1952,10 @@
         <is>
           <t>design_parameter/DP-CASE-0003
 document/ALP-EPC-00000-EL-CAL-0005
+document/ALP-EPC-00000-ME-DBR-0001
 document/ALP-EPC-00000-ME-RPT-0002
 document/ALP-EPC-00000-ME-SPC-0002
+mdl_rule/DL-DBR-ME
 mr/MR-EL-010
 mr/MR-ME-022</t>
         </is>
@@ -5627,7 +5634,8 @@
       <c r="I91" s="4" t="inlineStr"/>
       <c r="J91" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00EGA-ME-DSH-0001
+          <t>document/ALP-EPC-00000-ME-DBR-0001
+document/ALP-EPC-00EGA-ME-DSH-0001
 document/ALP-EPC-00EGA-ME-DSH-0002
 document/ALP-EPC-00EGA-ME-DSH-0003
 document/ALP-EPC-00EGA-ME-DSH-0004
@@ -5715,6 +5723,7 @@
 document/ALP-EPC-10LAC-ME-DSH-0001
 document/ALP-EPC-10LAC-PR-SDS-0001
 document/ALP-EPC-20LCB-ME-DSH-0001
+mdl_rule/DL-DBR-ME
 mdl_rule/DL-ME-DSH
 mr/MR-PI-006</t>
         </is>
@@ -6011,7 +6020,8 @@
       <c r="I96" s="4" t="inlineStr"/>
       <c r="J96" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00SAA-HV-SDS-0001
+          <t>document/ALP-EPC-00000-HV-DBR-0001
+document/ALP-EPC-00SAA-HV-SDS-0001
 document/ALP-EPC-00UAC-HV-GAD-0001
 document/ALP-EPC-00UBA-HV-GAD-0001
 document/ALP-EPC-00UBA-HV-GAD-0002
@@ -6026,6 +6036,7 @@
 document/ALP-EPC-10UMA-HV-GAD-0001
 document/ALP-EPC-10UMA-HV-GAD-0002
 document/ALP-EPC-20UMB-HV-GAD-0001
+mdl_rule/DL-DBR-HV
 mdl_rule/DL-HV-HVL
 mdl_rule/DL-HV-SRV</t>
         </is>
@@ -6330,7 +6341,8 @@
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-EL-RPT-0001
+          <t>document/ALP-EPC-00000-EL-DBR-0001
+document/ALP-EPC-00000-EL-RPT-0001
 document/ALP-EPC-00ACA-EL-DSH-0001
 document/ALP-EPC-00BBA-EL-DSH-0001
 document/ALP-EPC-00BBA-EL-SLD-0001
@@ -6357,6 +6369,7 @@
 document/ALP-EPC-00XJA-EL-DSH-0001
 document/ALP-EPC-10BBT-EL-DSH-0001
 document/ALP-EPC-20BBT-EL-DSH-0001
+mdl_rule/DL-DBR-EL
 mdl_rule/DL-EL-DSH
 mdl_rule/DL-EL-WLV
 mdl_rule/DL-EL-WMV</t>
@@ -6728,7 +6741,8 @@
       <c r="I108" s="4" t="inlineStr"/>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-IC-SPC-0005
+          <t>document/ALP-EPC-00000-IC-DBR-0001
+document/ALP-EPC-00000-IC-SPC-0005
 document/ALP-EPC-00000-IC-TST-0001
 document/ALP-EPC-00ACA-IC-DSH-0001
 document/ALP-EPC-00CJA-IC-BLK-0001
@@ -6862,6 +6876,7 @@
 document/ALP-EPC-20UMB-IC-HUP-0001
 document/ALP-EPC-20UMB-IC-LOP-0001
 document/ALP-EPC-20UMB-IC-LOP-0002
+mdl_rule/DL-DBR-IC
 mdl_rule/DL-IC-BLK
 mdl_rule/DL-IC-DSH
 mdl_rule/DL-IC-HUP
@@ -7478,6 +7493,7 @@
       <c r="J116" s="5" t="inlineStr">
         <is>
           <t>document/ALP-EPC-00000-CV-CAL-0001
+document/ALP-EPC-00000-CV-DBR-0001
 document/ALP-EPC-00000-CV-TRP-0001
 document/ALP-EPC-00000-CV-TST-0001
 document/ALP-EPC-00UAC-CV-CAL-0001
@@ -7542,7 +7558,8 @@
 mdl_rule/DL-CV-CAL
 mdl_rule/DL-CV-EFD
 mdl_rule/DL-CV-FND
-mdl_rule/DL-CV-PIL</t>
+mdl_rule/DL-CV-PIL
+mdl_rule/DL-DBR-CV</t>
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr">
@@ -8110,7 +8127,9 @@
       <c r="J124" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-CASE-0044
-document/ALP-EPC-00000-HS-STU-0001</t>
+document/ALP-EPC-00000-HS-DBR-0001
+document/ALP-EPC-00000-HS-STU-0001
+mdl_rule/DL-DBR-HS</t>
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr">
@@ -8247,6 +8266,7 @@
 document/ALP-E12-00000-GE-MOS-0004
 document/ALP-E12-00000-GE-MOS-0005
 document/ALP-E12-00000-GE-MOS-0006
+document/ALP-EPC-00000-HS-DBR-0001
 document/ALP-EPC-00000-HS-PLN-0001
 document/ALP-EPC-00000-HS-PLN-0002
 document/ALP-EPC-00000-HS-PLN-0005
@@ -8287,6 +8307,7 @@
 document/ALP-S02-10HNE-GE-MOS-0004
 document/ALP-S02-10HNE-GE-MOS-0005
 document/ALP-S02-10HNE-GE-MOS-0006
+mdl_rule/DL-DBR-HS
 mdl_rule/DL-S-MOS
 permit/PMT-010</t>
         </is>
@@ -8394,10 +8415,12 @@
       <c r="I128" s="4" t="inlineStr"/>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-HS-HAZ-0002
+          <t>document/ALP-EPC-00000-HS-DBR-0001
+document/ALP-EPC-00000-HS-HAZ-0002
 document/ALP-EPC-00000-HS-HAZ-0010
 document/ALP-EPC-00000-HS-RPT-0004
-document/ALP-EPC-00000-PR-RPT-0003</t>
+document/ALP-EPC-00000-PR-RPT-0003
+mdl_rule/DL-DBR-HS</t>
         </is>
       </c>
       <c r="K128" s="4" t="inlineStr">
@@ -8773,6 +8796,9 @@
 document/ALP-M24-00UZF-GE-ITP-0001
 document/ALP-S01-00000-GE-ITP-0001
 document/ALP-S02-10HNE-GE-ITP-0001
+gate_rule/G-PRC-ENQ
+gate_rule/G-PRC-FAB
+gate_rule/G-PRC-PO
 mdl_rule/DL-MR-ITP
 mdl_rule/DL-MR-MRQ
 mdl_rule/DL-MR-SPC
@@ -8914,6 +8940,8 @@
 document/ALP-M20-00SGA-ME-TST-0001
 document/ALP-M21-00SMA-ME-TRP-0001
 document/ALP-M21-00SMA-ME-TST-0001
+gate_rule/G-PRC-FAT
+gate_rule/G-PRC-SHP
 mdl_rule/DL-V-FAT
 mdl_rule/DL-V-FTR</t>
         </is>
@@ -9045,6 +9073,7 @@
 document/ALP-P05-00000-ME-MDB-0001
 document/ALP-P06-00000-ME-MDB-0001
 document/ALP-P07-00000-ME-MDB-0001
+gate_rule/G-PRC-SHP
 mdl_rule/DL-PR-PSV
 mdl_rule/DL-V-MDB
 mr/MR-PI-007</t>
@@ -9200,6 +9229,7 @@
 document/ALP-EPC-00GMA-CM-MDB-0001
 document/ALP-EPC-00GNA-CM-CMP-0001
 document/ALP-EPC-00GNA-CM-MDB-0001
+document/ALP-EPC-00GQA-CM-MDB-0001
 document/ALP-EPC-00GUA-CM-CMP-0001
 document/ALP-EPC-00GUA-CM-MDB-0001
 document/ALP-EPC-00LBG-CM-CMP-0001
@@ -9242,12 +9272,18 @@
 document/ALP-EPC-00SMA-CM-MDB-0001
 document/ALP-EPC-00XJA-CM-CMP-0001
 document/ALP-EPC-00XJA-CM-MDB-0001
+document/ALP-EPC-10BAA-CM-MDB-0001
+document/ALP-EPC-10BAC-CM-MDB-0001
+document/ALP-EPC-10BAT-CM-MDB-0001
 document/ALP-EPC-10BBT-CM-CMP-0001
 document/ALP-EPC-10BBT-CM-MDB-0001
+document/ALP-EPC-10HAA-CM-MDB-0001
 document/ALP-EPC-10HAN-CM-CMP-0001
 document/ALP-EPC-10HAN-CM-MDB-0001
+document/ALP-EPC-10HNA-CM-MDB-0001
 document/ALP-EPC-10HNE-CM-CMP-0001
 document/ALP-EPC-10HNE-CM-MDB-0001
+document/ALP-EPC-10HSA-CM-MDB-0001
 document/ALP-EPC-10HSB-CM-CMP-0001
 document/ALP-EPC-10HSB-CM-MDB-0001
 document/ALP-EPC-10LAB-CM-CMP-0001
@@ -9266,20 +9302,49 @@
 document/ALP-EPC-10LBC-CM-MDB-0001
 document/ALP-EPC-10LBD-CM-CMP-0001
 document/ALP-EPC-10LBD-CM-MDB-0001
+document/ALP-EPC-10MBA-CM-MDB-0001
+document/ALP-EPC-10MBL-CM-MDB-0001
+document/ALP-EPC-10MBN-CM-MDB-0001
+document/ALP-EPC-10MBP-CM-MDB-0001
+document/ALP-EPC-10MBU-CM-MDB-0001
+document/ALP-EPC-10MBV-CM-MDB-0001
+document/ALP-EPC-10MBY-CM-MDB-0001
+document/ALP-EPC-10MKA-CM-MDB-0001
+document/ALP-EPC-10MKC-CM-MDB-0001
+document/ALP-EPC-10MKG-CM-MDB-0001
+document/ALP-EPC-20BAA-CM-MDB-0001
+document/ALP-EPC-20BAC-CM-MDB-0001
+document/ALP-EPC-20BAT-CM-MDB-0001
 document/ALP-EPC-20BBT-CM-CMP-0001
 document/ALP-EPC-20BBT-CM-MDB-0001
 document/ALP-EPC-20LCA-CM-CMP-0001
 document/ALP-EPC-20LCA-CM-MDB-0001
 document/ALP-EPC-20LCB-CM-CMP-0001
 document/ALP-EPC-20LCB-CM-MDB-0001
+document/ALP-EPC-20MAA-CM-MDB-0001
+document/ALP-EPC-20MAB-CM-MDB-0001
+document/ALP-EPC-20MAG-CM-MDB-0001
+document/ALP-EPC-20MAJ-CM-MDB-0001
 document/ALP-EPC-20MAN-CM-CMP-0001
 document/ALP-EPC-20MAN-CM-MDB-0001
+document/ALP-EPC-20MAV-CM-MDB-0001
+document/ALP-EPC-20MAW-CM-MDB-0001
+document/ALP-EPC-20MAX-CM-MDB-0001
+document/ALP-EPC-20MAY-CM-MDB-0001
+document/ALP-EPC-20MKA-CM-MDB-0001
+document/ALP-EPC-20MKC-CM-MDB-0001
 document/ALP-IEC-10BAT-CM-CMP-0001
 document/ALP-IEC-10HAA-CM-CMP-0001
 document/ALP-IEC-10MBA-CM-CMP-0001
 document/ALP-IEC-10MBY-CM-CMP-0001
 document/ALP-IEC-10MKA-CM-CMP-0001
 document/ALP-IEC-20MAA-CM-CMP-0001
+gate_rule/G-COM-MC-EL
+gate_rule/G-COM-MC-FF
+gate_rule/G-COM-MC-WS
+gate_rule/G-COM-SC-EL
+gate_rule/G-COM-SC-FF
+gate_rule/G-COM-SC-WS
 mdl_rule/DL-CM-CMP
 mdl_rule/DL-CM-TOD
 mdl_rule/DL-V-CMP</t>
@@ -9452,7 +9517,8 @@
       <c r="J138" s="5" t="inlineStr">
         <is>
           <t>document/ALP-EPC-00000-CM-CMP-0002
-document/ALP-EPC-00000-CM-TRP-0002</t>
+document/ALP-EPC-00000-CM-TRP-0002
+gate_rule/G-OWN-TOC</t>
         </is>
       </c>
       <c r="K138" s="4" t="inlineStr">
@@ -9747,7 +9813,8 @@
       <c r="I143" s="4" t="inlineStr"/>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-GE-PRC-0002</t>
+          <t>document/ALP-EPC-00000-GE-PRC-0002
+gate_rule/G-OWN-BDP</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
@@ -9849,7 +9916,8 @@
         <is>
           <t>document/ALP-EPC-00000-GE-LST-0005
 document/ALP-EPC-00000-GE-PRC-0003
-document/ALP-EPC-00000-PI-M3D-0004</t>
+document/ALP-EPC-00000-PI-M3D-0004
+gate_rule/G-OPS-AB</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
@@ -10002,6 +10070,12 @@
 document/ALP-M19-10HAN-ME-OMM-0001
 document/ALP-M20-00SGA-ME-OMM-0001
 document/ALP-M21-00SMA-ME-OMM-0001
+gate_rule/G-COM-SC-EL
+gate_rule/G-COM-SC-FF
+gate_rule/G-COM-SC-WS
+gate_rule/G-OPS-HO-EL
+gate_rule/G-OPS-HO-FF
+gate_rule/G-OPS-HO-WS
 mdl_rule/DL-CM-OPR
 mdl_rule/DL-V-OMM</t>
         </is>
@@ -10149,6 +10223,7 @@
 document/ALP-M19-10HAN-ME-LST-0001
 document/ALP-M20-00SGA-ME-LST-0001
 document/ALP-M21-00SMA-ME-LST-0001
+gate_rule/G-OWN-TO
 mdl_rule/DL-V-SPL</t>
         </is>
       </c>
@@ -10504,7 +10579,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T17:23:32Z by SETUP | data 9c5db87d3bb3d7c9</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T18:43:04Z by SETUP | data 320a8d5c2b38b7e8</t>
         </is>
       </c>
     </row>
@@ -11751,7 +11826,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T17:23:32Z by SETUP | data 9c5db87d3bb3d7c9</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T18:43:04Z by SETUP | data 320a8d5c2b38b7e8</t>
         </is>
       </c>
     </row>
@@ -15537,7 +15612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T17:23:32Z by SETUP | data 9c5db87d3bb3d7c9</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T18:43:04Z by SETUP | data 320a8d5c2b38b7e8</t>
         </is>
       </c>
     </row>

--- a/output/requirements_matrix/ALP_requirements_matrix.xlsx
+++ b/output/requirements_matrix/ALP_requirements_matrix.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T18:43:04Z by SETUP | data 320a8d5c2b38b7e8</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T19:01:35Z by EPCE | data 6da7af5ec0e008bd</t>
         </is>
       </c>
     </row>
@@ -10579,7 +10579,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T18:43:04Z by SETUP | data 320a8d5c2b38b7e8</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T19:01:35Z by EPCE | data 6da7af5ec0e008bd</t>
         </is>
       </c>
     </row>
@@ -11826,7 +11826,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T18:43:04Z by SETUP | data 320a8d5c2b38b7e8</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T19:01:35Z by EPCE | data 6da7af5ec0e008bd</t>
         </is>
       </c>
     </row>
@@ -15612,7 +15612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T18:43:04Z by SETUP | data 320a8d5c2b38b7e8</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T19:01:35Z by EPCE | data 6da7af5ec0e008bd</t>
         </is>
       </c>
     </row>

--- a/output/requirements_matrix/ALP_requirements_matrix.xlsx
+++ b/output/requirements_matrix/ALP_requirements_matrix.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T19:01:35Z by EPCE | data 6da7af5ec0e008bd</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-29T02:55:42Z by SETUP | data 8d834179811a9cac</t>
         </is>
       </c>
     </row>
@@ -10579,7 +10579,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T19:01:35Z by EPCE | data 6da7af5ec0e008bd</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-29T02:55:42Z by SETUP | data 8d834179811a9cac</t>
         </is>
       </c>
     </row>
@@ -11826,7 +11826,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T19:01:35Z by EPCE | data 6da7af5ec0e008bd</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-29T02:55:42Z by SETUP | data 8d834179811a9cac</t>
         </is>
       </c>
     </row>
@@ -15612,7 +15612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-28T19:01:35Z by EPCE | data 6da7af5ec0e008bd</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-29T02:55:42Z by SETUP | data 8d834179811a9cac</t>
         </is>
       </c>
     </row>

--- a/output/requirements_matrix/ALP_requirements_matrix.xlsx
+++ b/output/requirements_matrix/ALP_requirements_matrix.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-29T02:55:42Z by SETUP | data 8d834179811a9cac</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-29T03:45:18Z by SETUP | data 2b54722a770c3045</t>
         </is>
       </c>
     </row>
@@ -925,6 +925,13 @@
           <t>design_parameter/DP-CASE-0034
 design_parameter/DP-CASE-0035
 design_parameter/DP-CASE-0036
+doc_clause/DC-EPCE-0439
+doc_clause/DC-EPCE-0442
+doc_clause/DC-EPCE-0445
+doc_clause/DC-EPCE-0446
+doc_clause/DC-EPCE-0595
+doc_clause/DC-EPCE-0601
+doc_clause/DC-EPCE-0640
 document/ALP-EPC-00000-GE-DBR-0001
 document/ALP-EPC-00000-PR-RPT-0004
 document/ALP-EPC-00000-PR-STU-0002</t>
@@ -1081,12 +1088,21 @@
       <c r="I10" s="4" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-GE-PRC-0001
+          <t>doc_clause/DC-EPCE-0080
+doc_clause/DC-EPCE-0131
+doc_clause/DC-EPCE-0143
+doc_clause/DC-EPCE-0197
+doc_clause/DC-EPCE-0243
+document/ALP-EPC-00000-GE-PRC-0001
 equipment/00ACA10
 equipment/00BBA10
 equipment/00BBA20
 equipment/00BFA10
+equipment/00BFA11
+equipment/00BFA12
 equipment/00BFA20
+equipment/00BFA21
+equipment/00BFA22
 equipment/00BFA30
 equipment/00BFA40
 equipment/00BFA50
@@ -1097,6 +1113,8 @@
 equipment/00BFT20
 equipment/00BFT30
 equipment/00BFT40
+equipment/00BFT70
+equipment/00BFT80
 equipment/00BMA10
 equipment/00BMA20
 equipment/00BRA10
@@ -1359,7 +1377,8 @@
       <c r="I11" s="4" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-GE-LST-0001
+          <t>doc_clause/DC-EPCE-0013
+document/ALP-EPC-00000-GE-LST-0001
 permit/PMT-005</t>
         </is>
       </c>
@@ -1627,6 +1646,7 @@
           <t>design_parameter/DP-CASE-0007
 design_parameter/DP-CASE-0008
 design_parameter/DP-CASE-0009
+doc_clause/DC-EPCE-0348
 document/ALP-EPC-00000-GE-DBR-0001</t>
         </is>
       </c>
@@ -1741,6 +1761,12 @@
       <c r="J18" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-CASE-0013
+doc_clause/DC-EPCE-0444
+doc_clause/DC-EPCE-0502
+doc_clause/DC-EPCE-0504
+doc_clause/DC-EPCE-0506
+doc_clause/DC-EPCE-0507
+doc_clause/DC-EPCE-0527
 document/ALP-EPC-00PAA-PR-SDS-0001</t>
         </is>
       </c>
@@ -1794,6 +1820,9 @@
           <t>design_parameter/DP-CASE-0004
 design_parameter/DP-CASE-0005
 design_parameter/DP-CASE-0006
+doc_clause/DC-EPCE-0271
+doc_clause/DC-EPCE-0272
+doc_clause/DC-EPCE-0328
 document/ALP-EPC-00000-GE-DBR-0001</t>
         </is>
       </c>
@@ -1849,6 +1878,12 @@
       <c r="J20" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-CASE-0002
+doc_clause/DC-EPCE-0246
+doc_clause/DC-EPCE-0276
+doc_clause/DC-EPCE-0277
+doc_clause/DC-EPCE-0279
+doc_clause/DC-EPCE-0280
+doc_clause/DC-EPCE-0316
 document/ALP-EPC-00000-CV-DBR-0001
 document/ALP-EPC-00000-CV-STU-0001</t>
         </is>
@@ -1900,7 +1935,18 @@
       <c r="I21" s="4" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CV-RPT-0001</t>
+          <t>doc_clause/DC-EPCE-0093
+doc_clause/DC-EPCE-0246
+doc_clause/DC-EPCE-0251
+doc_clause/DC-EPCE-0252
+doc_clause/DC-EPCE-0253
+doc_clause/DC-EPCE-0282
+doc_clause/DC-EPCE-0318
+doc_clause/DC-EPCE-0319
+doc_clause/DC-EPCE-0320
+doc_clause/DC-EPCE-0322
+doc_clause/DC-EPCE-0327
+document/ALP-EPC-00000-CV-RPT-0001</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -1951,6 +1997,23 @@
       <c r="J22" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-CASE-0003
+doc_clause/DC-EPCE-0008
+doc_clause/DC-EPCE-0139
+doc_clause/DC-EPCE-0307
+doc_clause/DC-EPCE-0340
+doc_clause/DC-EPCE-0350
+doc_clause/DC-EPCE-0377
+doc_clause/DC-EPCE-0388
+doc_clause/DC-EPCE-0443
+doc_clause/DC-EPCE-0477
+doc_clause/DC-EPCE-0494
+doc_clause/DC-EPCE-0497
+doc_clause/DC-EPCE-0499
+doc_clause/DC-EPCE-0525
+doc_clause/DC-EPCE-0548
+doc_clause/DC-EPCE-0550
+doc_clause/DC-EPCE-0554
+doc_clause/DC-EPCE-0594
 document/ALP-EPC-00000-EL-CAL-0005
 document/ALP-EPC-00000-ME-DBR-0001
 document/ALP-EPC-00000-ME-RPT-0002
@@ -2007,7 +2070,12 @@
       <c r="I23" s="4" t="inlineStr"/>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00UZC-CV-CVL-0001</t>
+          <t>design_parameter/DP-EPCE-0015
+doc_clause/DC-EPCE-0256
+doc_clause/DC-EPCE-0257
+doc_clause/DC-EPCE-0259
+doc_clause/DC-EPCE-0260
+document/ALP-EPC-00UZC-CV-CVL-0001</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -2064,6 +2132,8 @@
           <t>design_parameter/DP-OWNR-0005
 design_parameter/DP-OWNR-0007
 design_parameter/DP-OWNR-0008
+doc_clause/DC-EPCE-0063
+doc_clause/DC-EPCE-0118
 document/ALP-EPC-00ACA-EL-SPC-0001</t>
         </is>
       </c>
@@ -2168,6 +2238,10 @@
       <c r="J26" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-OWNR-0009
+doc_clause/DC-EPCE-0098
+doc_clause/DC-EPCE-0099
+doc_clause/DC-EPCE-0100
+doc_clause/DC-EPCE-0126
 document/ALP-EPC-00000-EL-STU-0004</t>
         </is>
       </c>
@@ -3134,6 +3208,8 @@
           <t>design_parameter/DP-CASE-0037
 design_parameter/DP-CASE-0038
 design_parameter/DP-CASE-0039
+doc_clause/DC-EPCE-0140
+doc_clause/DC-EPCE-0153
 document/ALP-IEC-10MBY-IC-CNR-0001</t>
         </is>
       </c>
@@ -3197,6 +3273,8 @@
       <c r="J44" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-CASE-0032
+doc_clause/DC-EPCE-0140
+doc_clause/DC-EPCE-0154
 document/ALP-EPC-00000-PR-RPT-0002
 document/ALP-IEC-10MBY-IC-CNR-0001</t>
         </is>
@@ -3261,6 +3339,7 @@
       <c r="J45" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-CASE-0033
+doc_clause/DC-EPCE-0154
 document/ALP-EPC-00000-PR-HMB-0001</t>
         </is>
       </c>
@@ -3316,6 +3395,12 @@
       <c r="J46" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-CASE-0026
+doc_clause/DC-EPCE-0006
+doc_clause/DC-EPCE-0048
+doc_clause/DC-EPCE-0049
+doc_clause/DC-EPCE-0088
+doc_clause/DC-EPCE-0127
+doc_clause/DC-EPCE-0154
 document/ALP-EPC-00000-EL-STU-0006</t>
         </is>
       </c>
@@ -3367,6 +3452,8 @@
       <c r="J47" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-CASE-0027
+doc_clause/DC-EPCE-0088
+doc_clause/DC-EPCE-0127
 document/ALP-EPC-00000-EL-STU-0006</t>
         </is>
       </c>
@@ -3417,7 +3504,10 @@
       <c r="I48" s="4" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-IC-CNR-0001</t>
+          <t>doc_clause/DC-EPCE-0040
+doc_clause/DC-EPCE-0048
+doc_clause/DC-EPCE-0127
+document/ALP-EPC-00000-IC-CNR-0001</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
@@ -3468,6 +3558,8 @@
       <c r="J49" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-CASE-0031
+doc_clause/DC-EPCE-0038
+doc_clause/DC-EPCE-0039
 document/ALP-EPC-00000-EL-LST-0001</t>
         </is>
       </c>
@@ -3869,7 +3961,10 @@
       <c r="I57" s="4" t="inlineStr"/>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-IEC-10MBY-IC-BLK-0001</t>
+          <t>doc_clause/DC-EPCE-0137
+doc_clause/DC-EPCE-0199
+doc_clause/DC-EPCE-0221
+document/ALP-IEC-10MBY-IC-BLK-0001</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
@@ -4333,7 +4428,9 @@
       <c r="I66" s="4" t="inlineStr"/>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00QJA-PR-SDS-0001</t>
+          <t>doc_clause/DC-EPCE-0487
+doc_clause/DC-EPCE-0488
+document/ALP-EPC-00QJA-PR-SDS-0001</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -4807,7 +4904,8 @@
       <c r="I75" s="4" t="inlineStr"/>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-20MAN-PR-SDS-0001</t>
+          <t>doc_clause/DC-EPCE-0207
+document/ALP-EPC-20MAN-PR-SDS-0001</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
@@ -4857,7 +4955,8 @@
       <c r="I76" s="4" t="inlineStr"/>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00QUA-PR-SDS-0001</t>
+          <t>doc_clause/DC-EPCE-0198
+document/ALP-EPC-00QUA-PR-SDS-0001</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
@@ -5060,7 +5159,11 @@
       <c r="I80" s="4" t="inlineStr"/>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00PAC-PR-SDS-0001</t>
+          <t>doc_clause/DC-EPCE-0455
+doc_clause/DC-EPCE-0461
+doc_clause/DC-EPCE-0493
+doc_clause/DC-EPCE-0506
+document/ALP-EPC-00PAC-PR-SDS-0001</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -5634,7 +5737,9 @@
       <c r="I91" s="4" t="inlineStr"/>
       <c r="J91" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-ME-DBR-0001
+          <t>doc_clause/DC-EPCE-0455
+doc_clause/DC-EPCE-0456
+document/ALP-EPC-00000-ME-DBR-0001
 document/ALP-EPC-00EGA-ME-DSH-0001
 document/ALP-EPC-00EGA-ME-DSH-0002
 document/ALP-EPC-00EGA-ME-DSH-0003
@@ -5775,7 +5880,9 @@
       <c r="I92" s="4" t="inlineStr"/>
       <c r="J92" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-20LCB-PR-SDS-0001</t>
+          <t>doc_clause/DC-EPCE-0455
+doc_clause/DC-EPCE-0456
+document/ALP-EPC-20LCB-PR-SDS-0001</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
@@ -5825,7 +5932,8 @@
       <c r="I93" s="4" t="inlineStr"/>
       <c r="J93" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00QEA-PR-SDS-0001</t>
+          <t>doc_clause/DC-EPCE-0464
+document/ALP-EPC-00QEA-PR-SDS-0001</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
@@ -5929,7 +6037,13 @@
       <c r="I95" s="4" t="inlineStr"/>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CM-TRP-0007
+          <t>doc_clause/DC-EPCE-0384
+doc_clause/DC-EPCE-0385
+doc_clause/DC-EPCE-0386
+doc_clause/DC-EPCE-0387
+doc_clause/DC-EPCE-0425
+doc_clause/DC-EPCE-0428
+document/ALP-EPC-00000-CM-TRP-0007
 document/ALP-EPC-00000-HS-HAZ-0009
 document/ALP-EPC-00000-HS-STU-0003
 document/ALP-EPC-00SGA-PR-CAL-0001
@@ -6020,7 +6134,42 @@
       <c r="I96" s="4" t="inlineStr"/>
       <c r="J96" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-HV-DBR-0001
+          <t>doc_clause/DC-EPCE-0105
+doc_clause/DC-EPCE-0117
+doc_clause/DC-EPCE-0239
+doc_clause/DC-EPCE-0343
+doc_clause/DC-EPCE-0344
+doc_clause/DC-EPCE-0345
+doc_clause/DC-EPCE-0351
+doc_clause/DC-EPCE-0352
+doc_clause/DC-EPCE-0353
+doc_clause/DC-EPCE-0354
+doc_clause/DC-EPCE-0355
+doc_clause/DC-EPCE-0356
+doc_clause/DC-EPCE-0357
+doc_clause/DC-EPCE-0358
+doc_clause/DC-EPCE-0359
+doc_clause/DC-EPCE-0360
+doc_clause/DC-EPCE-0361
+doc_clause/DC-EPCE-0362
+doc_clause/DC-EPCE-0363
+doc_clause/DC-EPCE-0364
+doc_clause/DC-EPCE-0365
+doc_clause/DC-EPCE-0366
+doc_clause/DC-EPCE-0367
+doc_clause/DC-EPCE-0368
+doc_clause/DC-EPCE-0369
+doc_clause/DC-EPCE-0370
+doc_clause/DC-EPCE-0372
+doc_clause/DC-EPCE-0373
+doc_clause/DC-EPCE-0374
+doc_clause/DC-EPCE-0375
+doc_clause/DC-EPCE-0376
+doc_clause/DC-EPCE-0378
+doc_clause/DC-EPCE-0389
+doc_clause/DC-EPCE-0390
+doc_clause/DC-EPCE-0419
+document/ALP-EPC-00000-HV-DBR-0001
 document/ALP-EPC-00SAA-HV-SDS-0001
 document/ALP-EPC-00UAC-HV-GAD-0001
 document/ALP-EPC-00UBA-HV-GAD-0001
@@ -6191,6 +6340,15 @@
         <is>
           <t>design_parameter/DP-CASE-0024
 design_parameter/DP-CASE-0025
+doc_clause/DC-EPCE-0001
+doc_clause/DC-EPCE-0002
+doc_clause/DC-EPCE-0006
+doc_clause/DC-EPCE-0010
+doc_clause/DC-EPCE-0017
+doc_clause/DC-EPCE-0031
+doc_clause/DC-EPCE-0085
+doc_clause/DC-EPCE-0118
+doc_clause/DC-EPCE-0121
 document/ALP-EPC-00ACA-EL-SPC-0001</t>
         </is>
       </c>
@@ -6241,7 +6399,12 @@
       <c r="I100" s="4" t="inlineStr"/>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-IEC-10MKA-EL-DSH-0001</t>
+          <t>doc_clause/DC-EPCE-0002
+doc_clause/DC-EPCE-0018
+doc_clause/DC-EPCE-0019
+doc_clause/DC-EPCE-0025
+doc_clause/DC-EPCE-0035
+document/ALP-IEC-10MKA-EL-DSH-0001</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
@@ -6291,7 +6454,9 @@
       <c r="I101" s="4" t="inlineStr"/>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-IEC-10BAT-EL-DSH-0001</t>
+          <t>doc_clause/DC-EPCE-0002
+doc_clause/DC-EPCE-0029
+document/ALP-IEC-10BAT-EL-DSH-0001</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
@@ -6341,7 +6506,20 @@
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-EL-DBR-0001
+          <t>doc_clause/DC-EPCE-0001
+doc_clause/DC-EPCE-0002
+doc_clause/DC-EPCE-0020
+doc_clause/DC-EPCE-0021
+doc_clause/DC-EPCE-0026
+doc_clause/DC-EPCE-0027
+doc_clause/DC-EPCE-0040
+doc_clause/DC-EPCE-0042
+doc_clause/DC-EPCE-0043
+doc_clause/DC-EPCE-0044
+doc_clause/DC-EPCE-0045
+doc_clause/DC-EPCE-0069
+doc_clause/DC-EPCE-0130
+document/ALP-EPC-00000-EL-DBR-0001
 document/ALP-EPC-00000-EL-RPT-0001
 document/ALP-EPC-00ACA-EL-DSH-0001
 document/ALP-EPC-00BBA-EL-DSH-0001
@@ -6422,7 +6600,24 @@
       <c r="I103" s="4" t="inlineStr"/>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-EL-CAL-0002
+          <t>doc_clause/DC-EPCE-0002
+doc_clause/DC-EPCE-0022
+doc_clause/DC-EPCE-0023
+doc_clause/DC-EPCE-0024
+doc_clause/DC-EPCE-0061
+doc_clause/DC-EPCE-0062
+doc_clause/DC-EPCE-0063
+doc_clause/DC-EPCE-0064
+doc_clause/DC-EPCE-0065
+doc_clause/DC-EPCE-0066
+doc_clause/DC-EPCE-0067
+doc_clause/DC-EPCE-0068
+doc_clause/DC-EPCE-0069
+doc_clause/DC-EPCE-0107
+doc_clause/DC-EPCE-0113
+doc_clause/DC-EPCE-0115
+doc_clause/DC-EPCE-0164
+document/ALP-EPC-00000-EL-CAL-0002
 document/ALP-EPC-00000-EL-CAL-0003
 document/ALP-EPC-00XJA-EL-SPC-0001</t>
         </is>
@@ -6474,7 +6669,20 @@
       <c r="I104" s="4" t="inlineStr"/>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-EL-LST-0003
+          <t>doc_clause/DC-EPCE-0025
+doc_clause/DC-EPCE-0060
+doc_clause/DC-EPCE-0068
+doc_clause/DC-EPCE-0081
+doc_clause/DC-EPCE-0082
+doc_clause/DC-EPCE-0083
+doc_clause/DC-EPCE-0084
+doc_clause/DC-EPCE-0085
+doc_clause/DC-EPCE-0086
+doc_clause/DC-EPCE-0087
+doc_clause/DC-EPCE-0091
+doc_clause/DC-EPCE-0121
+doc_clause/DC-EPCE-0125
+document/ALP-EPC-00000-EL-LST-0003
 document/ALP-EPC-00000-EL-STU-0002</t>
         </is>
       </c>
@@ -6525,7 +6733,17 @@
       <c r="I105" s="4" t="inlineStr"/>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-EL-STU-0003
+          <t>doc_clause/DC-EPCE-0092
+doc_clause/DC-EPCE-0093
+doc_clause/DC-EPCE-0094
+doc_clause/DC-EPCE-0095
+doc_clause/DC-EPCE-0096
+doc_clause/DC-EPCE-0097
+doc_clause/DC-EPCE-0098
+doc_clause/DC-EPCE-0106
+doc_clause/DC-EPCE-0126
+doc_clause/DC-EPCE-0186
+document/ALP-EPC-00000-EL-STU-0003
 document/ALP-EPC-00UAC-EL-ELY-0001
 document/ALP-EPC-00UAC-EL-ELY-0003
 document/ALP-EPC-00UBA-EL-ELY-0001
@@ -6611,7 +6829,13 @@
       <c r="I106" s="4" t="inlineStr"/>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-EL-BLK-0001
+          <t>doc_clause/DC-EPCE-0070
+doc_clause/DC-EPCE-0071
+doc_clause/DC-EPCE-0072
+doc_clause/DC-EPCE-0076
+doc_clause/DC-EPCE-0077
+doc_clause/DC-EPCE-0240
+document/ALP-EPC-00000-EL-BLK-0001
 document/ALP-EPC-00000-EL-BLK-0002
 document/ALP-EPC-00000-EL-CAL-0004
 document/ALP-EPC-00000-EL-SPC-0001
@@ -6690,7 +6914,8 @@
       <c r="I107" s="4" t="inlineStr"/>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-EL-SPC-0003
+          <t>doc_clause/DC-EPCE-0089
+document/ALP-EPC-00000-EL-SPC-0003
 document/ALP-EPC-00000-EL-TRP-0001</t>
         </is>
       </c>
@@ -6741,7 +6966,54 @@
       <c r="I108" s="4" t="inlineStr"/>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-IC-DBR-0001
+          <t>doc_clause/DC-EPCE-0091
+doc_clause/DC-EPCE-0132
+doc_clause/DC-EPCE-0133
+doc_clause/DC-EPCE-0144
+doc_clause/DC-EPCE-0145
+doc_clause/DC-EPCE-0146
+doc_clause/DC-EPCE-0147
+doc_clause/DC-EPCE-0148
+doc_clause/DC-EPCE-0149
+doc_clause/DC-EPCE-0150
+doc_clause/DC-EPCE-0151
+doc_clause/DC-EPCE-0156
+doc_clause/DC-EPCE-0158
+doc_clause/DC-EPCE-0159
+doc_clause/DC-EPCE-0160
+doc_clause/DC-EPCE-0161
+doc_clause/DC-EPCE-0162
+doc_clause/DC-EPCE-0163
+doc_clause/DC-EPCE-0164
+doc_clause/DC-EPCE-0165
+doc_clause/DC-EPCE-0166
+doc_clause/DC-EPCE-0168
+doc_clause/DC-EPCE-0169
+doc_clause/DC-EPCE-0170
+doc_clause/DC-EPCE-0180
+doc_clause/DC-EPCE-0181
+doc_clause/DC-EPCE-0182
+doc_clause/DC-EPCE-0183
+doc_clause/DC-EPCE-0184
+doc_clause/DC-EPCE-0187
+doc_clause/DC-EPCE-0188
+doc_clause/DC-EPCE-0191
+doc_clause/DC-EPCE-0197
+doc_clause/DC-EPCE-0202
+doc_clause/DC-EPCE-0207
+doc_clause/DC-EPCE-0209
+doc_clause/DC-EPCE-0210
+doc_clause/DC-EPCE-0211
+doc_clause/DC-EPCE-0212
+doc_clause/DC-EPCE-0213
+doc_clause/DC-EPCE-0214
+doc_clause/DC-EPCE-0215
+doc_clause/DC-EPCE-0216
+doc_clause/DC-EPCE-0217
+doc_clause/DC-EPCE-0226
+doc_clause/DC-EPCE-0239
+doc_clause/DC-EPCE-0242
+document/ALP-EPC-00000-IC-DBR-0001
 document/ALP-EPC-00000-IC-SPC-0005
 document/ALP-EPC-00000-IC-TST-0001
 document/ALP-EPC-00ACA-IC-DSH-0001
@@ -6935,7 +7207,15 @@
       <c r="I109" s="4" t="inlineStr"/>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-IC-DBR-0001
+          <t>doc_clause/DC-EPCE-0132
+doc_clause/DC-EPCE-0140
+doc_clause/DC-EPCE-0147
+doc_clause/DC-EPCE-0153
+doc_clause/DC-EPCE-0154
+doc_clause/DC-EPCE-0155
+doc_clause/DC-EPCE-0156
+doc_clause/DC-EPCE-0158
+document/ALP-EPC-00000-IC-DBR-0001
 document/ALP-EPC-00000-IC-LST-0002
 document/ALP-EPC-00ACA-IC-LOG-0001
 document/ALP-EPC-00BLA-IC-LOG-0001
@@ -7150,7 +7430,23 @@
       <c r="I110" s="4" t="inlineStr"/>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-HS-HAZ-0007
+          <t>doc_clause/DC-EPCE-0141
+doc_clause/DC-EPCE-0148
+doc_clause/DC-EPCE-0152
+doc_clause/DC-EPCE-0157
+doc_clause/DC-EPCE-0167
+doc_clause/DC-EPCE-0171
+doc_clause/DC-EPCE-0172
+doc_clause/DC-EPCE-0173
+doc_clause/DC-EPCE-0174
+doc_clause/DC-EPCE-0175
+doc_clause/DC-EPCE-0176
+doc_clause/DC-EPCE-0177
+doc_clause/DC-EPCE-0189
+doc_clause/DC-EPCE-0206
+doc_clause/DC-EPCE-0218
+doc_clause/DC-EPCE-0241
+document/ALP-EPC-00000-HS-HAZ-0007
 document/ALP-EPC-00000-IC-LST-0003
 document/ALP-EPC-00000-IC-SPC-0006
 document/ALP-EPC-00EGA-IC-CEM-0001
@@ -7231,7 +7527,14 @@
       <c r="I111" s="4" t="inlineStr"/>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00CQA-IC-SPC-0001
+          <t>doc_clause/DC-EPCE-0141
+doc_clause/DC-EPCE-0228
+doc_clause/DC-EPCE-0229
+doc_clause/DC-EPCE-0230
+doc_clause/DC-EPCE-0231
+doc_clause/DC-EPCE-0232
+doc_clause/DC-EPCE-0233
+document/ALP-EPC-00CQA-IC-SPC-0001
 document/ALP-EPC-00CQA-IC-TRP-0001
 permit/PMT-017</t>
         </is>
@@ -7283,7 +7586,14 @@
       <c r="I112" s="4" t="inlineStr"/>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00CKA-IC-BLK-0001</t>
+          <t>doc_clause/DC-EPCE-0142
+doc_clause/DC-EPCE-0179
+doc_clause/DC-EPCE-0190
+doc_clause/DC-EPCE-0200
+doc_clause/DC-EPCE-0234
+doc_clause/DC-EPCE-0235
+doc_clause/DC-EPCE-0236
+document/ALP-EPC-00CKA-IC-BLK-0001</t>
         </is>
       </c>
       <c r="K112" s="4" t="inlineStr">
@@ -7333,7 +7643,9 @@
       <c r="I113" s="4" t="inlineStr"/>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-IC-SPC-0007
+          <t>doc_clause/DC-EPCE-0237
+doc_clause/DC-EPCE-0238
+document/ALP-EPC-00000-IC-SPC-0007
 document/ALP-EPC-00CKA-IC-BLK-0001
 mr/MR-IC-009</t>
         </is>
@@ -7389,7 +7701,21 @@
       <c r="I114" s="4" t="inlineStr"/>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-IC-RPT-0002
+          <t>doc_clause/DC-EPCE-0141
+doc_clause/DC-EPCE-0145
+doc_clause/DC-EPCE-0146
+doc_clause/DC-EPCE-0149
+doc_clause/DC-EPCE-0176
+doc_clause/DC-EPCE-0181
+doc_clause/DC-EPCE-0219
+doc_clause/DC-EPCE-0220
+doc_clause/DC-EPCE-0221
+doc_clause/DC-EPCE-0222
+doc_clause/DC-EPCE-0223
+doc_clause/DC-EPCE-0224
+doc_clause/DC-EPCE-0232
+doc_clause/DC-EPCE-0235
+document/ALP-EPC-00000-IC-RPT-0002
 document/ALP-EPC-00000-IC-TRP-0001
 document/ALP-EPC-00000-IC-TST-0002
 mr/MR-IC-007</t>
@@ -7442,7 +7768,13 @@
       <c r="I115" s="4" t="inlineStr"/>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00CJA-IC-BLK-0001</t>
+          <t>doc_clause/DC-EPCE-0090
+doc_clause/DC-EPCE-0157
+doc_clause/DC-EPCE-0179
+doc_clause/DC-EPCE-0225
+doc_clause/DC-EPCE-0226
+doc_clause/DC-EPCE-0227
+document/ALP-EPC-00CJA-IC-BLK-0001</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
@@ -7492,7 +7824,13 @@
       <c r="I116" s="4" t="inlineStr"/>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CV-CAL-0001
+          <t>doc_clause/DC-EPCE-0247
+doc_clause/DC-EPCE-0281
+doc_clause/DC-EPCE-0286
+doc_clause/DC-EPCE-0287
+doc_clause/DC-EPCE-0292
+doc_clause/DC-EPCE-0325
+document/ALP-EPC-00000-CV-CAL-0001
 document/ALP-EPC-00000-CV-DBR-0001
 document/ALP-EPC-00000-CV-TRP-0001
 document/ALP-EPC-00000-CV-TST-0001
@@ -7609,7 +7947,10 @@
       <c r="I117" s="4" t="inlineStr"/>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CV-DBR-0001
+          <t>doc_clause/DC-EPCE-0244
+doc_clause/DC-EPCE-0339
+doc_clause/DC-EPCE-0341
+document/ALP-EPC-00000-CV-DBR-0001
 document/ALP-EPC-00UAC-CV-ARC-0001
 document/ALP-EPC-00UAC-SS-STL-0001
 document/ALP-EPC-00UBA-CV-ARC-0001
@@ -7678,7 +8019,13 @@
       <c r="I118" s="4" t="inlineStr"/>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-SS-SPC-0001
+          <t>doc_clause/DC-EPCE-0305
+doc_clause/DC-EPCE-0306
+doc_clause/DC-EPCE-0307
+doc_clause/DC-EPCE-0309
+doc_clause/DC-EPCE-0520
+doc_clause/DC-EPCE-0566
+document/ALP-EPC-00000-SS-SPC-0001
 document/ALP-EPC-00EGA-PI-SUP-0001
 document/ALP-EPC-00EGB-PI-SUP-0001
 document/ALP-EPC-00EGC-PI-SUP-0001
@@ -7806,7 +8153,17 @@
       <c r="I119" s="4" t="inlineStr"/>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CV-SPC-0001
+          <t>doc_clause/DC-EPCE-0261
+doc_clause/DC-EPCE-0293
+doc_clause/DC-EPCE-0294
+doc_clause/DC-EPCE-0295
+doc_clause/DC-EPCE-0296
+doc_clause/DC-EPCE-0298
+doc_clause/DC-EPCE-0299
+doc_clause/DC-EPCE-0301
+doc_clause/DC-EPCE-0303
+doc_clause/DC-EPCE-0321
+document/ALP-EPC-00000-CV-SPC-0001
 document/ALP-EPC-00UAC-CV-RBR-0001
 document/ALP-EPC-00UBA-CV-RBR-0001
 document/ALP-EPC-00UBF-CV-RBR-0001
@@ -7877,7 +8234,13 @@
       <c r="I120" s="4" t="inlineStr"/>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00GKA-PI-PPL-0001
+          <t>doc_clause/DC-EPCE-0328
+doc_clause/DC-EPCE-0329
+doc_clause/DC-EPCE-0330
+doc_clause/DC-EPCE-0331
+doc_clause/DC-EPCE-0332
+doc_clause/DC-EPCE-0333
+document/ALP-EPC-00GKA-PI-PPL-0001
 document/ALP-EPC-00GMA-PI-PPL-0001
 document/ALP-EPC-00PAB-PI-PPL-0001
 document/ALP-EPC-00SGA-PI-PPL-0001
@@ -7937,7 +8300,10 @@
       <c r="I121" s="4" t="inlineStr"/>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00UPA-CV-CVL-0001</t>
+          <t>doc_clause/DC-EPCE-0335
+doc_clause/DC-EPCE-0336
+doc_clause/DC-EPCE-0337
+document/ALP-EPC-00UPA-CV-CVL-0001</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
@@ -7991,7 +8357,29 @@
       <c r="I122" s="4" t="inlineStr"/>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-HS-PLN-0003
+          <t>doc_clause/DC-EPCE-0232
+doc_clause/DC-EPCE-0329
+doc_clause/DC-EPCE-0334
+doc_clause/DC-EPCE-0338
+doc_clause/DC-EPCE-0391
+doc_clause/DC-EPCE-0393
+doc_clause/DC-EPCE-0399
+doc_clause/DC-EPCE-0400
+doc_clause/DC-EPCE-0436
+doc_clause/DC-EPCE-0652
+doc_clause/DC-EPCE-0653
+doc_clause/DC-EPCE-0655
+doc_clause/DC-EPCE-0656
+doc_clause/DC-EPCE-0657
+doc_clause/DC-EPCE-0675
+doc_clause/DC-EPCE-0676
+doc_clause/DC-EPCE-0677
+doc_clause/DC-EPCE-0678
+doc_clause/DC-EPCE-0679
+doc_clause/DC-EPCE-0680
+doc_clause/DC-EPCE-0681
+doc_clause/DC-EPCE-0683
+document/ALP-EPC-00000-HS-PLN-0003
 document/ALP-EPC-00000-HS-PLN-0004
 document/ALP-EPC-00000-HS-RPT-0001
 document/ALP-EPC-00000-PR-LST-0003
@@ -8060,9 +8448,17 @@
           <t>design_parameter/DP-CASE-0040
 design_parameter/DP-CASE-0041
 design_parameter/DP-CASE-0042
+design_parameter/DP-EPCE-0009
 design_parameter/DP-OWNR-0041
 design_parameter/DP-OWNR-0042
 design_parameter/DP-OWNR-0043
+doc_clause/DC-EPCE-0137
+doc_clause/DC-EPCE-0228
+doc_clause/DC-EPCE-0233
+doc_clause/DC-EPCE-0396
+doc_clause/DC-EPCE-0397
+doc_clause/DC-EPCE-0658
+doc_clause/DC-EPCE-0659
 document/ALP-EPC-00000-HS-STU-0002
 document/ALP-EPC-00CQA-IC-SPC-0001</t>
         </is>
@@ -8127,6 +8523,20 @@
       <c r="J124" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-CASE-0044
+doc_clause/DC-EPCE-0137
+doc_clause/DC-EPCE-0204
+doc_clause/DC-EPCE-0205
+doc_clause/DC-EPCE-0379
+doc_clause/DC-EPCE-0380
+doc_clause/DC-EPCE-0381
+doc_clause/DC-EPCE-0382
+doc_clause/DC-EPCE-0383
+doc_clause/DC-EPCE-0401
+doc_clause/DC-EPCE-0402
+doc_clause/DC-EPCE-0403
+doc_clause/DC-EPCE-0404
+doc_clause/DC-EPCE-0453
+doc_clause/DC-EPCE-0668
 document/ALP-EPC-00000-HS-DBR-0001
 document/ALP-EPC-00000-HS-STU-0001
 mdl_rule/DL-DBR-HS</t>
@@ -8192,6 +8602,11 @@
       <c r="J125" s="5" t="inlineStr">
         <is>
           <t>design_parameter/DP-CASE-0045
+design_parameter/DP-EPCE-0010
+doc_clause/DC-EPCE-0379
+doc_clause/DC-EPCE-0402
+doc_clause/DC-EPCE-0658
+doc_clause/DC-EPCE-0668
 document/ALP-EPC-00000-HS-STU-0001</t>
         </is>
       </c>
@@ -8242,7 +8657,19 @@
       <c r="I126" s="4" t="inlineStr"/>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-C01-00000-GE-MOS-0001
+          <t>doc_clause/DC-EPCE-0391
+doc_clause/DC-EPCE-0392
+doc_clause/DC-EPCE-0404
+doc_clause/DC-EPCE-0405
+doc_clause/DC-EPCE-0406
+doc_clause/DC-EPCE-0407
+doc_clause/DC-EPCE-0414
+doc_clause/DC-EPCE-0420
+doc_clause/DC-EPCE-0421
+doc_clause/DC-EPCE-0422
+doc_clause/DC-EPCE-0423
+doc_clause/DC-EPCE-0437
+document/ALP-C01-00000-GE-MOS-0001
 document/ALP-C01-00000-GE-MOS-0002
 document/ALP-C01-00000-GE-MOS-0003
 document/ALP-C01-00000-GE-MOS-0004
@@ -8359,7 +8786,29 @@
       <c r="I127" s="4" t="inlineStr"/>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-EL-LST-0004
+          <t>doc_clause/DC-EPCE-0067
+doc_clause/DC-EPCE-0099
+doc_clause/DC-EPCE-0102
+doc_clause/DC-EPCE-0103
+doc_clause/DC-EPCE-0104
+doc_clause/DC-EPCE-0105
+doc_clause/DC-EPCE-0106
+doc_clause/DC-EPCE-0141
+doc_clause/DC-EPCE-0178
+doc_clause/DC-EPCE-0185
+doc_clause/DC-EPCE-0206
+doc_clause/DC-EPCE-0369
+doc_clause/DC-EPCE-0371
+doc_clause/DC-EPCE-0408
+doc_clause/DC-EPCE-0409
+doc_clause/DC-EPCE-0411
+doc_clause/DC-EPCE-0416
+doc_clause/DC-EPCE-0417
+doc_clause/DC-EPCE-0418
+doc_clause/DC-EPCE-0419
+doc_clause/DC-EPCE-0429
+doc_clause/DC-EPCE-0435
+document/ALP-EPC-00000-EL-LST-0004
 document/ALP-EPC-00000-HS-HAZ-0008
 document/ALP-EPC-00000-HS-RPT-0005</t>
         </is>
@@ -8415,7 +8864,16 @@
       <c r="I128" s="4" t="inlineStr"/>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-HS-DBR-0001
+          <t>doc_clause/DC-EPCE-0173
+doc_clause/DC-EPCE-0178
+doc_clause/DC-EPCE-0411
+doc_clause/DC-EPCE-0415
+doc_clause/DC-EPCE-0431
+doc_clause/DC-EPCE-0432
+doc_clause/DC-EPCE-0433
+doc_clause/DC-EPCE-0434
+doc_clause/DC-EPCE-0438
+document/ALP-EPC-00000-HS-DBR-0001
 document/ALP-EPC-00000-HS-HAZ-0002
 document/ALP-EPC-00000-HS-HAZ-0010
 document/ALP-EPC-00000-HS-RPT-0004
@@ -8470,7 +8928,9 @@
       <c r="I129" s="4" t="inlineStr"/>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-PR-STU-0004</t>
+          <t>doc_clause/DC-EPCE-0341
+doc_clause/DC-EPCE-0438
+document/ALP-EPC-00000-PR-STU-0004</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
@@ -8571,7 +9031,13 @@
       <c r="I131" s="4" t="inlineStr"/>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-C01-00000-GE-ITP-0001
+          <t>doc_clause/DC-EPCE-0489
+doc_clause/DC-EPCE-0588
+doc_clause/DC-EPCE-0589
+doc_clause/DC-EPCE-0590
+doc_clause/DC-EPCE-0591
+doc_clause/DC-EPCE-0592
+document/ALP-C01-00000-GE-ITP-0001
 document/ALP-C02-00000-GE-ITP-0001
 document/ALP-C03-00UPA-GE-ITP-0001
 document/ALP-E12-00000-GE-ITP-0001
@@ -8853,7 +9319,12 @@
       <c r="I132" s="4" t="inlineStr"/>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-E01-00ACA-ME-TRP-0001
+          <t>doc_clause/DC-EPCE-0137
+doc_clause/DC-EPCE-0169
+doc_clause/DC-EPCE-0209
+doc_clause/DC-EPCE-0241
+doc_clause/DC-EPCE-0491
+document/ALP-E01-00ACA-ME-TRP-0001
 document/ALP-E01-00ACA-ME-TST-0001
 document/ALP-E02-10BBT-ME-TRP-0001
 document/ALP-E02-10BBT-ME-TST-0001
@@ -8993,7 +9464,11 @@
       <c r="I133" s="4" t="inlineStr"/>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-E01-00ACA-ME-MDB-0001
+          <t>doc_clause/DC-EPCE-0490
+doc_clause/DC-EPCE-0544
+doc_clause/DC-EPCE-0545
+doc_clause/DC-EPCE-0593
+document/ALP-E01-00ACA-ME-MDB-0001
 document/ALP-E02-10BBT-ME-MDB-0001
 document/ALP-E03-00BBA-ME-MDB-0001
 document/ALP-E04-00BFT-ME-MDB-0001
@@ -9126,7 +9601,8 @@
       <c r="I134" s="4" t="inlineStr"/>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-PI-SPC-0003
+          <t>doc_clause/DC-EPCE-0473
+document/ALP-EPC-00000-PI-SPC-0003
 permit/PMT-013</t>
         </is>
       </c>
@@ -9177,7 +9653,8 @@
       <c r="I135" s="4" t="inlineStr"/>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CM-PLN-0001
+          <t>doc_clause/DC-EPCE-0238
+document/ALP-EPC-00000-CM-PLN-0001
 document/ALP-EPC-00000-CM-PRC-0002
 document/ALP-EPC-00ACA-CM-CMP-0001
 document/ALP-EPC-00ACA-CM-MDB-0001
@@ -9452,7 +9929,9 @@
       <c r="I137" s="4" t="inlineStr"/>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CM-CMP-0003
+          <t>doc_clause/DC-EPCE-0088
+doc_clause/DC-EPCE-0127
+document/ALP-EPC-00000-CM-CMP-0003
 document/ALP-EPC-00000-CM-TRP-0003
 permit/PMT-021</t>
         </is>
@@ -9636,7 +10115,8 @@
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-CM-CMP-0004
+          <t>doc_clause/DC-EPCE-0217
+document/ALP-EPC-00000-CM-CMP-0004
 document/ALP-EPC-00000-CM-TRP-0004</t>
         </is>
       </c>
@@ -9864,7 +10344,51 @@
       <c r="I144" s="4" t="inlineStr"/>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-EPC-00000-PC-SCH-0001</t>
+          <t>doc_clause/DC-EPCE-0685
+doc_clause/DC-EPCE-0686
+doc_clause/DC-EPCE-0687
+doc_clause/DC-EPCE-0688
+doc_clause/DC-EPCE-0690
+doc_clause/DC-EPCE-0691
+doc_clause/DC-EPCE-0692
+doc_clause/DC-EPCE-0693
+doc_clause/DC-EPCE-0696
+doc_clause/DC-EPCE-0697
+doc_clause/DC-EPCE-0698
+doc_clause/DC-EPCE-0700
+doc_clause/DC-EPCE-0701
+doc_clause/DC-EPCE-0702
+doc_clause/DC-EPCE-0703
+doc_clause/DC-EPCE-0704
+doc_clause/DC-EPCE-0705
+doc_clause/DC-EPCE-0706
+doc_clause/DC-EPCE-0707
+doc_clause/DC-EPCE-0708
+doc_clause/DC-EPCE-0714
+doc_clause/DC-EPCE-0715
+doc_clause/DC-EPCE-0716
+doc_clause/DC-EPCE-0717
+doc_clause/DC-EPCE-0718
+doc_clause/DC-EPCE-0719
+doc_clause/DC-EPCE-0720
+doc_clause/DC-EPCE-0722
+doc_clause/DC-EPCE-0723
+doc_clause/DC-EPCE-0724
+doc_clause/DC-EPCE-0725
+doc_clause/DC-EPCE-0728
+doc_clause/DC-EPCE-0729
+doc_clause/DC-EPCE-0730
+doc_clause/DC-EPCE-0731
+doc_clause/DC-EPCE-0732
+doc_clause/DC-EPCE-0733
+doc_clause/DC-EPCE-0734
+doc_clause/DC-EPCE-0735
+doc_clause/DC-EPCE-0736
+doc_clause/DC-EPCE-0737
+doc_clause/DC-EPCE-0738
+doc_clause/DC-EPCE-0739
+doc_clause/DC-EPCE-0740
+document/ALP-EPC-00000-PC-SCH-0001</t>
         </is>
       </c>
       <c r="K144" s="4" t="inlineStr">
@@ -9967,7 +10491,8 @@
       <c r="I146" s="4" t="inlineStr"/>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-E01-00ACA-ME-OMM-0001
+          <t>doc_clause/DC-EPCE-0492
+document/ALP-E01-00ACA-ME-OMM-0001
 document/ALP-E02-10BBT-ME-OMM-0001
 document/ALP-E03-00BBA-ME-OMM-0001
 document/ALP-E04-00BFT-ME-OMM-0001
@@ -10178,7 +10703,9 @@
       <c r="I148" s="4" t="inlineStr"/>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>document/ALP-E01-00ACA-ME-LST-0001
+          <t>doc_clause/DC-EPCE-0492
+doc_clause/DC-EPCE-0493
+document/ALP-E01-00ACA-ME-LST-0001
 document/ALP-E02-10BBT-ME-LST-0001
 document/ALP-E03-00BBA-ME-LST-0001
 document/ALP-E04-00BFT-ME-LST-0001
@@ -10579,7 +11106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-29T02:55:42Z by SETUP | data 8d834179811a9cac</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-29T03:45:18Z by SETUP | data 2b54722a770c3045</t>
         </is>
       </c>
     </row>
@@ -11826,7 +12353,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-29T02:55:42Z by SETUP | data 8d834179811a9cac</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-29T03:45:18Z by SETUP | data 2b54722a770c3045</t>
         </is>
       </c>
     </row>
@@ -15612,7 +16139,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine requirements_matrix v1.0.0 | generated 2026-09-29T02:55:42Z by SETUP | data 8d834179811a9cac</t>
+          <t>engine requirements_matrix v1.0.0 | generated 2026-09-29T03:45:18Z by SETUP | data 2b54722a770c3045</t>
         </is>
       </c>
     </row>
